--- a/Lista Articoli per consultazione.xlsx
+++ b/Lista Articoli per consultazione.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicola.Minguzzi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{331012D5-3021-4939-B82F-D4487121C2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713506E7-BCF0-4465-A950-643E00D55AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Corrugar Rotoli" sheetId="6" r:id="rId1"/>
@@ -42,11 +42,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Kingcor!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Monopipe!$A$1:$C$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Monotubo '!$A$1:$C$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'PE 100 Barre'!$A$1:$C$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'PE 100 Barre'!$A$1:$C$126</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'PE 100 Gas Barre'!$A$1:$C$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'PE 100 Gas Rotoli'!$A$1:$C$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'PE 100 Rotoli'!$A$1:$C$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'RC2'!$A$1:$C$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'RC2'!$A$1:$C$147</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sedici Plus'!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Tripplo '!$A$1:$C$42</definedName>
   </definedNames>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="1557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1642" uniqueCount="1555">
   <si>
     <t>06110P10</t>
   </si>
@@ -644,12 +644,6 @@
   </si>
   <si>
     <t>BARRA POLIER PE100 PN16 110 12m</t>
-  </si>
-  <si>
-    <t>06B110P16M</t>
-  </si>
-  <si>
-    <t>BARRA POLIER 100 AD PN16 110 6m</t>
   </si>
   <si>
     <t>06B110P16RC2</t>
@@ -5096,21 +5090,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C1" t="s">
         <v>1545</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="B2" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="C2">
         <v>40</v>
@@ -5118,10 +5112,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="B3" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C3">
         <v>40</v>
@@ -5129,10 +5123,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="B4" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="C4">
         <v>40</v>
@@ -5140,10 +5134,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="B5" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="C5">
         <v>40</v>
@@ -5151,10 +5145,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="B6" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="C6">
         <v>40</v>
@@ -5162,10 +5156,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="B7" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="C7">
         <v>40</v>
@@ -5173,10 +5167,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="B8" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -5184,10 +5178,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="B9" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="C9">
         <v>40</v>
@@ -5195,10 +5189,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="B10" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C10">
         <v>50</v>
@@ -5206,10 +5200,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="B11" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="C11">
         <v>50</v>
@@ -5217,10 +5211,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B12" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="C12">
         <v>50</v>
@@ -5228,10 +5222,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="B13" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C13">
         <v>50</v>
@@ -5239,10 +5233,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="B14" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="C14">
         <v>50</v>
@@ -5250,10 +5244,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="B15" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="C15">
         <v>50</v>
@@ -5261,10 +5255,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="B16" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="C16">
         <v>50</v>
@@ -5272,10 +5266,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="B17" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C17">
         <v>50</v>
@@ -5283,10 +5277,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="B18" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="C18">
         <v>50</v>
@@ -5294,10 +5288,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="B19" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="C19">
         <v>50</v>
@@ -5305,10 +5299,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B20" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="C20">
         <v>63</v>
@@ -5316,10 +5310,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="B21" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="C21">
         <v>63</v>
@@ -5327,10 +5321,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="B22" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="C22">
         <v>63</v>
@@ -5338,10 +5332,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="B23" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="C23">
         <v>63</v>
@@ -5349,10 +5343,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="B24" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="C24">
         <v>63</v>
@@ -5360,10 +5354,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B25" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="C25">
         <v>63</v>
@@ -5371,10 +5365,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="B26" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="C26">
         <v>63</v>
@@ -5382,10 +5376,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="B27" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="C27">
         <v>63</v>
@@ -5393,10 +5387,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B28" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="C28">
         <v>63</v>
@@ -5404,10 +5398,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="B29" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="C29">
         <v>75</v>
@@ -5415,10 +5409,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="B30" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="C30">
         <v>75</v>
@@ -5426,10 +5420,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="B31" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="C31">
         <v>75</v>
@@ -5437,10 +5431,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="B32" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="C32">
         <v>75</v>
@@ -5448,10 +5442,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="B33" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="C33">
         <v>75</v>
@@ -5459,10 +5453,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B34" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="C34">
         <v>75</v>
@@ -5470,10 +5464,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B35" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="C35">
         <v>75</v>
@@ -5481,10 +5475,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B36" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="C36">
         <v>75</v>
@@ -5492,10 +5486,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="B37" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="C37">
         <v>75</v>
@@ -5503,10 +5497,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="B38" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="C38">
         <v>90</v>
@@ -5514,10 +5508,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B39" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="C39">
         <v>90</v>
@@ -5525,10 +5519,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="B40" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="C40">
         <v>90</v>
@@ -5536,10 +5530,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="B41" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="C41">
         <v>90</v>
@@ -5547,10 +5541,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="B42" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="C42">
         <v>90</v>
@@ -5558,10 +5552,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="B43" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C43">
         <v>90</v>
@@ -5569,10 +5563,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="B44" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="C44">
         <v>90</v>
@@ -5580,10 +5574,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="B45" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C45">
         <v>110</v>
@@ -5591,10 +5585,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B46" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="C46">
         <v>110</v>
@@ -5602,10 +5596,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="B47" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="C47">
         <v>110</v>
@@ -5613,10 +5607,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="B48" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="C48">
         <v>110</v>
@@ -5624,10 +5618,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="B49" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="C49">
         <v>110</v>
@@ -5635,10 +5629,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="B50" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="C50">
         <v>110</v>
@@ -5646,10 +5640,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="B51" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="C51">
         <v>110</v>
@@ -5657,10 +5651,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="B52" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="C52">
         <v>110</v>
@@ -5668,10 +5662,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="B53" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C53">
         <v>125</v>
@@ -5679,10 +5673,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="B54" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C54">
         <v>125</v>
@@ -5690,10 +5684,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="B55" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="C55">
         <v>125</v>
@@ -5701,10 +5695,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="B56" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="C56">
         <v>125</v>
@@ -5712,10 +5706,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B57" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="C57">
         <v>125</v>
@@ -5723,10 +5717,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B58" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="C58">
         <v>125</v>
@@ -5734,10 +5728,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="B59" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="C59">
         <v>125</v>
@@ -5745,10 +5739,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="B60" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C60">
         <v>160</v>
@@ -5756,10 +5750,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="B61" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="C61">
         <v>160</v>
@@ -5767,10 +5761,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="B62" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="C62">
         <v>160</v>
@@ -5778,10 +5772,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="B63" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="C63">
         <v>160</v>
@@ -5789,10 +5783,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="B64" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="C64">
         <v>160</v>
@@ -5800,10 +5794,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B65" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C65">
         <v>160</v>
@@ -5811,10 +5805,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="B66" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="C66">
         <v>160</v>
@@ -5822,10 +5816,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="B67" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C67">
         <v>160</v>
@@ -5833,10 +5827,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="B68" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C68">
         <v>160</v>
@@ -5844,10 +5838,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B69" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="C69">
         <v>160</v>
@@ -5855,10 +5849,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B70" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="C70">
         <v>200</v>
@@ -5866,10 +5860,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="B71" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="C71">
         <v>200</v>
@@ -5877,10 +5871,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="B72" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="C72">
         <v>200</v>
@@ -5888,10 +5882,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="B73" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="C73">
         <v>200</v>
@@ -5899,10 +5893,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B74" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="C74">
         <v>200</v>
@@ -5929,21 +5923,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C1" t="s">
         <v>1545</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B2" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C2">
         <v>20</v>
@@ -5951,10 +5945,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B3" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C3">
         <v>25</v>
@@ -5962,10 +5956,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B4" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="C4">
         <v>25</v>
@@ -5973,10 +5967,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B5" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C5">
         <v>32</v>
@@ -5984,10 +5978,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B6" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C6">
         <v>32</v>
@@ -5995,10 +5989,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B7" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="C7">
         <v>40</v>
@@ -6006,10 +6000,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B8" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -6017,10 +6011,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B9" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="C9">
         <v>40</v>
@@ -6028,10 +6022,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B10" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="C10">
         <v>50</v>
@@ -6039,10 +6033,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B11" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C11">
         <v>50</v>
@@ -6050,10 +6044,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B12" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C12">
         <v>63</v>
@@ -6061,10 +6055,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B13" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="C13">
         <v>63</v>
@@ -6072,10 +6066,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B14" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C14">
         <v>63</v>
@@ -6083,10 +6077,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B15" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="C15">
         <v>75</v>
@@ -6094,10 +6088,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B16" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="C16">
         <v>75</v>
@@ -6105,10 +6099,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="B17" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C17">
         <v>90</v>
@@ -6116,10 +6110,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B18" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="C18">
         <v>90</v>
@@ -6127,10 +6121,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B19" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C19">
         <v>110</v>
@@ -6138,10 +6132,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B20" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C20">
         <v>110</v>
@@ -6149,10 +6143,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B21" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C21">
         <v>125</v>
@@ -6179,21 +6173,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1545</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B2" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="C2">
         <v>125</v>
@@ -6201,10 +6195,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="B3" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="C3">
         <v>125</v>
@@ -6212,10 +6206,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="B4" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="C4">
         <v>160</v>
@@ -6223,10 +6217,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="B5" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="C5">
         <v>160</v>
@@ -6234,10 +6228,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B6" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="C6">
         <v>200</v>
@@ -6245,10 +6239,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="B7" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="C7">
         <v>200</v>
@@ -6256,10 +6250,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="B8" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="C8">
         <v>200</v>
@@ -6267,10 +6261,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="B9" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C9">
         <v>200</v>
@@ -6278,10 +6272,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="B10" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="C10">
         <v>200</v>
@@ -6289,10 +6283,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="B11" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="C11">
         <v>250</v>
@@ -6300,10 +6294,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="B12" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="C12">
         <v>250</v>
@@ -6311,10 +6305,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="B13" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="C13">
         <v>250</v>
@@ -6322,10 +6316,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="B14" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="C14">
         <v>250</v>
@@ -6333,10 +6327,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="B15" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="C15">
         <v>250</v>
@@ -6344,10 +6338,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="B16" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="C16">
         <v>315</v>
@@ -6355,10 +6349,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="B17" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="C17">
         <v>315</v>
@@ -6366,10 +6360,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B18" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="C18">
         <v>315</v>
@@ -6377,10 +6371,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="B19" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="C19">
         <v>315</v>
@@ -6388,10 +6382,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="B20" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="C20">
         <v>400</v>
@@ -6399,10 +6393,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="B21" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -6410,10 +6404,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="B22" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="C22">
         <v>400</v>
@@ -6421,10 +6415,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="B23" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="C23">
         <v>500</v>
@@ -6432,10 +6426,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="B24" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="C24">
         <v>500</v>
@@ -6443,10 +6437,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="B25" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="C25">
         <v>500</v>
@@ -6454,10 +6448,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="B26" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="C26">
         <v>630</v>
@@ -6465,10 +6459,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B27" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="C27">
         <v>630</v>
@@ -6476,10 +6470,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="B28" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="C28">
         <v>630</v>
@@ -6487,10 +6481,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="B29" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="C29">
         <v>800</v>
@@ -6498,10 +6492,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="B30" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="C30">
         <v>800</v>
@@ -6509,10 +6503,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="B31" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="C31">
         <v>800</v>
@@ -6520,10 +6514,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="B32" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="C32">
         <v>930</v>
@@ -6531,10 +6525,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="B33" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="C33">
         <v>930</v>
@@ -6542,10 +6536,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="B34" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="C34">
         <v>1000</v>
@@ -6553,10 +6547,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="B35" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="C35">
         <v>1000</v>
@@ -6564,10 +6558,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="B36" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="C36">
         <v>1200</v>
@@ -6575,10 +6569,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="B37" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="C37">
         <v>1200</v>
@@ -6586,10 +6580,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="B38" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="C38">
         <v>1200</v>
@@ -6607,7 +6601,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12F58F33-338C-4EAE-955A-2D66D12526F9}">
-  <dimension ref="A1:C127"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.28515625" customWidth="1"/>
@@ -6617,21 +6611,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1545</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C2">
         <v>20</v>
@@ -6639,10 +6633,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -6650,10 +6644,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C4">
         <v>25</v>
@@ -6661,10 +6655,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C5">
         <v>25</v>
@@ -6672,10 +6666,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C6">
         <v>32</v>
@@ -6683,10 +6677,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C7">
         <v>32</v>
@@ -6694,10 +6688,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B8" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C8">
         <v>32</v>
@@ -6705,10 +6699,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B9" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C9">
         <v>40</v>
@@ -6716,10 +6710,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B10" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C10">
         <v>40</v>
@@ -6727,10 +6721,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B11" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C11">
         <v>40</v>
@@ -6738,10 +6732,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B12" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C12">
         <v>50</v>
@@ -6749,10 +6743,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B13" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C13">
         <v>50</v>
@@ -6760,10 +6754,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B14" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C14">
         <v>50</v>
@@ -6771,10 +6765,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B15" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C15">
         <v>50</v>
@@ -6782,10 +6776,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B16" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C16">
         <v>50</v>
@@ -6793,10 +6787,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B17" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C17">
         <v>50</v>
@@ -6804,10 +6798,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B18" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C18">
         <v>50</v>
@@ -6815,10 +6809,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B19" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C19">
         <v>63</v>
@@ -6826,10 +6820,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C20">
         <v>63</v>
@@ -6837,10 +6831,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B21" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C21">
         <v>63</v>
@@ -6848,10 +6842,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B22" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C22">
         <v>63</v>
@@ -6859,10 +6853,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B23" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C23">
         <v>63</v>
@@ -6870,10 +6864,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B24" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C24">
         <v>63</v>
@@ -6881,10 +6875,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B25" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C25">
         <v>63</v>
@@ -6892,10 +6886,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B26" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C26">
         <v>63</v>
@@ -6903,10 +6897,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B27" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C27">
         <v>75</v>
@@ -6914,10 +6908,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B28" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C28">
         <v>75</v>
@@ -6925,10 +6919,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B29" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C29">
         <v>75</v>
@@ -6936,10 +6930,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B30" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C30">
         <v>75</v>
@@ -6947,10 +6941,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B31" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C31">
         <v>75</v>
@@ -6958,10 +6952,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B32" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C32">
         <v>75</v>
@@ -6969,10 +6963,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B33" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C33">
         <v>75</v>
@@ -6980,10 +6974,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B34" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C34">
         <v>75</v>
@@ -6991,10 +6985,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B35" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C35">
         <v>90</v>
@@ -7002,10 +6996,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B36" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C36">
         <v>90</v>
@@ -7013,10 +7007,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B37" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C37">
         <v>90</v>
@@ -7024,10 +7018,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B38" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C38">
         <v>90</v>
@@ -7035,10 +7029,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B39" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C39">
         <v>90</v>
@@ -7046,10 +7040,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B40" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C40">
         <v>90</v>
@@ -7057,10 +7051,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B41" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C41">
         <v>90</v>
@@ -7068,10 +7062,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B42" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C42">
         <v>90</v>
@@ -7145,10 +7139,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B49" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C49">
         <v>110</v>
@@ -7173,7 +7167,7 @@
         <v>201</v>
       </c>
       <c r="C51">
-        <v>110</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -7211,10 +7205,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B55" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C55">
         <v>125</v>
@@ -7239,7 +7233,7 @@
         <v>217</v>
       </c>
       <c r="C57">
-        <v>125</v>
+        <v>140</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -7277,10 +7271,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B61" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C61">
         <v>140</v>
@@ -7305,7 +7299,7 @@
         <v>233</v>
       </c>
       <c r="C63">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -7341,28 +7335,6 @@
         <v>160</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>240</v>
-      </c>
-      <c r="B67" t="s">
-        <v>241</v>
-      </c>
-      <c r="C67">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>242</v>
-      </c>
-      <c r="B68" t="s">
-        <v>243</v>
-      </c>
-      <c r="C68">
-        <v>160</v>
-      </c>
-    </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>244</v>
@@ -7393,7 +7365,7 @@
         <v>249</v>
       </c>
       <c r="C71">
-        <v>160</v>
+        <v>180</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -7431,10 +7403,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B75" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C75">
         <v>180</v>
@@ -7459,7 +7431,7 @@
         <v>265</v>
       </c>
       <c r="C77">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -7519,10 +7491,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B83" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C83">
         <v>200</v>
@@ -7541,13 +7513,13 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B85" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C85">
-        <v>200</v>
+        <v>225</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -7585,10 +7557,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B89" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C89">
         <v>225</v>
@@ -7613,7 +7585,7 @@
         <v>305</v>
       </c>
       <c r="C91">
-        <v>225</v>
+        <v>250</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -7662,10 +7634,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B96" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C96">
         <v>250</v>
@@ -7684,13 +7656,13 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B98" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C98">
-        <v>250</v>
+        <v>280</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -7756,7 +7728,7 @@
         <v>341</v>
       </c>
       <c r="C104">
-        <v>280</v>
+        <v>315</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -7794,10 +7766,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B108" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C108">
         <v>315</v>
@@ -7816,13 +7788,13 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B110" t="s">
+        <v>363</v>
+      </c>
+      <c r="C110">
         <v>355</v>
-      </c>
-      <c r="C110">
-        <v>315</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -7877,7 +7849,7 @@
         <v>373</v>
       </c>
       <c r="C115">
-        <v>355</v>
+        <v>400</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -7893,10 +7865,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B117" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C117">
         <v>400</v>
@@ -7937,13 +7909,13 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B121" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C121">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -7965,7 +7937,7 @@
         <v>399</v>
       </c>
       <c r="C123">
-        <v>450</v>
+        <v>500</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -8001,21 +7973,10 @@
         <v>500</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>406</v>
-      </c>
-      <c r="B127" t="s">
-        <v>407</v>
-      </c>
-      <c r="C127">
-        <v>500</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C127" xr:uid="{12F58F33-338C-4EAE-955A-2D66D12526F9}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C127">
-      <sortCondition ref="C1:C127"/>
+  <autoFilter ref="A1:C126" xr:uid="{12F58F33-338C-4EAE-955A-2D66D12526F9}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C126">
+      <sortCondition ref="C1:C126"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8033,18 +7994,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="B1" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C2">
         <v>20</v>
@@ -8052,10 +8013,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -8063,10 +8024,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C4">
         <v>20</v>
@@ -8151,10 +8112,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B12" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C12">
         <v>25</v>
@@ -8162,10 +8123,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B13" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C13">
         <v>25</v>
@@ -8173,10 +8134,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B14" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C14">
         <v>25</v>
@@ -8283,10 +8244,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B24" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C24">
         <v>32</v>
@@ -8932,90 +8893,90 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B117" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C117" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B118" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C118" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B119" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C119" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B120" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C120" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B121" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C121" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B122" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C122" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B123" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C123" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B124" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C124" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
     </row>
   </sheetData>
@@ -9031,7 +8992,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23A339B5-4043-4BE6-BEFA-F44E56E3189D}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:C148"/>
+  <dimension ref="A1:C147"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
@@ -9040,13 +9001,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1545</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1555</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -9062,10 +9023,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C3">
         <v>25</v>
@@ -9084,10 +9045,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C5">
         <v>32</v>
@@ -9117,10 +9078,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B8" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -9152,10 +9113,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B13" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C13">
         <v>50</v>
@@ -9174,10 +9135,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B15" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C15">
         <v>63</v>
@@ -9185,10 +9146,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B16" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C16">
         <v>63</v>
@@ -9196,10 +9157,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B17" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C17">
         <v>63</v>
@@ -9209,10 +9170,10 @@
     <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B20" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C20">
         <v>63</v>
@@ -9220,10 +9181,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B21" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C21">
         <v>63</v>
@@ -9277,10 +9238,10 @@
     <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B28" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C28">
         <v>75</v>
@@ -9288,10 +9249,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B29" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C29">
         <v>75</v>
@@ -9299,10 +9260,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B30" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C30">
         <v>75</v>
@@ -9354,10 +9315,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B35" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C35">
         <v>110</v>
@@ -9366,10 +9327,10 @@
     <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B37" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C37">
         <v>110</v>
@@ -9388,10 +9349,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B39" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C39">
         <v>125</v>
@@ -9401,10 +9362,10 @@
     <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B42" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C42">
         <v>125</v>
@@ -9412,25 +9373,35 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B43" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C43">
         <v>140</v>
       </c>
     </row>
-    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>226</v>
+      </c>
+      <c r="B44" t="s">
+        <v>227</v>
+      </c>
+      <c r="C44">
+        <v>140</v>
+      </c>
+    </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="B45" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C45">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -9446,13 +9417,13 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B47" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C47">
-        <v>160</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -9468,13 +9439,13 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B49" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="C49">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -9488,18 +9459,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>280</v>
-      </c>
-      <c r="B51" t="s">
-        <v>281</v>
-      </c>
-      <c r="C51">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>296</v>
+      </c>
+      <c r="B52" t="s">
+        <v>297</v>
+      </c>
+      <c r="C52">
+        <v>225</v>
+      </c>
+    </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>298</v>
@@ -9513,13 +9484,13 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="B54" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="C54">
-        <v>225</v>
+        <v>250</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -9535,54 +9506,54 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="B56" t="s">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="C56">
-        <v>250</v>
+        <v>315</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="B57" t="s">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="C57">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>378</v>
-      </c>
-      <c r="B58" t="s">
-        <v>379</v>
-      </c>
-      <c r="C58">
         <v>400</v>
       </c>
     </row>
+    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="65" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="77" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="82" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="91" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="98" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="111" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="76" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="81" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="90" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="97" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="110" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="115" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="116" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="117" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="121" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="122" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="123" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="126" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="131" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="125" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="130" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="135" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="136" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="137" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="140" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="139" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>482</v>
+      </c>
+      <c r="B146" t="s">
+        <v>483</v>
+      </c>
+      <c r="C146">
+        <v>90</v>
+      </c>
+    </row>
     <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>484</v>
@@ -9594,26 +9565,15 @@
         <v>90</v>
       </c>
     </row>
-    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>486</v>
-      </c>
-      <c r="B148" t="s">
-        <v>487</v>
-      </c>
-      <c r="C148">
-        <v>90</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C148" xr:uid="{23A339B5-4043-4BE6-BEFA-F44E56E3189D}">
+  <autoFilter ref="A1:C147" xr:uid="{23A339B5-4043-4BE6-BEFA-F44E56E3189D}">
     <filterColumn colId="0">
       <customFilters>
         <customFilter operator="notEqual" val="*RC2*"/>
       </customFilters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C146">
-      <sortCondition ref="C1:C148"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C145">
+      <sortCondition ref="C1:C147"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9632,21 +9592,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1545</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C2">
         <v>25</v>
@@ -9654,10 +9614,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B3" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C3">
         <v>40</v>
@@ -9665,10 +9625,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B4" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C4">
         <v>40</v>
@@ -9676,10 +9636,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B5" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C5">
         <v>40</v>
@@ -9687,10 +9647,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B6" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C6">
         <v>40</v>
@@ -9698,10 +9658,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B7" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C7">
         <v>40</v>
@@ -9709,10 +9669,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B8" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -9720,10 +9680,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B9" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C9">
         <v>40</v>
@@ -9731,10 +9691,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B10" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C10">
         <v>40</v>
@@ -9742,10 +9702,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B11" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C11">
         <v>40</v>
@@ -9753,10 +9713,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B12" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C12">
         <v>40</v>
@@ -9764,10 +9724,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B13" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C13">
         <v>40</v>
@@ -9775,10 +9735,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B14" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C14">
         <v>40</v>
@@ -9786,10 +9746,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B15" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C15">
         <v>40</v>
@@ -9797,10 +9757,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B16" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C16">
         <v>40</v>
@@ -9808,10 +9768,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B17" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C17">
         <v>40</v>
@@ -9819,10 +9779,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B18" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C18">
         <v>40</v>
@@ -9830,10 +9790,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B19" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C19">
         <v>40</v>
@@ -9841,10 +9801,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B20" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C20">
         <v>50</v>
@@ -9852,10 +9812,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B21" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C21">
         <v>50</v>
@@ -9863,10 +9823,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B22" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C22">
         <v>50</v>
@@ -9874,10 +9834,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B23" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C23">
         <v>50</v>
@@ -9885,10 +9845,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B24" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C24">
         <v>50</v>
@@ -9896,10 +9856,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B25" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C25">
         <v>50</v>
@@ -9907,10 +9867,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B26" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C26">
         <v>50</v>
@@ -9918,10 +9878,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B27" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C27">
         <v>50</v>
@@ -9929,10 +9889,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B28" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C28">
         <v>50</v>
@@ -9940,10 +9900,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B29" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C29">
         <v>50</v>
@@ -9951,10 +9911,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B30" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C30">
         <v>50</v>
@@ -9962,10 +9922,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B31" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C31">
         <v>50</v>
@@ -9973,10 +9933,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B32" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C32">
         <v>50</v>
@@ -9984,10 +9944,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B33" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C33">
         <v>50</v>
@@ -9995,10 +9955,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B34" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C34">
         <v>50</v>
@@ -10006,10 +9966,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B35" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C35">
         <v>50</v>
@@ -10017,10 +9977,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B36" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C36">
         <v>50</v>
@@ -10028,10 +9988,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B37" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C37">
         <v>50</v>
@@ -10039,10 +9999,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B38" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C38">
         <v>50</v>
@@ -10050,10 +10010,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B39" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C39">
         <v>63</v>
@@ -10061,10 +10021,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B40" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C40">
         <v>63</v>
@@ -10072,10 +10032,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B41" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C41">
         <v>63</v>
@@ -10083,10 +10043,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B42" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C42">
         <v>63</v>
@@ -10094,10 +10054,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B43" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C43">
         <v>63</v>
@@ -10105,10 +10065,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B44" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C44">
         <v>75</v>
@@ -10116,10 +10076,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B45" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C45">
         <v>75</v>
@@ -10127,10 +10087,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B46" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C46">
         <v>75</v>
@@ -10138,10 +10098,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B47" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C47">
         <v>90</v>
@@ -10149,10 +10109,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B48" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C48">
         <v>90</v>
@@ -10160,10 +10120,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B49" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C49">
         <v>90</v>
@@ -10171,10 +10131,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B50" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C50">
         <v>110</v>
@@ -10182,10 +10142,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B51" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C51">
         <v>110</v>
@@ -10193,10 +10153,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B52" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C52">
         <v>125</v>
@@ -10204,10 +10164,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B53" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C53">
         <v>125</v>
@@ -10215,10 +10175,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B54" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C54">
         <v>125</v>
@@ -10226,10 +10186,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B55" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C55">
         <v>125</v>
@@ -10237,10 +10197,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B56" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C56">
         <v>125</v>
@@ -10248,10 +10208,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B57" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C57">
         <v>140</v>
@@ -10259,10 +10219,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B58" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C58">
         <v>140</v>
@@ -10270,10 +10230,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B59" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C59">
         <v>140</v>
@@ -10281,10 +10241,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B60" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C60">
         <v>140</v>
@@ -10292,10 +10252,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B61" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C61">
         <v>140</v>
@@ -10303,10 +10263,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B62" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C62">
         <v>140</v>
@@ -10314,10 +10274,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B63" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C63">
         <v>160</v>
@@ -10325,10 +10285,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B64" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C64">
         <v>160</v>
@@ -10336,10 +10296,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B65" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C65">
         <v>160</v>
@@ -10347,10 +10307,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B66" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C66">
         <v>160</v>
@@ -10358,10 +10318,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B67" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C67">
         <v>160</v>
@@ -10369,10 +10329,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B68" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C68">
         <v>160</v>
@@ -10380,10 +10340,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B69" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C69">
         <v>160</v>
@@ -10391,10 +10351,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B70" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C70">
         <v>180</v>
@@ -10402,10 +10362,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B71" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C71">
         <v>180</v>
@@ -10413,10 +10373,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B72" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C72">
         <v>180</v>
@@ -10424,10 +10384,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B73" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C73">
         <v>200</v>
@@ -10435,10 +10395,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B74" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C74">
         <v>200</v>
@@ -10446,10 +10406,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B75" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C75">
         <v>200</v>
@@ -10457,10 +10417,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B76" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C76">
         <v>200</v>
@@ -10468,10 +10428,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B77" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C77">
         <v>200</v>
@@ -10479,10 +10439,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B78" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C78">
         <v>200</v>
@@ -10490,10 +10450,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B79" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C79">
         <v>200</v>
@@ -10501,10 +10461,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B80" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C80">
         <v>225</v>
@@ -10512,10 +10472,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B81" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C81">
         <v>225</v>
@@ -10523,10 +10483,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B82" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C82">
         <v>250</v>
@@ -10534,10 +10494,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B83" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C83">
         <v>250</v>
@@ -10545,10 +10505,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B84" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C84">
         <v>250</v>
@@ -10556,10 +10516,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B85" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C85">
         <v>250</v>
@@ -10567,10 +10527,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B86" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C86">
         <v>280</v>
@@ -10578,10 +10538,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B87" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C87">
         <v>280</v>
@@ -10589,10 +10549,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B88" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C88">
         <v>280</v>
@@ -10600,10 +10560,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B89" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C89">
         <v>315</v>
@@ -10611,10 +10571,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B90" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C90">
         <v>315</v>
@@ -10622,10 +10582,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B91" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C91">
         <v>315</v>
@@ -10633,10 +10593,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B92" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C92">
         <v>315</v>
@@ -10644,10 +10604,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B93" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C93">
         <v>400</v>
@@ -10655,10 +10615,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B94" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C94">
         <v>400</v>
@@ -10666,10 +10626,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B95" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C95">
         <v>400</v>
@@ -10677,10 +10637,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B96" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C96">
         <v>500</v>
@@ -10707,21 +10667,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="B1" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C2">
         <v>16</v>
@@ -10729,10 +10689,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B3" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C3">
         <v>16</v>
@@ -10740,10 +10700,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B4" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C4">
         <v>16</v>
@@ -10751,10 +10711,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B5" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C5">
         <v>16</v>
@@ -10762,10 +10722,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B6" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C6">
         <v>16</v>
@@ -10773,10 +10733,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B7" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C7">
         <v>16</v>
@@ -10784,10 +10744,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B8" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C8">
         <v>20</v>
@@ -10795,10 +10755,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B9" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C9">
         <v>20</v>
@@ -10806,10 +10766,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B10" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C10">
         <v>20</v>
@@ -10817,10 +10777,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B11" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C11">
         <v>20</v>
@@ -10828,10 +10788,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B12" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C12">
         <v>20</v>
@@ -10839,10 +10799,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B13" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C13">
         <v>20</v>
@@ -10850,10 +10810,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B14" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C14">
         <v>20</v>
@@ -10861,10 +10821,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B15" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C15">
         <v>20</v>
@@ -10872,10 +10832,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B16" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C16">
         <v>20</v>
@@ -10883,10 +10843,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B17" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C17">
         <v>20</v>
@@ -10894,10 +10854,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B18" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C18">
         <v>20</v>
@@ -10905,10 +10865,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B19" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C19">
         <v>20</v>
@@ -10916,10 +10876,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B20" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C20">
         <v>20</v>
@@ -10927,10 +10887,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B21" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C21">
         <v>25</v>
@@ -10938,10 +10898,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B22" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C22">
         <v>25</v>
@@ -10949,10 +10909,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B23" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C23">
         <v>25</v>
@@ -10960,10 +10920,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B24" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C24">
         <v>25</v>
@@ -10971,10 +10931,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B25" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C25">
         <v>25</v>
@@ -10982,10 +10942,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B26" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -10993,10 +10953,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B27" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C27">
         <v>25</v>
@@ -11004,10 +10964,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B28" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C28">
         <v>25</v>
@@ -11015,10 +10975,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B29" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C29">
         <v>25</v>
@@ -11026,10 +10986,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B30" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C30">
         <v>25</v>
@@ -11037,10 +10997,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B31" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C31">
         <v>32</v>
@@ -11048,10 +11008,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B32" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C32">
         <v>32</v>
@@ -11059,10 +11019,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B33" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C33">
         <v>32</v>
@@ -11070,10 +11030,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B34" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C34">
         <v>32</v>
@@ -11081,10 +11041,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B35" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C35">
         <v>32</v>
@@ -11092,10 +11052,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B36" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C36">
         <v>32</v>
@@ -11103,10 +11063,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B37" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C37">
         <v>32</v>
@@ -11114,10 +11074,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B38" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C38">
         <v>32</v>
@@ -11125,10 +11085,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B39" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C39">
         <v>40</v>
@@ -11136,10 +11096,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B40" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C40">
         <v>40</v>
@@ -11147,10 +11107,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B41" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C41">
         <v>40</v>
@@ -11158,10 +11118,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B42" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C42">
         <v>40</v>
@@ -11169,10 +11129,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B43" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C43">
         <v>40</v>
@@ -11180,10 +11140,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B44" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C44">
         <v>40</v>
@@ -11191,10 +11151,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B45" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C45">
         <v>50</v>
@@ -11202,10 +11162,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B46" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C46">
         <v>50</v>
@@ -11213,10 +11173,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B47" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C47">
         <v>50</v>
@@ -11224,10 +11184,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B48" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C48">
         <v>50</v>
@@ -11235,10 +11195,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B49" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C49">
         <v>50</v>
@@ -11246,10 +11206,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B50" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C50">
         <v>50</v>
@@ -11257,10 +11217,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B51" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C51">
         <v>63</v>
@@ -11268,10 +11228,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B52" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C52">
         <v>63</v>
@@ -11279,10 +11239,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B53" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C53">
         <v>63</v>
@@ -11290,10 +11250,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B54" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C54">
         <v>63</v>
@@ -11301,10 +11261,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B55" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C55">
         <v>75</v>
@@ -11312,10 +11272,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B56" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C56">
         <v>75</v>
@@ -11323,10 +11283,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B57" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C57">
         <v>75</v>
@@ -11334,10 +11294,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B58" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C58">
         <v>75</v>
@@ -11345,10 +11305,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B59" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C59">
         <v>90</v>
@@ -11356,10 +11316,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B60" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C60">
         <v>90</v>
@@ -11367,10 +11327,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B61" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C61">
         <v>110</v>
@@ -11378,10 +11338,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B62" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C62">
         <v>110</v>
@@ -11389,10 +11349,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B63" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C63">
         <v>161</v>
@@ -11400,10 +11360,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B64" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C64">
         <v>161</v>
@@ -11411,10 +11371,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B65" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C65">
         <v>162</v>
@@ -11422,10 +11382,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B66" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C66">
         <v>162</v>
@@ -11433,10 +11393,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B67" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C67">
         <v>162</v>
@@ -11444,10 +11404,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B68" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C68">
         <v>165</v>
@@ -11455,10 +11415,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B69" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C69">
         <v>165</v>
@@ -11485,21 +11445,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1545</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B2" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C2">
         <v>16</v>
@@ -11507,10 +11467,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B3" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C3">
         <v>16</v>
@@ -11518,10 +11478,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B4" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C4">
         <v>16</v>
@@ -11529,10 +11489,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B5" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C5">
         <v>16</v>
@@ -11540,10 +11500,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B6" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C6">
         <v>16</v>
@@ -11551,10 +11511,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B7" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C7">
         <v>16</v>
@@ -11562,10 +11522,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B8" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C8">
         <v>16</v>
@@ -11573,10 +11533,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B9" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C9">
         <v>16</v>
@@ -11584,10 +11544,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B10" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="C10">
         <v>20</v>
@@ -11595,10 +11555,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B11" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C11">
         <v>20</v>
@@ -11606,10 +11566,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B12" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C12">
         <v>20</v>
@@ -11617,10 +11577,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B13" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C13">
         <v>20</v>
@@ -11628,10 +11588,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B14" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C14">
         <v>20</v>
@@ -11639,10 +11599,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B15" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C15">
         <v>20</v>
@@ -11650,10 +11610,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B16" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C16">
         <v>20</v>
@@ -11661,10 +11621,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B17" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="C17">
         <v>25</v>
@@ -11672,10 +11632,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B18" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C18">
         <v>25</v>
@@ -11683,10 +11643,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B19" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C19">
         <v>25</v>
@@ -11694,10 +11654,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B20" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C20">
         <v>25</v>
@@ -11705,10 +11665,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B21" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C21">
         <v>25</v>
@@ -11716,10 +11676,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B22" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C22">
         <v>32</v>
@@ -11727,10 +11687,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B23" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C23">
         <v>32</v>
@@ -11738,10 +11698,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B24" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C24">
         <v>32</v>
@@ -11749,10 +11709,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B25" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="C25">
         <v>32</v>
@@ -11760,10 +11720,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B26" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C26">
         <v>32</v>
@@ -11771,10 +11731,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B27" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C27">
         <v>32</v>
@@ -11782,10 +11742,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B28" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C28">
         <v>40</v>
@@ -11793,10 +11753,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B29" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="C29">
         <v>40</v>
@@ -11804,10 +11764,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B30" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C30">
         <v>40</v>
@@ -11815,10 +11775,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B31" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="C31">
         <v>40</v>
@@ -11826,10 +11786,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B32" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C32">
         <v>40</v>
@@ -11837,10 +11797,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B33" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C33">
         <v>40</v>
@@ -11848,10 +11808,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B34" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C34">
         <v>50</v>
@@ -11859,10 +11819,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B35" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C35">
         <v>50</v>
@@ -11870,10 +11830,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B36" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C36">
         <v>50</v>
@@ -11881,10 +11841,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B37" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C37">
         <v>63</v>
@@ -11892,10 +11852,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B38" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C38">
         <v>63</v>
@@ -11903,10 +11863,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B39" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C39">
         <v>75</v>
@@ -11914,10 +11874,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B40" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="C40">
         <v>75</v>
@@ -11925,10 +11885,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B41" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C41">
         <v>90</v>
@@ -11936,10 +11896,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B42" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C42">
         <v>90</v>
@@ -11947,10 +11907,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B43" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C43">
         <v>110</v>
@@ -11958,10 +11918,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B44" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C44">
         <v>110</v>
@@ -11989,21 +11949,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C1" t="s">
         <v>1545</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B2" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="C2">
         <v>63</v>
@@ -12011,10 +11971,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="B3" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="C3">
         <v>75</v>
@@ -12022,10 +11982,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="B4" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="C4">
         <v>90</v>
@@ -12033,10 +11993,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="B5" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="C5">
         <v>110</v>
@@ -12044,10 +12004,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="B6" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="C6">
         <v>110</v>
@@ -12055,10 +12015,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="B7" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="C7">
         <v>125</v>
@@ -12066,10 +12026,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="B8" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="C8">
         <v>125</v>
@@ -12077,10 +12037,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="B9" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="C9">
         <v>125</v>
@@ -12088,10 +12048,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="B10" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="C10">
         <v>125</v>
@@ -12099,10 +12059,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="B11" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="C11">
         <v>160</v>
@@ -12110,10 +12070,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="B12" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="C12">
         <v>160</v>
@@ -12121,10 +12081,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B13" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="C13">
         <v>160</v>
@@ -12132,10 +12092,10 @@
     </row>
     <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="B14" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="C14">
         <v>125</v>
@@ -12143,10 +12103,10 @@
     </row>
     <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B15" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="C15">
         <v>125</v>
@@ -12154,10 +12114,10 @@
     </row>
     <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B16" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="C16">
         <v>125</v>
@@ -12165,10 +12125,10 @@
     </row>
     <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="B17" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="C17">
         <v>125</v>
@@ -12176,10 +12136,10 @@
     </row>
     <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="B18" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="C18">
         <v>160</v>
@@ -12187,10 +12147,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B19" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="C19">
         <v>160</v>
@@ -12198,10 +12158,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="B20" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="C20">
         <v>200</v>
@@ -12209,10 +12169,10 @@
     </row>
     <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="B21" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="C21">
         <v>160</v>
@@ -12220,10 +12180,10 @@
     </row>
     <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B22" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C22">
         <v>160</v>
@@ -12231,10 +12191,10 @@
     </row>
     <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="B23" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="C23">
         <v>160</v>
@@ -12242,10 +12202,10 @@
     </row>
     <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="B24" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C24">
         <v>160</v>
@@ -12253,10 +12213,10 @@
     </row>
     <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="B25" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C25">
         <v>160</v>
@@ -12264,10 +12224,10 @@
     </row>
     <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B26" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="C26">
         <v>160</v>
@@ -12275,10 +12235,10 @@
     </row>
     <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B27" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -12286,10 +12246,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B28" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -12317,21 +12277,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C1" t="s">
         <v>1545</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="B2" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="C2">
         <v>63</v>
@@ -12339,10 +12299,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="B3" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="C3">
         <v>63</v>
@@ -12350,10 +12310,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="B4" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="C4">
         <v>63</v>
@@ -12361,10 +12321,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B5" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="C5">
         <v>75</v>
@@ -12372,10 +12332,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="B6" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="C6">
         <v>75</v>
@@ -12383,10 +12343,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="B7" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C7">
         <v>75</v>
@@ -12394,10 +12354,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B8" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="C8">
         <v>90</v>
@@ -12405,10 +12365,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="B9" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="C9">
         <v>90</v>
@@ -12416,10 +12376,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="B10" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="C10">
         <v>90</v>
@@ -12427,10 +12387,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B11" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="C11">
         <v>110</v>
@@ -12438,10 +12398,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B12" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="C12">
         <v>110</v>
@@ -12449,10 +12409,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="B13" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C13">
         <v>110</v>
@@ -12460,10 +12420,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="B14" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="C14">
         <v>110</v>
@@ -12471,10 +12431,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B15" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="C15">
         <v>125</v>
@@ -12482,10 +12442,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B16" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="C16">
         <v>125</v>
@@ -12493,10 +12453,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="B17" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="C17">
         <v>125</v>
@@ -12504,10 +12464,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B18" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="C18">
         <v>160</v>
@@ -12515,10 +12475,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="B19" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="C19">
         <v>160</v>
@@ -12526,10 +12486,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="B20" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="C20">
         <v>160</v>
@@ -12537,10 +12497,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="B21" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="C21">
         <v>200</v>
@@ -12548,10 +12508,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="B22" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="C22">
         <v>200</v>
@@ -12579,21 +12539,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C1" t="s">
         <v>1545</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="B2" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="C2">
         <v>75</v>
@@ -12601,10 +12561,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="B3" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="C3">
         <v>90</v>
@@ -12612,10 +12572,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="B4" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="C4">
         <v>110</v>
@@ -12623,10 +12583,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="B5" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="C5">
         <v>125</v>
@@ -12634,10 +12594,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="B6" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="C6">
         <v>160</v>
@@ -12645,10 +12605,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="B7" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="C7">
         <v>200</v>
@@ -12676,21 +12636,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C1" t="s">
         <v>1545</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="B2" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="C2">
         <v>200</v>
@@ -12698,10 +12658,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="B3" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="C3">
         <v>250</v>
@@ -12709,10 +12669,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="B4" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="C4">
         <v>315</v>
@@ -12720,10 +12680,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="B5" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="C5">
         <v>400</v>
@@ -12731,10 +12691,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="B6" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="C6">
         <v>500</v>
@@ -12742,10 +12702,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="B7" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="C7">
         <v>630</v>
@@ -12769,21 +12729,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C1" t="s">
         <v>1545</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="B2" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="C2">
         <v>630</v>
@@ -12791,10 +12751,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="B3" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="C3">
         <v>160</v>
@@ -12802,10 +12762,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="B4" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="C4">
         <v>200</v>
@@ -12813,10 +12773,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="B5" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="C5">
         <v>250</v>
@@ -12824,10 +12784,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="B6" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="C6">
         <v>300</v>
@@ -12835,10 +12795,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="B7" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="C7">
         <v>400</v>
@@ -12846,10 +12806,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="B8" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="C8">
         <v>500</v>
@@ -12857,10 +12817,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="B9" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="C9">
         <v>600</v>
@@ -12885,21 +12845,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C1" t="s">
         <v>1545</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="B2" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="C2">
         <v>110</v>
@@ -12907,10 +12867,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="B3" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="C3">
         <v>110</v>
@@ -12918,10 +12878,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="B4" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C4">
         <v>125</v>
@@ -12929,10 +12889,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="B5" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="C5">
         <v>125</v>
@@ -12940,10 +12900,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="B6" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="C6">
         <v>125</v>
@@ -12951,10 +12911,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="B7" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="C7">
         <v>160</v>
@@ -12962,10 +12922,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="B8" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="C8">
         <v>160</v>
@@ -12973,10 +12933,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="B9" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="C9">
         <v>160</v>
@@ -12984,10 +12944,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="B10" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="C10">
         <v>160</v>
@@ -12995,10 +12955,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="B11" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="C11">
         <v>160</v>
@@ -13006,10 +12966,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="B12" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="C12">
         <v>160</v>
@@ -13017,10 +12977,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="B13" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="C13">
         <v>200</v>
@@ -13028,10 +12988,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="B14" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="C14">
         <v>200</v>
@@ -13039,10 +12999,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="B15" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -13050,10 +13010,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="B16" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="C16">
         <v>200</v>
@@ -13061,10 +13021,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="B17" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="C17">
         <v>200</v>
@@ -13072,10 +13032,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B18" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="C18">
         <v>200</v>
@@ -13083,10 +13043,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="B19" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="C19">
         <v>250</v>
@@ -13094,10 +13054,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="B20" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="C20">
         <v>250</v>
@@ -13105,10 +13065,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="B21" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="C21">
         <v>250</v>
@@ -13116,10 +13076,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="B22" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="C22">
         <v>250</v>
@@ -13127,10 +13087,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B23" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="C23">
         <v>250</v>
@@ -13138,10 +13098,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="B24" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="C24">
         <v>250</v>
@@ -13149,10 +13109,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="B25" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="C25">
         <v>315</v>
@@ -13160,10 +13120,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="B26" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="C26">
         <v>315</v>
@@ -13171,10 +13131,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="B27" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="C27">
         <v>315</v>
@@ -13182,10 +13142,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="B28" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="C28">
         <v>315</v>
@@ -13193,10 +13153,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="B29" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="C29">
         <v>315</v>
@@ -13204,10 +13164,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="B30" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="C30">
         <v>315</v>
@@ -13215,10 +13175,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="B31" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="C31">
         <v>400</v>
@@ -13226,10 +13186,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="B32" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="C32">
         <v>400</v>
@@ -13237,10 +13197,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="B33" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="C33">
         <v>400</v>
@@ -13248,10 +13208,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="B34" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="C34">
         <v>400</v>
@@ -13259,10 +13219,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="B35" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="C35">
         <v>400</v>
@@ -13270,10 +13230,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="B36" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="C36">
         <v>400</v>
@@ -13281,10 +13241,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="B37" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="C37">
         <v>500</v>
@@ -13292,10 +13252,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="B38" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="C38">
         <v>500</v>
@@ -13303,10 +13263,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="B39" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="C39">
         <v>500</v>
@@ -13314,10 +13274,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="B40" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="C40">
         <v>500</v>
@@ -13325,10 +13285,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="B41" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="C41">
         <v>500</v>
@@ -13336,10 +13296,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="B42" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="C42">
         <v>500</v>
@@ -13362,21 +13322,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C1" t="s">
         <v>1545</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="B2" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="C2">
         <v>110</v>
@@ -13384,10 +13344,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="B3" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="C3">
         <v>110</v>
@@ -13395,10 +13355,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B4" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="C4">
         <v>110</v>
@@ -13406,10 +13366,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="B5" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="C5">
         <v>125</v>
@@ -13417,10 +13377,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="B6" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="C6">
         <v>125</v>
@@ -13428,10 +13388,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="B7" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="C7">
         <v>160</v>
@@ -13439,10 +13399,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B8" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="C8">
         <v>160</v>
@@ -13450,10 +13410,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B9" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="C9">
         <v>160</v>
@@ -13461,10 +13421,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="B10" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="C10">
         <v>160</v>
@@ -13472,10 +13432,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="B11" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="C11">
         <v>160</v>
@@ -13483,10 +13443,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="B12" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="C12">
         <v>200</v>
@@ -13494,10 +13454,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="B13" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="C13">
         <v>200</v>
@@ -13505,10 +13465,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="B14" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="C14">
         <v>200</v>
@@ -13516,10 +13476,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="B15" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -13527,10 +13487,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="B16" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="C16">
         <v>250</v>
@@ -13538,10 +13498,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="B17" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="C17">
         <v>250</v>
@@ -13549,10 +13509,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="B18" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="C18">
         <v>250</v>
@@ -13560,10 +13520,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="B19" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="C19">
         <v>250</v>
@@ -13571,10 +13531,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="B20" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="C20">
         <v>315</v>
@@ -13582,10 +13542,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="B21" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="C21">
         <v>315</v>
@@ -13593,10 +13553,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B22" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="C22">
         <v>315</v>
@@ -13604,10 +13564,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="B23" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="C23">
         <v>315</v>
@@ -13615,10 +13575,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="B24" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="C24">
         <v>400</v>
@@ -13626,10 +13586,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="B25" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="C25">
         <v>400</v>
@@ -13637,10 +13597,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="B26" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="C26">
         <v>400</v>
@@ -13648,10 +13608,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="B27" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="C27">
         <v>400</v>
@@ -13659,10 +13619,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="B28" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="C28">
         <v>500</v>
@@ -13670,10 +13630,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="B29" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="C29">
         <v>500</v>
@@ -13681,10 +13641,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="B30" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="C30">
         <v>500</v>
@@ -13707,21 +13667,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C1" t="s">
         <v>1545</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B2" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C2">
         <v>25</v>
@@ -13729,10 +13689,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B3" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C3">
         <v>32</v>
@@ -13740,10 +13700,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="B4" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C4">
         <v>40</v>
@@ -13751,10 +13711,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B5" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C5">
         <v>40</v>
@@ -13762,10 +13722,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="B6" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C6">
         <v>50</v>
@@ -13773,10 +13733,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="B7" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C7">
         <v>50</v>
@@ -13784,10 +13744,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B8" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="C8">
         <v>63</v>
@@ -13795,10 +13755,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B9" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="C9">
         <v>63</v>
@@ -13806,10 +13766,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="B10" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="C10">
         <v>75</v>
@@ -13817,10 +13777,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="B11" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C11">
         <v>75</v>
@@ -13828,10 +13788,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B12" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C12">
         <v>90</v>
@@ -13839,10 +13799,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B13" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="C13">
         <v>90</v>
@@ -13850,10 +13810,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B14" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="C14">
         <v>90</v>
@@ -13861,10 +13821,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="B15" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="C15">
         <v>90</v>
@@ -13872,10 +13832,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B16" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C16">
         <v>110</v>
@@ -13883,10 +13843,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B17" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="C17">
         <v>110</v>
@@ -13894,10 +13854,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B18" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="C18">
         <v>110</v>
@@ -13905,10 +13865,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B19" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C19">
         <v>110</v>
@@ -13916,10 +13876,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B20" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C20">
         <v>125</v>
@@ -13927,10 +13887,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B21" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="C21">
         <v>125</v>
@@ -13938,10 +13898,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B22" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="C22">
         <v>125</v>
@@ -13949,10 +13909,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B23" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="C23">
         <v>125</v>
@@ -13960,10 +13920,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B24" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C24">
         <v>140</v>
@@ -13971,10 +13931,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B25" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C25">
         <v>140</v>
@@ -13982,10 +13942,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B26" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C26">
         <v>140</v>
@@ -13993,10 +13953,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B27" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C27">
         <v>160</v>
@@ -14004,10 +13964,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B28" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C28">
         <v>160</v>
@@ -14015,10 +13975,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B29" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C29">
         <v>160</v>
@@ -14026,10 +13986,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B30" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="C30">
         <v>160</v>
@@ -14037,10 +13997,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B31" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="C31">
         <v>180</v>
@@ -14048,10 +14008,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B32" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C32">
         <v>180</v>
@@ -14059,10 +14019,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B33" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="C33">
         <v>180</v>
@@ -14070,10 +14030,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B34" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C34">
         <v>180</v>
@@ -14081,10 +14041,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B35" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="C35">
         <v>200</v>
@@ -14092,10 +14052,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B36" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C36">
         <v>200</v>
@@ -14103,10 +14063,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="B37" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="C37">
         <v>200</v>
@@ -14114,10 +14074,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B38" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="C38">
         <v>200</v>
@@ -14125,10 +14085,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B39" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="C39">
         <v>225</v>
@@ -14136,10 +14096,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B40" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C40">
         <v>225</v>
@@ -14147,10 +14107,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B41" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="C41">
         <v>225</v>
@@ -14158,10 +14118,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B42" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C42">
         <v>225</v>
@@ -14169,10 +14129,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="B43" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="C43">
         <v>250</v>
@@ -14180,10 +14140,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B44" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="C44">
         <v>250</v>
@@ -14191,10 +14151,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="B45" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="C45">
         <v>250</v>
@@ -14202,10 +14162,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="B46" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="C46">
         <v>250</v>
@@ -14213,10 +14173,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B47" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C47">
         <v>280</v>
@@ -14224,10 +14184,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B48" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C48">
         <v>280</v>
@@ -14235,10 +14195,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B49" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C49">
         <v>280</v>
@@ -14246,10 +14206,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="B50" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C50">
         <v>315</v>
@@ -14257,10 +14217,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B51" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C51">
         <v>315</v>
@@ -14268,10 +14228,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B52" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C52">
         <v>315</v>
@@ -14279,10 +14239,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B53" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="C53">
         <v>355</v>
@@ -14290,10 +14250,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B54" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C54">
         <v>355</v>
@@ -14301,10 +14261,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="B55" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C55">
         <v>355</v>
@@ -14312,10 +14272,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B56" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C56">
         <v>400</v>
@@ -14323,10 +14283,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B57" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C57">
         <v>400</v>
@@ -14334,10 +14294,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="B58" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C58">
         <v>450</v>
@@ -14345,10 +14305,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B59" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C59">
         <v>500</v>

--- a/Lista Articoli per consultazione.xlsx
+++ b/Lista Articoli per consultazione.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicola.Minguzzi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713506E7-BCF0-4465-A950-643E00D55AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8730C684-807B-445B-A382-F323F9223954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Corrugar Rotoli" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Monopipe!$A$1:$C$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Monotubo '!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'PE 100 Barre'!$A$1:$C$126</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'PE 100 Gas Barre'!$A$1:$C$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'PE 100 Gas Barre'!$A$1:$C$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'PE 100 Gas Rotoli'!$A$1:$C$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'PE 100 Rotoli'!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'RC2'!$A$1:$C$147</definedName>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1642" uniqueCount="1555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="1511">
   <si>
     <t>06110P10</t>
   </si>
@@ -2956,18 +2956,6 @@
     <t>BARRA POLIER GAS S5 0110 12m</t>
   </si>
   <si>
-    <t>09B110S8</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 110 6m</t>
-  </si>
-  <si>
-    <t>09B110S8D</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 110 12m</t>
-  </si>
-  <si>
     <t>09B125S5</t>
   </si>
   <si>
@@ -2980,18 +2968,6 @@
     <t>BARRA POLIER GAS S5 0125 12m</t>
   </si>
   <si>
-    <t>09B125S8</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 125 6m</t>
-  </si>
-  <si>
-    <t>09B125S8D</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 125 12m</t>
-  </si>
-  <si>
     <t>09B140S5</t>
   </si>
   <si>
@@ -3004,12 +2980,6 @@
     <t>BARRA POLIER GAS S5 140 12m</t>
   </si>
   <si>
-    <t>09B140S8</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 140 6m</t>
-  </si>
-  <si>
     <t>09B160S5</t>
   </si>
   <si>
@@ -3022,18 +2992,6 @@
     <t>BARRA POLIER GAS S5 160 12m</t>
   </si>
   <si>
-    <t>09B160S8</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 160 6m</t>
-  </si>
-  <si>
-    <t>09B160S8D</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 160 12m</t>
-  </si>
-  <si>
     <t>09B180S5</t>
   </si>
   <si>
@@ -3046,18 +3004,6 @@
     <t>BARRA POLIER GAS S5 0180 M. 12</t>
   </si>
   <si>
-    <t>09B180S8</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 0180 M. 6</t>
-  </si>
-  <si>
-    <t>09B180S8D</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 0180 M. 12</t>
-  </si>
-  <si>
     <t>09B200S5</t>
   </si>
   <si>
@@ -3070,18 +3016,6 @@
     <t>BARRA POLIER GAS S5 200 12m</t>
   </si>
   <si>
-    <t>09B200S8</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 0200 M. 6</t>
-  </si>
-  <si>
-    <t>09B200S8D</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 0200 M. 12</t>
-  </si>
-  <si>
     <t>09B225S5</t>
   </si>
   <si>
@@ -3094,18 +3028,6 @@
     <t>BARRA POLIER GAS S5 0225 M. 12</t>
   </si>
   <si>
-    <t>09B225S8</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 0225 M. 6</t>
-  </si>
-  <si>
-    <t>09B225S8D</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 0225 M. 12</t>
-  </si>
-  <si>
     <t>09B250S5</t>
   </si>
   <si>
@@ -3118,18 +3040,6 @@
     <t>BARRA POLIER GAS S5 250 12m</t>
   </si>
   <si>
-    <t>09B250S8</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 0250 6m</t>
-  </si>
-  <si>
-    <t>09B250S8D</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 0250 M. 12</t>
-  </si>
-  <si>
     <t>09B25S5</t>
   </si>
   <si>
@@ -3148,12 +3058,6 @@
     <t>BARRA POLIER GAS S5 0280 M. 12</t>
   </si>
   <si>
-    <t>09B280S8D</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 0280 M. 12</t>
-  </si>
-  <si>
     <t>09B315S5</t>
   </si>
   <si>
@@ -3166,12 +3070,6 @@
     <t>BARRA POLIER GAS S5 0315 12m</t>
   </si>
   <si>
-    <t>09B315S8</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 0315 M. 6</t>
-  </si>
-  <si>
     <t>09B32S5</t>
   </si>
   <si>
@@ -3190,12 +3088,6 @@
     <t>BARRA POLIER GAS S5 0355 M. 12</t>
   </si>
   <si>
-    <t>09B355S8</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 0355 M. 6</t>
-  </si>
-  <si>
     <t>09B400S5</t>
   </si>
   <si>
@@ -3220,18 +3112,6 @@
     <t>BARRA POLIER GAS S5 040 M.12</t>
   </si>
   <si>
-    <t>09B450S8</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 0450 M. 6</t>
-  </si>
-  <si>
-    <t>09B500S8</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 0500 M. 6</t>
-  </si>
-  <si>
     <t>09B50S5</t>
   </si>
   <si>
@@ -3278,18 +3158,6 @@
   </si>
   <si>
     <t>BARRA POLIER GAS S5 090 M. 12</t>
-  </si>
-  <si>
-    <t>09B90S8</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 090 M. 6</t>
-  </si>
-  <si>
-    <t>09B90S8D</t>
-  </si>
-  <si>
-    <t>BARRA POLIER GAS S8 090 12m</t>
   </si>
   <si>
     <t>19B063R</t>
@@ -5090,21 +4958,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1543</v>
+        <v>1499</v>
       </c>
       <c r="B1" t="s">
-        <v>1544</v>
+        <v>1500</v>
       </c>
       <c r="C1" t="s">
-        <v>1545</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1090</v>
+        <v>1046</v>
       </c>
       <c r="B2" t="s">
-        <v>1091</v>
+        <v>1047</v>
       </c>
       <c r="C2">
         <v>40</v>
@@ -5112,10 +4980,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1162</v>
+        <v>1118</v>
       </c>
       <c r="B3" t="s">
-        <v>1163</v>
+        <v>1119</v>
       </c>
       <c r="C3">
         <v>40</v>
@@ -5123,10 +4991,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1164</v>
+        <v>1120</v>
       </c>
       <c r="B4" t="s">
-        <v>1165</v>
+        <v>1121</v>
       </c>
       <c r="C4">
         <v>40</v>
@@ -5134,10 +5002,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1166</v>
+        <v>1122</v>
       </c>
       <c r="B5" t="s">
-        <v>1167</v>
+        <v>1123</v>
       </c>
       <c r="C5">
         <v>40</v>
@@ -5145,10 +5013,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1168</v>
+        <v>1124</v>
       </c>
       <c r="B6" t="s">
-        <v>1169</v>
+        <v>1125</v>
       </c>
       <c r="C6">
         <v>40</v>
@@ -5156,10 +5024,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1170</v>
+        <v>1126</v>
       </c>
       <c r="B7" t="s">
-        <v>1171</v>
+        <v>1127</v>
       </c>
       <c r="C7">
         <v>40</v>
@@ -5167,10 +5035,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1274</v>
+        <v>1230</v>
       </c>
       <c r="B8" t="s">
-        <v>1275</v>
+        <v>1231</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -5178,10 +5046,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1276</v>
+        <v>1232</v>
       </c>
       <c r="B9" t="s">
-        <v>1277</v>
+        <v>1233</v>
       </c>
       <c r="C9">
         <v>40</v>
@@ -5189,10 +5057,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1092</v>
+        <v>1048</v>
       </c>
       <c r="B10" t="s">
-        <v>1093</v>
+        <v>1049</v>
       </c>
       <c r="C10">
         <v>50</v>
@@ -5200,10 +5068,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1172</v>
+        <v>1128</v>
       </c>
       <c r="B11" t="s">
-        <v>1173</v>
+        <v>1129</v>
       </c>
       <c r="C11">
         <v>50</v>
@@ -5211,10 +5079,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1174</v>
+        <v>1130</v>
       </c>
       <c r="B12" t="s">
-        <v>1175</v>
+        <v>1131</v>
       </c>
       <c r="C12">
         <v>50</v>
@@ -5222,10 +5090,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1176</v>
+        <v>1132</v>
       </c>
       <c r="B13" t="s">
-        <v>1177</v>
+        <v>1133</v>
       </c>
       <c r="C13">
         <v>50</v>
@@ -5233,10 +5101,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1178</v>
+        <v>1134</v>
       </c>
       <c r="B14" t="s">
-        <v>1179</v>
+        <v>1135</v>
       </c>
       <c r="C14">
         <v>50</v>
@@ -5244,10 +5112,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1180</v>
+        <v>1136</v>
       </c>
       <c r="B15" t="s">
-        <v>1181</v>
+        <v>1137</v>
       </c>
       <c r="C15">
         <v>50</v>
@@ -5255,10 +5123,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1182</v>
+        <v>1138</v>
       </c>
       <c r="B16" t="s">
-        <v>1183</v>
+        <v>1139</v>
       </c>
       <c r="C16">
         <v>50</v>
@@ -5266,10 +5134,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1184</v>
+        <v>1140</v>
       </c>
       <c r="B17" t="s">
-        <v>1185</v>
+        <v>1141</v>
       </c>
       <c r="C17">
         <v>50</v>
@@ -5277,10 +5145,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1278</v>
+        <v>1234</v>
       </c>
       <c r="B18" t="s">
-        <v>1279</v>
+        <v>1235</v>
       </c>
       <c r="C18">
         <v>50</v>
@@ -5288,10 +5156,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1280</v>
+        <v>1236</v>
       </c>
       <c r="B19" t="s">
-        <v>1281</v>
+        <v>1237</v>
       </c>
       <c r="C19">
         <v>50</v>
@@ -5299,10 +5167,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1094</v>
+        <v>1050</v>
       </c>
       <c r="B20" t="s">
-        <v>1095</v>
+        <v>1051</v>
       </c>
       <c r="C20">
         <v>63</v>
@@ -5310,10 +5178,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1186</v>
+        <v>1142</v>
       </c>
       <c r="B21" t="s">
-        <v>1187</v>
+        <v>1143</v>
       </c>
       <c r="C21">
         <v>63</v>
@@ -5321,10 +5189,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1188</v>
+        <v>1144</v>
       </c>
       <c r="B22" t="s">
-        <v>1189</v>
+        <v>1145</v>
       </c>
       <c r="C22">
         <v>63</v>
@@ -5332,10 +5200,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1190</v>
+        <v>1146</v>
       </c>
       <c r="B23" t="s">
-        <v>1191</v>
+        <v>1147</v>
       </c>
       <c r="C23">
         <v>63</v>
@@ -5343,10 +5211,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1192</v>
+        <v>1148</v>
       </c>
       <c r="B24" t="s">
-        <v>1193</v>
+        <v>1149</v>
       </c>
       <c r="C24">
         <v>63</v>
@@ -5354,10 +5222,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1194</v>
+        <v>1150</v>
       </c>
       <c r="B25" t="s">
-        <v>1195</v>
+        <v>1151</v>
       </c>
       <c r="C25">
         <v>63</v>
@@ -5365,10 +5233,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1196</v>
+        <v>1152</v>
       </c>
       <c r="B26" t="s">
-        <v>1197</v>
+        <v>1153</v>
       </c>
       <c r="C26">
         <v>63</v>
@@ -5376,10 +5244,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1282</v>
+        <v>1238</v>
       </c>
       <c r="B27" t="s">
-        <v>1283</v>
+        <v>1239</v>
       </c>
       <c r="C27">
         <v>63</v>
@@ -5387,10 +5255,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1284</v>
+        <v>1240</v>
       </c>
       <c r="B28" t="s">
-        <v>1285</v>
+        <v>1241</v>
       </c>
       <c r="C28">
         <v>63</v>
@@ -5398,10 +5266,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1096</v>
+        <v>1052</v>
       </c>
       <c r="B29" t="s">
-        <v>1097</v>
+        <v>1053</v>
       </c>
       <c r="C29">
         <v>75</v>
@@ -5409,10 +5277,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1198</v>
+        <v>1154</v>
       </c>
       <c r="B30" t="s">
-        <v>1199</v>
+        <v>1155</v>
       </c>
       <c r="C30">
         <v>75</v>
@@ -5420,10 +5288,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1200</v>
+        <v>1156</v>
       </c>
       <c r="B31" t="s">
-        <v>1201</v>
+        <v>1157</v>
       </c>
       <c r="C31">
         <v>75</v>
@@ -5431,10 +5299,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1202</v>
+        <v>1158</v>
       </c>
       <c r="B32" t="s">
-        <v>1203</v>
+        <v>1159</v>
       </c>
       <c r="C32">
         <v>75</v>
@@ -5442,10 +5310,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1204</v>
+        <v>1160</v>
       </c>
       <c r="B33" t="s">
-        <v>1205</v>
+        <v>1161</v>
       </c>
       <c r="C33">
         <v>75</v>
@@ -5453,10 +5321,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1206</v>
+        <v>1162</v>
       </c>
       <c r="B34" t="s">
-        <v>1207</v>
+        <v>1163</v>
       </c>
       <c r="C34">
         <v>75</v>
@@ -5464,10 +5332,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1208</v>
+        <v>1164</v>
       </c>
       <c r="B35" t="s">
-        <v>1209</v>
+        <v>1165</v>
       </c>
       <c r="C35">
         <v>75</v>
@@ -5475,10 +5343,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1286</v>
+        <v>1242</v>
       </c>
       <c r="B36" t="s">
-        <v>1287</v>
+        <v>1243</v>
       </c>
       <c r="C36">
         <v>75</v>
@@ -5486,10 +5354,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1288</v>
+        <v>1244</v>
       </c>
       <c r="B37" t="s">
-        <v>1289</v>
+        <v>1245</v>
       </c>
       <c r="C37">
         <v>75</v>
@@ -5497,10 +5365,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1098</v>
+        <v>1054</v>
       </c>
       <c r="B38" t="s">
-        <v>1099</v>
+        <v>1055</v>
       </c>
       <c r="C38">
         <v>90</v>
@@ -5508,10 +5376,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1210</v>
+        <v>1166</v>
       </c>
       <c r="B39" t="s">
-        <v>1211</v>
+        <v>1167</v>
       </c>
       <c r="C39">
         <v>90</v>
@@ -5519,10 +5387,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1214</v>
+        <v>1170</v>
       </c>
       <c r="B40" t="s">
-        <v>1215</v>
+        <v>1171</v>
       </c>
       <c r="C40">
         <v>90</v>
@@ -5530,10 +5398,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1216</v>
+        <v>1172</v>
       </c>
       <c r="B41" t="s">
-        <v>1217</v>
+        <v>1173</v>
       </c>
       <c r="C41">
         <v>90</v>
@@ -5541,10 +5409,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1218</v>
+        <v>1174</v>
       </c>
       <c r="B42" t="s">
-        <v>1219</v>
+        <v>1175</v>
       </c>
       <c r="C42">
         <v>90</v>
@@ -5552,10 +5420,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1220</v>
+        <v>1176</v>
       </c>
       <c r="B43" t="s">
-        <v>1221</v>
+        <v>1177</v>
       </c>
       <c r="C43">
         <v>90</v>
@@ -5563,10 +5431,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1290</v>
+        <v>1246</v>
       </c>
       <c r="B44" t="s">
-        <v>1291</v>
+        <v>1247</v>
       </c>
       <c r="C44">
         <v>90</v>
@@ -5574,10 +5442,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1100</v>
+        <v>1056</v>
       </c>
       <c r="B45" t="s">
-        <v>1101</v>
+        <v>1057</v>
       </c>
       <c r="C45">
         <v>110</v>
@@ -5585,10 +5453,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1222</v>
+        <v>1178</v>
       </c>
       <c r="B46" t="s">
-        <v>1223</v>
+        <v>1179</v>
       </c>
       <c r="C46">
         <v>110</v>
@@ -5596,10 +5464,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1226</v>
+        <v>1182</v>
       </c>
       <c r="B47" t="s">
-        <v>1227</v>
+        <v>1183</v>
       </c>
       <c r="C47">
         <v>110</v>
@@ -5607,10 +5475,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1228</v>
+        <v>1184</v>
       </c>
       <c r="B48" t="s">
-        <v>1229</v>
+        <v>1185</v>
       </c>
       <c r="C48">
         <v>110</v>
@@ -5618,10 +5486,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1230</v>
+        <v>1186</v>
       </c>
       <c r="B49" t="s">
-        <v>1231</v>
+        <v>1187</v>
       </c>
       <c r="C49">
         <v>110</v>
@@ -5629,10 +5497,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1232</v>
+        <v>1188</v>
       </c>
       <c r="B50" t="s">
-        <v>1233</v>
+        <v>1189</v>
       </c>
       <c r="C50">
         <v>110</v>
@@ -5640,10 +5508,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1292</v>
+        <v>1248</v>
       </c>
       <c r="B51" t="s">
-        <v>1293</v>
+        <v>1249</v>
       </c>
       <c r="C51">
         <v>110</v>
@@ -5651,10 +5519,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1294</v>
+        <v>1250</v>
       </c>
       <c r="B52" t="s">
-        <v>1295</v>
+        <v>1251</v>
       </c>
       <c r="C52">
         <v>110</v>
@@ -5662,10 +5530,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1102</v>
+        <v>1058</v>
       </c>
       <c r="B53" t="s">
-        <v>1103</v>
+        <v>1059</v>
       </c>
       <c r="C53">
         <v>125</v>
@@ -5673,10 +5541,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1234</v>
+        <v>1190</v>
       </c>
       <c r="B54" t="s">
-        <v>1235</v>
+        <v>1191</v>
       </c>
       <c r="C54">
         <v>125</v>
@@ -5684,10 +5552,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1296</v>
+        <v>1252</v>
       </c>
       <c r="B55" t="s">
-        <v>1297</v>
+        <v>1253</v>
       </c>
       <c r="C55">
         <v>125</v>
@@ -5695,10 +5563,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1240</v>
+        <v>1196</v>
       </c>
       <c r="B56" t="s">
-        <v>1241</v>
+        <v>1197</v>
       </c>
       <c r="C56">
         <v>125</v>
@@ -5706,10 +5574,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1242</v>
+        <v>1198</v>
       </c>
       <c r="B57" t="s">
-        <v>1243</v>
+        <v>1199</v>
       </c>
       <c r="C57">
         <v>125</v>
@@ -5717,10 +5585,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1244</v>
+        <v>1200</v>
       </c>
       <c r="B58" t="s">
-        <v>1245</v>
+        <v>1201</v>
       </c>
       <c r="C58">
         <v>125</v>
@@ -5728,10 +5596,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1246</v>
+        <v>1202</v>
       </c>
       <c r="B59" t="s">
-        <v>1247</v>
+        <v>1203</v>
       </c>
       <c r="C59">
         <v>125</v>
@@ -5739,10 +5607,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1104</v>
+        <v>1060</v>
       </c>
       <c r="B60" t="s">
-        <v>1105</v>
+        <v>1061</v>
       </c>
       <c r="C60">
         <v>160</v>
@@ -5750,10 +5618,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1298</v>
+        <v>1254</v>
       </c>
       <c r="B61" t="s">
-        <v>1299</v>
+        <v>1255</v>
       </c>
       <c r="C61">
         <v>160</v>
@@ -5761,10 +5629,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1300</v>
+        <v>1256</v>
       </c>
       <c r="B62" t="s">
-        <v>1301</v>
+        <v>1257</v>
       </c>
       <c r="C62">
         <v>160</v>
@@ -5772,10 +5640,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1248</v>
+        <v>1204</v>
       </c>
       <c r="B63" t="s">
-        <v>1249</v>
+        <v>1205</v>
       </c>
       <c r="C63">
         <v>160</v>
@@ -5783,10 +5651,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1254</v>
+        <v>1210</v>
       </c>
       <c r="B64" t="s">
-        <v>1255</v>
+        <v>1211</v>
       </c>
       <c r="C64">
         <v>160</v>
@@ -5794,10 +5662,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1256</v>
+        <v>1212</v>
       </c>
       <c r="B65" t="s">
-        <v>1257</v>
+        <v>1213</v>
       </c>
       <c r="C65">
         <v>160</v>
@@ -5805,10 +5673,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1258</v>
+        <v>1214</v>
       </c>
       <c r="B66" t="s">
-        <v>1259</v>
+        <v>1215</v>
       </c>
       <c r="C66">
         <v>160</v>
@@ -5816,10 +5684,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1260</v>
+        <v>1216</v>
       </c>
       <c r="B67" t="s">
-        <v>1261</v>
+        <v>1217</v>
       </c>
       <c r="C67">
         <v>160</v>
@@ -5827,10 +5695,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1262</v>
+        <v>1218</v>
       </c>
       <c r="B68" t="s">
-        <v>1263</v>
+        <v>1219</v>
       </c>
       <c r="C68">
         <v>160</v>
@@ -5838,10 +5706,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1264</v>
+        <v>1220</v>
       </c>
       <c r="B69" t="s">
-        <v>1265</v>
+        <v>1221</v>
       </c>
       <c r="C69">
         <v>160</v>
@@ -5849,10 +5717,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1106</v>
+        <v>1062</v>
       </c>
       <c r="B70" t="s">
-        <v>1107</v>
+        <v>1063</v>
       </c>
       <c r="C70">
         <v>200</v>
@@ -5860,10 +5728,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1270</v>
+        <v>1226</v>
       </c>
       <c r="B71" t="s">
-        <v>1271</v>
+        <v>1227</v>
       </c>
       <c r="C71">
         <v>200</v>
@@ -5871,10 +5739,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1272</v>
+        <v>1228</v>
       </c>
       <c r="B72" t="s">
-        <v>1273</v>
+        <v>1229</v>
       </c>
       <c r="C72">
         <v>200</v>
@@ -5882,10 +5750,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1302</v>
+        <v>1258</v>
       </c>
       <c r="B73" t="s">
-        <v>1303</v>
+        <v>1259</v>
       </c>
       <c r="C73">
         <v>200</v>
@@ -5893,10 +5761,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1266</v>
+        <v>1222</v>
       </c>
       <c r="B74" t="s">
-        <v>1267</v>
+        <v>1223</v>
       </c>
       <c r="C74">
         <v>200</v>
@@ -5923,13 +5791,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1543</v>
+        <v>1499</v>
       </c>
       <c r="B1" t="s">
-        <v>1544</v>
+        <v>1500</v>
       </c>
       <c r="C1" t="s">
-        <v>1545</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -6173,21 +6041,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1543</v>
+        <v>1499</v>
       </c>
       <c r="B1" t="s">
-        <v>1544</v>
+        <v>1500</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1545</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1314</v>
+        <v>1270</v>
       </c>
       <c r="B2" t="s">
-        <v>1315</v>
+        <v>1271</v>
       </c>
       <c r="C2">
         <v>125</v>
@@ -6195,10 +6063,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1316</v>
+        <v>1272</v>
       </c>
       <c r="B3" t="s">
-        <v>1317</v>
+        <v>1273</v>
       </c>
       <c r="C3">
         <v>125</v>
@@ -6206,10 +6074,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1318</v>
+        <v>1274</v>
       </c>
       <c r="B4" t="s">
-        <v>1319</v>
+        <v>1275</v>
       </c>
       <c r="C4">
         <v>160</v>
@@ -6217,10 +6085,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1320</v>
+        <v>1276</v>
       </c>
       <c r="B5" t="s">
-        <v>1321</v>
+        <v>1277</v>
       </c>
       <c r="C5">
         <v>160</v>
@@ -6228,10 +6096,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1322</v>
+        <v>1278</v>
       </c>
       <c r="B6" t="s">
-        <v>1323</v>
+        <v>1279</v>
       </c>
       <c r="C6">
         <v>200</v>
@@ -6239,10 +6107,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1324</v>
+        <v>1280</v>
       </c>
       <c r="B7" t="s">
-        <v>1325</v>
+        <v>1281</v>
       </c>
       <c r="C7">
         <v>200</v>
@@ -6250,10 +6118,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1326</v>
+        <v>1282</v>
       </c>
       <c r="B8" t="s">
-        <v>1327</v>
+        <v>1283</v>
       </c>
       <c r="C8">
         <v>200</v>
@@ -6261,10 +6129,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1328</v>
+        <v>1284</v>
       </c>
       <c r="B9" t="s">
-        <v>1329</v>
+        <v>1285</v>
       </c>
       <c r="C9">
         <v>200</v>
@@ -6272,10 +6140,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1330</v>
+        <v>1286</v>
       </c>
       <c r="B10" t="s">
-        <v>1331</v>
+        <v>1287</v>
       </c>
       <c r="C10">
         <v>200</v>
@@ -6283,10 +6151,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1332</v>
+        <v>1288</v>
       </c>
       <c r="B11" t="s">
-        <v>1333</v>
+        <v>1289</v>
       </c>
       <c r="C11">
         <v>250</v>
@@ -6294,10 +6162,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1334</v>
+        <v>1290</v>
       </c>
       <c r="B12" t="s">
-        <v>1546</v>
+        <v>1502</v>
       </c>
       <c r="C12">
         <v>250</v>
@@ -6305,10 +6173,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1334</v>
+        <v>1290</v>
       </c>
       <c r="B13" t="s">
-        <v>1335</v>
+        <v>1291</v>
       </c>
       <c r="C13">
         <v>250</v>
@@ -6316,10 +6184,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1336</v>
+        <v>1292</v>
       </c>
       <c r="B14" t="s">
-        <v>1337</v>
+        <v>1293</v>
       </c>
       <c r="C14">
         <v>250</v>
@@ -6327,10 +6195,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1338</v>
+        <v>1294</v>
       </c>
       <c r="B15" t="s">
-        <v>1339</v>
+        <v>1295</v>
       </c>
       <c r="C15">
         <v>250</v>
@@ -6338,10 +6206,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1340</v>
+        <v>1296</v>
       </c>
       <c r="B16" t="s">
-        <v>1341</v>
+        <v>1297</v>
       </c>
       <c r="C16">
         <v>315</v>
@@ -6349,10 +6217,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1342</v>
+        <v>1298</v>
       </c>
       <c r="B17" t="s">
-        <v>1343</v>
+        <v>1299</v>
       </c>
       <c r="C17">
         <v>315</v>
@@ -6360,10 +6228,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1344</v>
+        <v>1300</v>
       </c>
       <c r="B18" t="s">
-        <v>1345</v>
+        <v>1301</v>
       </c>
       <c r="C18">
         <v>315</v>
@@ -6371,10 +6239,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1346</v>
+        <v>1302</v>
       </c>
       <c r="B19" t="s">
-        <v>1347</v>
+        <v>1303</v>
       </c>
       <c r="C19">
         <v>315</v>
@@ -6382,10 +6250,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1348</v>
+        <v>1304</v>
       </c>
       <c r="B20" t="s">
-        <v>1349</v>
+        <v>1305</v>
       </c>
       <c r="C20">
         <v>400</v>
@@ -6393,10 +6261,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1350</v>
+        <v>1306</v>
       </c>
       <c r="B21" t="s">
-        <v>1351</v>
+        <v>1307</v>
       </c>
       <c r="C21">
         <v>400</v>
@@ -6404,10 +6272,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1352</v>
+        <v>1308</v>
       </c>
       <c r="B22" t="s">
-        <v>1353</v>
+        <v>1309</v>
       </c>
       <c r="C22">
         <v>400</v>
@@ -6415,10 +6283,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1354</v>
+        <v>1310</v>
       </c>
       <c r="B23" t="s">
-        <v>1355</v>
+        <v>1311</v>
       </c>
       <c r="C23">
         <v>500</v>
@@ -6426,10 +6294,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1356</v>
+        <v>1312</v>
       </c>
       <c r="B24" t="s">
-        <v>1357</v>
+        <v>1313</v>
       </c>
       <c r="C24">
         <v>500</v>
@@ -6437,10 +6305,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1358</v>
+        <v>1314</v>
       </c>
       <c r="B25" t="s">
-        <v>1359</v>
+        <v>1315</v>
       </c>
       <c r="C25">
         <v>500</v>
@@ -6448,10 +6316,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1360</v>
+        <v>1316</v>
       </c>
       <c r="B26" t="s">
-        <v>1361</v>
+        <v>1317</v>
       </c>
       <c r="C26">
         <v>630</v>
@@ -6459,10 +6327,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1362</v>
+        <v>1318</v>
       </c>
       <c r="B27" t="s">
-        <v>1363</v>
+        <v>1319</v>
       </c>
       <c r="C27">
         <v>630</v>
@@ -6470,10 +6338,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1364</v>
+        <v>1320</v>
       </c>
       <c r="B28" t="s">
-        <v>1365</v>
+        <v>1321</v>
       </c>
       <c r="C28">
         <v>630</v>
@@ -6481,10 +6349,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1366</v>
+        <v>1322</v>
       </c>
       <c r="B29" t="s">
-        <v>1367</v>
+        <v>1323</v>
       </c>
       <c r="C29">
         <v>800</v>
@@ -6492,10 +6360,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1368</v>
+        <v>1324</v>
       </c>
       <c r="B30" t="s">
-        <v>1369</v>
+        <v>1325</v>
       </c>
       <c r="C30">
         <v>800</v>
@@ -6503,10 +6371,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1370</v>
+        <v>1326</v>
       </c>
       <c r="B31" t="s">
-        <v>1371</v>
+        <v>1327</v>
       </c>
       <c r="C31">
         <v>800</v>
@@ -6514,10 +6382,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1372</v>
+        <v>1328</v>
       </c>
       <c r="B32" t="s">
-        <v>1373</v>
+        <v>1329</v>
       </c>
       <c r="C32">
         <v>930</v>
@@ -6525,10 +6393,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1374</v>
+        <v>1330</v>
       </c>
       <c r="B33" t="s">
-        <v>1375</v>
+        <v>1331</v>
       </c>
       <c r="C33">
         <v>930</v>
@@ -6536,10 +6404,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1304</v>
+        <v>1260</v>
       </c>
       <c r="B34" t="s">
-        <v>1305</v>
+        <v>1261</v>
       </c>
       <c r="C34">
         <v>1000</v>
@@ -6547,10 +6415,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1306</v>
+        <v>1262</v>
       </c>
       <c r="B35" t="s">
-        <v>1307</v>
+        <v>1263</v>
       </c>
       <c r="C35">
         <v>1000</v>
@@ -6558,10 +6426,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1308</v>
+        <v>1264</v>
       </c>
       <c r="B36" t="s">
-        <v>1309</v>
+        <v>1265</v>
       </c>
       <c r="C36">
         <v>1200</v>
@@ -6569,10 +6437,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1310</v>
+        <v>1266</v>
       </c>
       <c r="B37" t="s">
-        <v>1311</v>
+        <v>1267</v>
       </c>
       <c r="C37">
         <v>1200</v>
@@ -6580,10 +6448,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1312</v>
+        <v>1268</v>
       </c>
       <c r="B38" t="s">
-        <v>1313</v>
+        <v>1269</v>
       </c>
       <c r="C38">
         <v>1200</v>
@@ -6611,13 +6479,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1543</v>
+        <v>1499</v>
       </c>
       <c r="B1" t="s">
-        <v>1544</v>
+        <v>1500</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1545</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -7994,10 +7862,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1543</v>
+        <v>1499</v>
       </c>
       <c r="B1" t="s">
-        <v>1544</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -8899,7 +8767,7 @@
         <v>491</v>
       </c>
       <c r="C117" t="s">
-        <v>1552</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -8910,7 +8778,7 @@
         <v>493</v>
       </c>
       <c r="C118" t="s">
-        <v>1547</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -8921,7 +8789,7 @@
         <v>495</v>
       </c>
       <c r="C119" t="s">
-        <v>1548</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -8932,7 +8800,7 @@
         <v>497</v>
       </c>
       <c r="C120" t="s">
-        <v>1547</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -8943,7 +8811,7 @@
         <v>499</v>
       </c>
       <c r="C121" t="s">
-        <v>1549</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -8954,7 +8822,7 @@
         <v>501</v>
       </c>
       <c r="C122" t="s">
-        <v>1549</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -8965,7 +8833,7 @@
         <v>503</v>
       </c>
       <c r="C123" t="s">
-        <v>1550</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -8976,7 +8844,7 @@
         <v>505</v>
       </c>
       <c r="C124" t="s">
-        <v>1551</v>
+        <v>1507</v>
       </c>
     </row>
   </sheetData>
@@ -9001,13 +8869,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1543</v>
+        <v>1499</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1553</v>
+        <v>1509</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1545</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -9592,13 +9460,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1543</v>
+        <v>1499</v>
       </c>
       <c r="B1" t="s">
-        <v>1544</v>
+        <v>1500</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1545</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -10667,13 +10535,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1543</v>
+        <v>1499</v>
       </c>
       <c r="B1" t="s">
-        <v>1544</v>
+        <v>1500</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1554</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -11445,13 +11313,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1543</v>
+        <v>1499</v>
       </c>
       <c r="B1" t="s">
-        <v>1544</v>
+        <v>1500</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1545</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -11949,21 +11817,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1543</v>
+        <v>1499</v>
       </c>
       <c r="B1" t="s">
-        <v>1544</v>
+        <v>1500</v>
       </c>
       <c r="C1" t="s">
-        <v>1545</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1074</v>
+        <v>1030</v>
       </c>
       <c r="B2" t="s">
-        <v>1075</v>
+        <v>1031</v>
       </c>
       <c r="C2">
         <v>63</v>
@@ -11971,10 +11839,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1076</v>
+        <v>1032</v>
       </c>
       <c r="B3" t="s">
-        <v>1077</v>
+        <v>1033</v>
       </c>
       <c r="C3">
         <v>75</v>
@@ -11982,10 +11850,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1212</v>
+        <v>1168</v>
       </c>
       <c r="B4" t="s">
-        <v>1213</v>
+        <v>1169</v>
       </c>
       <c r="C4">
         <v>90</v>
@@ -11993,10 +11861,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1078</v>
+        <v>1034</v>
       </c>
       <c r="B5" t="s">
-        <v>1079</v>
+        <v>1035</v>
       </c>
       <c r="C5">
         <v>110</v>
@@ -12004,10 +11872,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1224</v>
+        <v>1180</v>
       </c>
       <c r="B6" t="s">
-        <v>1225</v>
+        <v>1181</v>
       </c>
       <c r="C6">
         <v>110</v>
@@ -12015,10 +11883,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1080</v>
+        <v>1036</v>
       </c>
       <c r="B7" t="s">
-        <v>1081</v>
+        <v>1037</v>
       </c>
       <c r="C7">
         <v>125</v>
@@ -12026,10 +11894,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1082</v>
+        <v>1038</v>
       </c>
       <c r="B8" t="s">
-        <v>1083</v>
+        <v>1039</v>
       </c>
       <c r="C8">
         <v>125</v>
@@ -12037,10 +11905,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1236</v>
+        <v>1192</v>
       </c>
       <c r="B9" t="s">
-        <v>1237</v>
+        <v>1193</v>
       </c>
       <c r="C9">
         <v>125</v>
@@ -12048,10 +11916,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1238</v>
+        <v>1194</v>
       </c>
       <c r="B10" t="s">
-        <v>1239</v>
+        <v>1195</v>
       </c>
       <c r="C10">
         <v>125</v>
@@ -12059,10 +11927,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1084</v>
+        <v>1040</v>
       </c>
       <c r="B11" t="s">
-        <v>1085</v>
+        <v>1041</v>
       </c>
       <c r="C11">
         <v>160</v>
@@ -12070,10 +11938,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1086</v>
+        <v>1042</v>
       </c>
       <c r="B12" t="s">
-        <v>1087</v>
+        <v>1043</v>
       </c>
       <c r="C12">
         <v>160</v>
@@ -12081,10 +11949,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1250</v>
+        <v>1206</v>
       </c>
       <c r="B13" t="s">
-        <v>1251</v>
+        <v>1207</v>
       </c>
       <c r="C13">
         <v>160</v>
@@ -12092,10 +11960,10 @@
     </row>
     <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1240</v>
+        <v>1196</v>
       </c>
       <c r="B14" t="s">
-        <v>1241</v>
+        <v>1197</v>
       </c>
       <c r="C14">
         <v>125</v>
@@ -12103,10 +11971,10 @@
     </row>
     <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1242</v>
+        <v>1198</v>
       </c>
       <c r="B15" t="s">
-        <v>1243</v>
+        <v>1199</v>
       </c>
       <c r="C15">
         <v>125</v>
@@ -12114,10 +11982,10 @@
     </row>
     <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1244</v>
+        <v>1200</v>
       </c>
       <c r="B16" t="s">
-        <v>1245</v>
+        <v>1201</v>
       </c>
       <c r="C16">
         <v>125</v>
@@ -12125,10 +11993,10 @@
     </row>
     <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1246</v>
+        <v>1202</v>
       </c>
       <c r="B17" t="s">
-        <v>1247</v>
+        <v>1203</v>
       </c>
       <c r="C17">
         <v>125</v>
@@ -12136,10 +12004,10 @@
     </row>
     <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1248</v>
+        <v>1204</v>
       </c>
       <c r="B18" t="s">
-        <v>1249</v>
+        <v>1205</v>
       </c>
       <c r="C18">
         <v>160</v>
@@ -12147,10 +12015,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1252</v>
+        <v>1208</v>
       </c>
       <c r="B19" t="s">
-        <v>1253</v>
+        <v>1209</v>
       </c>
       <c r="C19">
         <v>160</v>
@@ -12158,10 +12026,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1088</v>
+        <v>1044</v>
       </c>
       <c r="B20" t="s">
-        <v>1089</v>
+        <v>1045</v>
       </c>
       <c r="C20">
         <v>200</v>
@@ -12169,10 +12037,10 @@
     </row>
     <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1254</v>
+        <v>1210</v>
       </c>
       <c r="B21" t="s">
-        <v>1255</v>
+        <v>1211</v>
       </c>
       <c r="C21">
         <v>160</v>
@@ -12180,10 +12048,10 @@
     </row>
     <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1256</v>
+        <v>1212</v>
       </c>
       <c r="B22" t="s">
-        <v>1257</v>
+        <v>1213</v>
       </c>
       <c r="C22">
         <v>160</v>
@@ -12191,10 +12059,10 @@
     </row>
     <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1258</v>
+        <v>1214</v>
       </c>
       <c r="B23" t="s">
-        <v>1259</v>
+        <v>1215</v>
       </c>
       <c r="C23">
         <v>160</v>
@@ -12202,10 +12070,10 @@
     </row>
     <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1260</v>
+        <v>1216</v>
       </c>
       <c r="B24" t="s">
-        <v>1261</v>
+        <v>1217</v>
       </c>
       <c r="C24">
         <v>160</v>
@@ -12213,10 +12081,10 @@
     </row>
     <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1262</v>
+        <v>1218</v>
       </c>
       <c r="B25" t="s">
-        <v>1263</v>
+        <v>1219</v>
       </c>
       <c r="C25">
         <v>160</v>
@@ -12224,10 +12092,10 @@
     </row>
     <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1264</v>
+        <v>1220</v>
       </c>
       <c r="B26" t="s">
-        <v>1265</v>
+        <v>1221</v>
       </c>
       <c r="C26">
         <v>160</v>
@@ -12235,10 +12103,10 @@
     </row>
     <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1266</v>
+        <v>1222</v>
       </c>
       <c r="B27" t="s">
-        <v>1267</v>
+        <v>1223</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -12246,10 +12114,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1268</v>
+        <v>1224</v>
       </c>
       <c r="B28" t="s">
-        <v>1269</v>
+        <v>1225</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -12277,21 +12145,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1543</v>
+        <v>1499</v>
       </c>
       <c r="B1" t="s">
-        <v>1544</v>
+        <v>1500</v>
       </c>
       <c r="C1" t="s">
-        <v>1545</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1120</v>
+        <v>1076</v>
       </c>
       <c r="B2" t="s">
-        <v>1121</v>
+        <v>1077</v>
       </c>
       <c r="C2">
         <v>63</v>
@@ -12299,10 +12167,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1136</v>
+        <v>1092</v>
       </c>
       <c r="B3" t="s">
-        <v>1137</v>
+        <v>1093</v>
       </c>
       <c r="C3">
         <v>63</v>
@@ -12310,10 +12178,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1138</v>
+        <v>1094</v>
       </c>
       <c r="B4" t="s">
-        <v>1139</v>
+        <v>1095</v>
       </c>
       <c r="C4">
         <v>63</v>
@@ -12321,10 +12189,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1122</v>
+        <v>1078</v>
       </c>
       <c r="B5" t="s">
-        <v>1123</v>
+        <v>1079</v>
       </c>
       <c r="C5">
         <v>75</v>
@@ -12332,10 +12200,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1140</v>
+        <v>1096</v>
       </c>
       <c r="B6" t="s">
-        <v>1141</v>
+        <v>1097</v>
       </c>
       <c r="C6">
         <v>75</v>
@@ -12343,10 +12211,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1142</v>
+        <v>1098</v>
       </c>
       <c r="B7" t="s">
-        <v>1143</v>
+        <v>1099</v>
       </c>
       <c r="C7">
         <v>75</v>
@@ -12354,10 +12222,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1124</v>
+        <v>1080</v>
       </c>
       <c r="B8" t="s">
-        <v>1125</v>
+        <v>1081</v>
       </c>
       <c r="C8">
         <v>90</v>
@@ -12365,10 +12233,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1144</v>
+        <v>1100</v>
       </c>
       <c r="B9" t="s">
-        <v>1145</v>
+        <v>1101</v>
       </c>
       <c r="C9">
         <v>90</v>
@@ -12376,10 +12244,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1146</v>
+        <v>1102</v>
       </c>
       <c r="B10" t="s">
-        <v>1147</v>
+        <v>1103</v>
       </c>
       <c r="C10">
         <v>90</v>
@@ -12387,10 +12255,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1126</v>
+        <v>1082</v>
       </c>
       <c r="B11" t="s">
-        <v>1127</v>
+        <v>1083</v>
       </c>
       <c r="C11">
         <v>110</v>
@@ -12398,10 +12266,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1128</v>
+        <v>1084</v>
       </c>
       <c r="B12" t="s">
-        <v>1129</v>
+        <v>1085</v>
       </c>
       <c r="C12">
         <v>110</v>
@@ -12409,10 +12277,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1148</v>
+        <v>1104</v>
       </c>
       <c r="B13" t="s">
-        <v>1149</v>
+        <v>1105</v>
       </c>
       <c r="C13">
         <v>110</v>
@@ -12420,10 +12288,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1150</v>
+        <v>1106</v>
       </c>
       <c r="B14" t="s">
-        <v>1151</v>
+        <v>1107</v>
       </c>
       <c r="C14">
         <v>110</v>
@@ -12431,10 +12299,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1130</v>
+        <v>1086</v>
       </c>
       <c r="B15" t="s">
-        <v>1131</v>
+        <v>1087</v>
       </c>
       <c r="C15">
         <v>125</v>
@@ -12442,10 +12310,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1152</v>
+        <v>1108</v>
       </c>
       <c r="B16" t="s">
-        <v>1153</v>
+        <v>1109</v>
       </c>
       <c r="C16">
         <v>125</v>
@@ -12453,10 +12321,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1154</v>
+        <v>1110</v>
       </c>
       <c r="B17" t="s">
-        <v>1155</v>
+        <v>1111</v>
       </c>
       <c r="C17">
         <v>125</v>
@@ -12464,10 +12332,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1132</v>
+        <v>1088</v>
       </c>
       <c r="B18" t="s">
-        <v>1133</v>
+        <v>1089</v>
       </c>
       <c r="C18">
         <v>160</v>
@@ -12475,10 +12343,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1156</v>
+        <v>1112</v>
       </c>
       <c r="B19" t="s">
-        <v>1157</v>
+        <v>1113</v>
       </c>
       <c r="C19">
         <v>160</v>
@@ -12486,10 +12354,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1158</v>
+        <v>1114</v>
       </c>
       <c r="B20" t="s">
-        <v>1159</v>
+        <v>1115</v>
       </c>
       <c r="C20">
         <v>160</v>
@@ -12497,10 +12365,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1134</v>
+        <v>1090</v>
       </c>
       <c r="B21" t="s">
-        <v>1135</v>
+        <v>1091</v>
       </c>
       <c r="C21">
         <v>200</v>
@@ -12508,10 +12376,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1160</v>
+        <v>1116</v>
       </c>
       <c r="B22" t="s">
-        <v>1161</v>
+        <v>1117</v>
       </c>
       <c r="C22">
         <v>200</v>
@@ -12539,21 +12407,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1543</v>
+        <v>1499</v>
       </c>
       <c r="B1" t="s">
-        <v>1544</v>
+        <v>1500</v>
       </c>
       <c r="C1" t="s">
-        <v>1545</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1108</v>
+        <v>1064</v>
       </c>
       <c r="B2" t="s">
-        <v>1109</v>
+        <v>1065</v>
       </c>
       <c r="C2">
         <v>75</v>
@@ -12561,10 +12429,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1110</v>
+        <v>1066</v>
       </c>
       <c r="B3" t="s">
-        <v>1111</v>
+        <v>1067</v>
       </c>
       <c r="C3">
         <v>90</v>
@@ -12572,10 +12440,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1112</v>
+        <v>1068</v>
       </c>
       <c r="B4" t="s">
-        <v>1113</v>
+        <v>1069</v>
       </c>
       <c r="C4">
         <v>110</v>
@@ -12583,10 +12451,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1114</v>
+        <v>1070</v>
       </c>
       <c r="B5" t="s">
-        <v>1115</v>
+        <v>1071</v>
       </c>
       <c r="C5">
         <v>125</v>
@@ -12594,10 +12462,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1116</v>
+        <v>1072</v>
       </c>
       <c r="B6" t="s">
-        <v>1117</v>
+        <v>1073</v>
       </c>
       <c r="C6">
         <v>160</v>
@@ -12605,10 +12473,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1118</v>
+        <v>1074</v>
       </c>
       <c r="B7" t="s">
-        <v>1119</v>
+        <v>1075</v>
       </c>
       <c r="C7">
         <v>200</v>
@@ -12636,21 +12504,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1543</v>
+        <v>1499</v>
       </c>
       <c r="B1" t="s">
-        <v>1544</v>
+        <v>1500</v>
       </c>
       <c r="C1" t="s">
-        <v>1545</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1531</v>
+        <v>1487</v>
       </c>
       <c r="B2" t="s">
-        <v>1532</v>
+        <v>1488</v>
       </c>
       <c r="C2">
         <v>200</v>
@@ -12658,10 +12526,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1533</v>
+        <v>1489</v>
       </c>
       <c r="B3" t="s">
-        <v>1534</v>
+        <v>1490</v>
       </c>
       <c r="C3">
         <v>250</v>
@@ -12669,10 +12537,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1535</v>
+        <v>1491</v>
       </c>
       <c r="B4" t="s">
-        <v>1536</v>
+        <v>1492</v>
       </c>
       <c r="C4">
         <v>315</v>
@@ -12680,10 +12548,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1537</v>
+        <v>1493</v>
       </c>
       <c r="B5" t="s">
-        <v>1538</v>
+        <v>1494</v>
       </c>
       <c r="C5">
         <v>400</v>
@@ -12691,10 +12559,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1539</v>
+        <v>1495</v>
       </c>
       <c r="B6" t="s">
-        <v>1540</v>
+        <v>1496</v>
       </c>
       <c r="C6">
         <v>500</v>
@@ -12702,10 +12570,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1541</v>
+        <v>1497</v>
       </c>
       <c r="B7" t="s">
-        <v>1542</v>
+        <v>1498</v>
       </c>
       <c r="C7">
         <v>630</v>
@@ -12729,21 +12597,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1543</v>
+        <v>1499</v>
       </c>
       <c r="B1" t="s">
-        <v>1544</v>
+        <v>1500</v>
       </c>
       <c r="C1" t="s">
-        <v>1545</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1515</v>
+        <v>1471</v>
       </c>
       <c r="B2" t="s">
-        <v>1516</v>
+        <v>1472</v>
       </c>
       <c r="C2">
         <v>630</v>
@@ -12751,10 +12619,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1517</v>
+        <v>1473</v>
       </c>
       <c r="B3" t="s">
-        <v>1518</v>
+        <v>1474</v>
       </c>
       <c r="C3">
         <v>160</v>
@@ -12762,10 +12630,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1519</v>
+        <v>1475</v>
       </c>
       <c r="B4" t="s">
-        <v>1520</v>
+        <v>1476</v>
       </c>
       <c r="C4">
         <v>200</v>
@@ -12773,10 +12641,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1521</v>
+        <v>1477</v>
       </c>
       <c r="B5" t="s">
-        <v>1522</v>
+        <v>1478</v>
       </c>
       <c r="C5">
         <v>250</v>
@@ -12784,10 +12652,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1523</v>
+        <v>1479</v>
       </c>
       <c r="B6" t="s">
-        <v>1524</v>
+        <v>1480</v>
       </c>
       <c r="C6">
         <v>300</v>
@@ -12795,10 +12663,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1525</v>
+        <v>1481</v>
       </c>
       <c r="B7" t="s">
-        <v>1526</v>
+        <v>1482</v>
       </c>
       <c r="C7">
         <v>400</v>
@@ -12806,10 +12674,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1527</v>
+        <v>1483</v>
       </c>
       <c r="B8" t="s">
-        <v>1528</v>
+        <v>1484</v>
       </c>
       <c r="C8">
         <v>500</v>
@@ -12817,10 +12685,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1529</v>
+        <v>1485</v>
       </c>
       <c r="B9" t="s">
-        <v>1530</v>
+        <v>1486</v>
       </c>
       <c r="C9">
         <v>600</v>
@@ -12845,21 +12713,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1543</v>
+        <v>1499</v>
       </c>
       <c r="B1" t="s">
-        <v>1544</v>
+        <v>1500</v>
       </c>
       <c r="C1" t="s">
-        <v>1545</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1382</v>
+        <v>1338</v>
       </c>
       <c r="B2" t="s">
-        <v>1383</v>
+        <v>1339</v>
       </c>
       <c r="C2">
         <v>110</v>
@@ -12867,10 +12735,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1384</v>
+        <v>1340</v>
       </c>
       <c r="B3" t="s">
-        <v>1385</v>
+        <v>1341</v>
       </c>
       <c r="C3">
         <v>110</v>
@@ -12878,10 +12746,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1390</v>
+        <v>1346</v>
       </c>
       <c r="B4" t="s">
-        <v>1391</v>
+        <v>1347</v>
       </c>
       <c r="C4">
         <v>125</v>
@@ -12889,10 +12757,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1392</v>
+        <v>1348</v>
       </c>
       <c r="B5" t="s">
-        <v>1393</v>
+        <v>1349</v>
       </c>
       <c r="C5">
         <v>125</v>
@@ -12900,10 +12768,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1394</v>
+        <v>1350</v>
       </c>
       <c r="B6" t="s">
-        <v>1395</v>
+        <v>1351</v>
       </c>
       <c r="C6">
         <v>125</v>
@@ -12911,10 +12779,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1405</v>
+        <v>1361</v>
       </c>
       <c r="B7" t="s">
-        <v>1406</v>
+        <v>1362</v>
       </c>
       <c r="C7">
         <v>160</v>
@@ -12922,10 +12790,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1407</v>
+        <v>1363</v>
       </c>
       <c r="B8" t="s">
-        <v>1408</v>
+        <v>1364</v>
       </c>
       <c r="C8">
         <v>160</v>
@@ -12933,10 +12801,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1409</v>
+        <v>1365</v>
       </c>
       <c r="B9" t="s">
-        <v>1410</v>
+        <v>1366</v>
       </c>
       <c r="C9">
         <v>160</v>
@@ -12944,10 +12812,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1411</v>
+        <v>1367</v>
       </c>
       <c r="B10" t="s">
-        <v>1412</v>
+        <v>1368</v>
       </c>
       <c r="C10">
         <v>160</v>
@@ -12955,10 +12823,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1413</v>
+        <v>1369</v>
       </c>
       <c r="B11" t="s">
-        <v>1414</v>
+        <v>1370</v>
       </c>
       <c r="C11">
         <v>160</v>
@@ -12966,10 +12834,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1415</v>
+        <v>1371</v>
       </c>
       <c r="B12" t="s">
-        <v>1416</v>
+        <v>1372</v>
       </c>
       <c r="C12">
         <v>160</v>
@@ -12977,10 +12845,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1425</v>
+        <v>1381</v>
       </c>
       <c r="B13" t="s">
-        <v>1426</v>
+        <v>1382</v>
       </c>
       <c r="C13">
         <v>200</v>
@@ -12988,10 +12856,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1427</v>
+        <v>1383</v>
       </c>
       <c r="B14" t="s">
-        <v>1428</v>
+        <v>1384</v>
       </c>
       <c r="C14">
         <v>200</v>
@@ -12999,10 +12867,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1429</v>
+        <v>1385</v>
       </c>
       <c r="B15" t="s">
-        <v>1430</v>
+        <v>1386</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -13010,10 +12878,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1431</v>
+        <v>1387</v>
       </c>
       <c r="B16" t="s">
-        <v>1432</v>
+        <v>1388</v>
       </c>
       <c r="C16">
         <v>200</v>
@@ -13021,10 +12889,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1433</v>
+        <v>1389</v>
       </c>
       <c r="B17" t="s">
-        <v>1434</v>
+        <v>1390</v>
       </c>
       <c r="C17">
         <v>200</v>
@@ -13032,10 +12900,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1435</v>
+        <v>1391</v>
       </c>
       <c r="B18" t="s">
-        <v>1436</v>
+        <v>1392</v>
       </c>
       <c r="C18">
         <v>200</v>
@@ -13043,10 +12911,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1445</v>
+        <v>1401</v>
       </c>
       <c r="B19" t="s">
-        <v>1446</v>
+        <v>1402</v>
       </c>
       <c r="C19">
         <v>250</v>
@@ -13054,10 +12922,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1447</v>
+        <v>1403</v>
       </c>
       <c r="B20" t="s">
-        <v>1448</v>
+        <v>1404</v>
       </c>
       <c r="C20">
         <v>250</v>
@@ -13065,10 +12933,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1449</v>
+        <v>1405</v>
       </c>
       <c r="B21" t="s">
-        <v>1450</v>
+        <v>1406</v>
       </c>
       <c r="C21">
         <v>250</v>
@@ -13076,10 +12944,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1451</v>
+        <v>1407</v>
       </c>
       <c r="B22" t="s">
-        <v>1452</v>
+        <v>1408</v>
       </c>
       <c r="C22">
         <v>250</v>
@@ -13087,10 +12955,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1453</v>
+        <v>1409</v>
       </c>
       <c r="B23" t="s">
-        <v>1454</v>
+        <v>1410</v>
       </c>
       <c r="C23">
         <v>250</v>
@@ -13098,10 +12966,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1455</v>
+        <v>1411</v>
       </c>
       <c r="B24" t="s">
-        <v>1456</v>
+        <v>1412</v>
       </c>
       <c r="C24">
         <v>250</v>
@@ -13109,10 +12977,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1465</v>
+        <v>1421</v>
       </c>
       <c r="B25" t="s">
-        <v>1466</v>
+        <v>1422</v>
       </c>
       <c r="C25">
         <v>315</v>
@@ -13120,10 +12988,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1467</v>
+        <v>1423</v>
       </c>
       <c r="B26" t="s">
-        <v>1468</v>
+        <v>1424</v>
       </c>
       <c r="C26">
         <v>315</v>
@@ -13131,10 +12999,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1469</v>
+        <v>1425</v>
       </c>
       <c r="B27" t="s">
-        <v>1470</v>
+        <v>1426</v>
       </c>
       <c r="C27">
         <v>315</v>
@@ -13142,10 +13010,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1471</v>
+        <v>1427</v>
       </c>
       <c r="B28" t="s">
-        <v>1472</v>
+        <v>1428</v>
       </c>
       <c r="C28">
         <v>315</v>
@@ -13153,10 +13021,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1473</v>
+        <v>1429</v>
       </c>
       <c r="B29" t="s">
-        <v>1474</v>
+        <v>1430</v>
       </c>
       <c r="C29">
         <v>315</v>
@@ -13164,10 +13032,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1475</v>
+        <v>1431</v>
       </c>
       <c r="B30" t="s">
-        <v>1476</v>
+        <v>1432</v>
       </c>
       <c r="C30">
         <v>315</v>
@@ -13175,10 +13043,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1485</v>
+        <v>1441</v>
       </c>
       <c r="B31" t="s">
-        <v>1486</v>
+        <v>1442</v>
       </c>
       <c r="C31">
         <v>400</v>
@@ -13186,10 +13054,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1487</v>
+        <v>1443</v>
       </c>
       <c r="B32" t="s">
-        <v>1488</v>
+        <v>1444</v>
       </c>
       <c r="C32">
         <v>400</v>
@@ -13197,10 +13065,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1489</v>
+        <v>1445</v>
       </c>
       <c r="B33" t="s">
-        <v>1490</v>
+        <v>1446</v>
       </c>
       <c r="C33">
         <v>400</v>
@@ -13208,10 +13076,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1491</v>
+        <v>1447</v>
       </c>
       <c r="B34" t="s">
-        <v>1492</v>
+        <v>1448</v>
       </c>
       <c r="C34">
         <v>400</v>
@@ -13219,10 +13087,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1493</v>
+        <v>1449</v>
       </c>
       <c r="B35" t="s">
-        <v>1494</v>
+        <v>1450</v>
       </c>
       <c r="C35">
         <v>400</v>
@@ -13230,10 +13098,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1495</v>
+        <v>1451</v>
       </c>
       <c r="B36" t="s">
-        <v>1496</v>
+        <v>1452</v>
       </c>
       <c r="C36">
         <v>400</v>
@@ -13241,10 +13109,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1503</v>
+        <v>1459</v>
       </c>
       <c r="B37" t="s">
-        <v>1504</v>
+        <v>1460</v>
       </c>
       <c r="C37">
         <v>500</v>
@@ -13252,10 +13120,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1505</v>
+        <v>1461</v>
       </c>
       <c r="B38" t="s">
-        <v>1506</v>
+        <v>1462</v>
       </c>
       <c r="C38">
         <v>500</v>
@@ -13263,10 +13131,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1507</v>
+        <v>1463</v>
       </c>
       <c r="B39" t="s">
-        <v>1508</v>
+        <v>1464</v>
       </c>
       <c r="C39">
         <v>500</v>
@@ -13274,10 +13142,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1509</v>
+        <v>1465</v>
       </c>
       <c r="B40" t="s">
-        <v>1510</v>
+        <v>1466</v>
       </c>
       <c r="C40">
         <v>500</v>
@@ -13285,10 +13153,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1511</v>
+        <v>1467</v>
       </c>
       <c r="B41" t="s">
-        <v>1512</v>
+        <v>1468</v>
       </c>
       <c r="C41">
         <v>500</v>
@@ -13296,10 +13164,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1513</v>
+        <v>1469</v>
       </c>
       <c r="B42" t="s">
-        <v>1514</v>
+        <v>1470</v>
       </c>
       <c r="C42">
         <v>500</v>
@@ -13322,21 +13190,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1543</v>
+        <v>1499</v>
       </c>
       <c r="B1" t="s">
-        <v>1544</v>
+        <v>1500</v>
       </c>
       <c r="C1" t="s">
-        <v>1545</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1376</v>
+        <v>1332</v>
       </c>
       <c r="B2" t="s">
-        <v>1377</v>
+        <v>1333</v>
       </c>
       <c r="C2">
         <v>110</v>
@@ -13344,10 +13212,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1378</v>
+        <v>1334</v>
       </c>
       <c r="B3" t="s">
-        <v>1379</v>
+        <v>1335</v>
       </c>
       <c r="C3">
         <v>110</v>
@@ -13355,10 +13223,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1380</v>
+        <v>1336</v>
       </c>
       <c r="B4" t="s">
-        <v>1381</v>
+        <v>1337</v>
       </c>
       <c r="C4">
         <v>110</v>
@@ -13366,10 +13234,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1386</v>
+        <v>1342</v>
       </c>
       <c r="B5" t="s">
-        <v>1387</v>
+        <v>1343</v>
       </c>
       <c r="C5">
         <v>125</v>
@@ -13377,10 +13245,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1388</v>
+        <v>1344</v>
       </c>
       <c r="B6" t="s">
-        <v>1389</v>
+        <v>1345</v>
       </c>
       <c r="C6">
         <v>125</v>
@@ -13388,10 +13256,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1396</v>
+        <v>1352</v>
       </c>
       <c r="B7" t="s">
-        <v>1397</v>
+        <v>1353</v>
       </c>
       <c r="C7">
         <v>160</v>
@@ -13399,10 +13267,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1398</v>
+        <v>1354</v>
       </c>
       <c r="B8" t="s">
-        <v>1399</v>
+        <v>1355</v>
       </c>
       <c r="C8">
         <v>160</v>
@@ -13410,10 +13278,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1400</v>
+        <v>1356</v>
       </c>
       <c r="B9" t="s">
-        <v>1399</v>
+        <v>1355</v>
       </c>
       <c r="C9">
         <v>160</v>
@@ -13421,10 +13289,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1401</v>
+        <v>1357</v>
       </c>
       <c r="B10" t="s">
-        <v>1402</v>
+        <v>1358</v>
       </c>
       <c r="C10">
         <v>160</v>
@@ -13432,10 +13300,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1403</v>
+        <v>1359</v>
       </c>
       <c r="B11" t="s">
-        <v>1404</v>
+        <v>1360</v>
       </c>
       <c r="C11">
         <v>160</v>
@@ -13443,10 +13311,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1417</v>
+        <v>1373</v>
       </c>
       <c r="B12" t="s">
-        <v>1418</v>
+        <v>1374</v>
       </c>
       <c r="C12">
         <v>200</v>
@@ -13454,10 +13322,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1419</v>
+        <v>1375</v>
       </c>
       <c r="B13" t="s">
-        <v>1420</v>
+        <v>1376</v>
       </c>
       <c r="C13">
         <v>200</v>
@@ -13465,10 +13333,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1421</v>
+        <v>1377</v>
       </c>
       <c r="B14" t="s">
-        <v>1422</v>
+        <v>1378</v>
       </c>
       <c r="C14">
         <v>200</v>
@@ -13476,10 +13344,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1423</v>
+        <v>1379</v>
       </c>
       <c r="B15" t="s">
-        <v>1424</v>
+        <v>1380</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -13487,10 +13355,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1437</v>
+        <v>1393</v>
       </c>
       <c r="B16" t="s">
-        <v>1438</v>
+        <v>1394</v>
       </c>
       <c r="C16">
         <v>250</v>
@@ -13498,10 +13366,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1439</v>
+        <v>1395</v>
       </c>
       <c r="B17" t="s">
-        <v>1440</v>
+        <v>1396</v>
       </c>
       <c r="C17">
         <v>250</v>
@@ -13509,10 +13377,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1441</v>
+        <v>1397</v>
       </c>
       <c r="B18" t="s">
-        <v>1442</v>
+        <v>1398</v>
       </c>
       <c r="C18">
         <v>250</v>
@@ -13520,10 +13388,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1443</v>
+        <v>1399</v>
       </c>
       <c r="B19" t="s">
-        <v>1444</v>
+        <v>1400</v>
       </c>
       <c r="C19">
         <v>250</v>
@@ -13531,10 +13399,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1457</v>
+        <v>1413</v>
       </c>
       <c r="B20" t="s">
-        <v>1458</v>
+        <v>1414</v>
       </c>
       <c r="C20">
         <v>315</v>
@@ -13542,10 +13410,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1459</v>
+        <v>1415</v>
       </c>
       <c r="B21" t="s">
-        <v>1460</v>
+        <v>1416</v>
       </c>
       <c r="C21">
         <v>315</v>
@@ -13553,10 +13421,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1461</v>
+        <v>1417</v>
       </c>
       <c r="B22" t="s">
-        <v>1462</v>
+        <v>1418</v>
       </c>
       <c r="C22">
         <v>315</v>
@@ -13564,10 +13432,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1463</v>
+        <v>1419</v>
       </c>
       <c r="B23" t="s">
-        <v>1464</v>
+        <v>1420</v>
       </c>
       <c r="C23">
         <v>315</v>
@@ -13575,10 +13443,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1477</v>
+        <v>1433</v>
       </c>
       <c r="B24" t="s">
-        <v>1478</v>
+        <v>1434</v>
       </c>
       <c r="C24">
         <v>400</v>
@@ -13586,10 +13454,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1479</v>
+        <v>1435</v>
       </c>
       <c r="B25" t="s">
-        <v>1480</v>
+        <v>1436</v>
       </c>
       <c r="C25">
         <v>400</v>
@@ -13597,10 +13465,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1481</v>
+        <v>1437</v>
       </c>
       <c r="B26" t="s">
-        <v>1482</v>
+        <v>1438</v>
       </c>
       <c r="C26">
         <v>400</v>
@@ -13608,10 +13476,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1483</v>
+        <v>1439</v>
       </c>
       <c r="B27" t="s">
-        <v>1484</v>
+        <v>1440</v>
       </c>
       <c r="C27">
         <v>400</v>
@@ -13619,10 +13487,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1497</v>
+        <v>1453</v>
       </c>
       <c r="B28" t="s">
-        <v>1498</v>
+        <v>1454</v>
       </c>
       <c r="C28">
         <v>500</v>
@@ -13630,10 +13498,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1499</v>
+        <v>1455</v>
       </c>
       <c r="B29" t="s">
-        <v>1500</v>
+        <v>1456</v>
       </c>
       <c r="C29">
         <v>500</v>
@@ -13641,10 +13509,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1501</v>
+        <v>1457</v>
       </c>
       <c r="B30" t="s">
-        <v>1502</v>
+        <v>1458</v>
       </c>
       <c r="C30">
         <v>500</v>
@@ -13658,7 +13526,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95D8859B-2510-4C5A-B75B-5EB593F58EA9}">
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -13667,21 +13535,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1543</v>
+        <v>1499</v>
       </c>
       <c r="B1" t="s">
-        <v>1544</v>
+        <v>1500</v>
       </c>
       <c r="C1" t="s">
-        <v>1545</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="B2" t="s">
-        <v>1021</v>
+        <v>991</v>
       </c>
       <c r="C2">
         <v>25</v>
@@ -13689,10 +13557,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1034</v>
+        <v>1000</v>
       </c>
       <c r="B3" t="s">
-        <v>1035</v>
+        <v>1001</v>
       </c>
       <c r="C3">
         <v>32</v>
@@ -13700,10 +13568,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1046</v>
+        <v>1010</v>
       </c>
       <c r="B4" t="s">
-        <v>1047</v>
+        <v>1011</v>
       </c>
       <c r="C4">
         <v>40</v>
@@ -13711,10 +13579,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1048</v>
+        <v>1012</v>
       </c>
       <c r="B5" t="s">
-        <v>1049</v>
+        <v>1013</v>
       </c>
       <c r="C5">
         <v>40</v>
@@ -13722,10 +13590,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1054</v>
+        <v>1014</v>
       </c>
       <c r="B6" t="s">
-        <v>1055</v>
+        <v>1015</v>
       </c>
       <c r="C6">
         <v>50</v>
@@ -13733,10 +13601,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1056</v>
+        <v>1016</v>
       </c>
       <c r="B7" t="s">
-        <v>1057</v>
+        <v>1017</v>
       </c>
       <c r="C7">
         <v>50</v>
@@ -13744,10 +13612,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1058</v>
+        <v>1018</v>
       </c>
       <c r="B8" t="s">
-        <v>1059</v>
+        <v>1019</v>
       </c>
       <c r="C8">
         <v>63</v>
@@ -13755,10 +13623,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1060</v>
+        <v>1020</v>
       </c>
       <c r="B9" t="s">
-        <v>1061</v>
+        <v>1021</v>
       </c>
       <c r="C9">
         <v>63</v>
@@ -13766,10 +13634,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1062</v>
+        <v>1022</v>
       </c>
       <c r="B10" t="s">
-        <v>1063</v>
+        <v>1023</v>
       </c>
       <c r="C10">
         <v>75</v>
@@ -13777,10 +13645,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1064</v>
+        <v>1024</v>
       </c>
       <c r="B11" t="s">
-        <v>1065</v>
+        <v>1025</v>
       </c>
       <c r="C11">
         <v>75</v>
@@ -13788,10 +13656,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1066</v>
+        <v>1026</v>
       </c>
       <c r="B12" t="s">
-        <v>1067</v>
+        <v>1027</v>
       </c>
       <c r="C12">
         <v>90</v>
@@ -13799,10 +13667,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1068</v>
+        <v>1028</v>
       </c>
       <c r="B13" t="s">
-        <v>1069</v>
+        <v>1029</v>
       </c>
       <c r="C13">
         <v>90</v>
@@ -13810,513 +13678,271 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1070</v>
+        <v>958</v>
       </c>
       <c r="B14" t="s">
-        <v>1071</v>
+        <v>959</v>
       </c>
       <c r="C14">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1072</v>
+        <v>960</v>
       </c>
       <c r="B15" t="s">
-        <v>1073</v>
+        <v>961</v>
       </c>
       <c r="C15">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="B16" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="C16">
-        <v>110</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="B17" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="C17">
-        <v>110</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="B18" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="C18">
-        <v>110</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="B19" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="C19">
-        <v>110</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="B20" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="C20">
-        <v>125</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="B21" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="C21">
-        <v>125</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="B22" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="C22">
-        <v>125</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="B23" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="C23">
-        <v>125</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="B24" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="C24">
-        <v>140</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="B25" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="C25">
-        <v>140</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="B26" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="C26">
-        <v>140</v>
+        <v>225</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="B27" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="C27">
-        <v>160</v>
+        <v>225</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="B28" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="C28">
-        <v>160</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="B29" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="C29">
-        <v>160</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="B30" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="C30">
-        <v>160</v>
+        <v>280</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="B31" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="C31">
-        <v>180</v>
+        <v>280</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="B32" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="C32">
-        <v>180</v>
+        <v>315</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="B33" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="C33">
-        <v>180</v>
+        <v>315</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
       <c r="B34" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
       <c r="C34">
-        <v>180</v>
+        <v>355</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="B35" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
       <c r="C35">
-        <v>200</v>
+        <v>355</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="B36" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
       <c r="C36">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="B37" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
       <c r="C37">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B38" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C38">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1005</v>
-      </c>
-      <c r="C39">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>1006</v>
-      </c>
-      <c r="B40" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C40">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B41" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C41">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C42">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>1012</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1013</v>
-      </c>
-      <c r="C43">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B44" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C44">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>1016</v>
-      </c>
-      <c r="B45" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C45">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>1018</v>
-      </c>
-      <c r="B46" t="s">
-        <v>1019</v>
-      </c>
-      <c r="C46">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>1022</v>
-      </c>
-      <c r="B47" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C47">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B48" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C48">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B49" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C49">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B50" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C50">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B51" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C51">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>1032</v>
-      </c>
-      <c r="B52" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C52">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B53" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C53">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B54" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C54">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>1040</v>
-      </c>
-      <c r="B55" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C55">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>1042</v>
-      </c>
-      <c r="B56" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C56">
         <v>400</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B57" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C57">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B58" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C58">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>1052</v>
-      </c>
-      <c r="B59" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C59">
-        <v>500</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C59" xr:uid="{59BC1178-1591-4F9F-8FFF-EC12F4EB22BB}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C59">
+  <autoFilter ref="A1:C37" xr:uid="{59BC1178-1591-4F9F-8FFF-EC12F4EB22BB}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C37">
       <sortCondition ref="C1"/>
     </sortState>
   </autoFilter>

--- a/Lista Articoli per consultazione.xlsx
+++ b/Lista Articoli per consultazione.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicola.Minguzzi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49709F44-D510-4F8D-A77F-394BC0797A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89348253-FD41-47B4-BF55-59F4F9EA61AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Corrugar Rotoli" sheetId="6" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2223" uniqueCount="1564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2194" uniqueCount="1560">
   <si>
     <t>06110P10</t>
   </si>
@@ -3826,12 +3826,6 @@
     <t>TUBO PE FGN CORR. SN8 930 M6</t>
   </si>
   <si>
-    <t>43930ML</t>
-  </si>
-  <si>
-    <t>TUBO PE FGN CORR. SN4 DE930 / DI800 6m</t>
-  </si>
-  <si>
     <t>5311016M3</t>
   </si>
   <si>
@@ -4336,9 +4330,6 @@
     <t>Diametro</t>
   </si>
   <si>
-    <t>FLUID PE FGN CORR. SN 0250 M3</t>
-  </si>
-  <si>
     <t>Articolo</t>
   </si>
   <si>
@@ -4463,9 +4454,6 @@
   </si>
   <si>
     <t>SN8 M3</t>
-  </si>
-  <si>
-    <t>SN 0250 M3</t>
   </si>
   <si>
     <t>SN4 M3</t>
@@ -4800,11 +4788,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -5120,16 +5106,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C1" t="s">
         <v>1419</v>
       </c>
-      <c r="B1" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1421</v>
-      </c>
       <c r="D1" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -5143,7 +5129,7 @@
         <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -5157,7 +5143,7 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -5171,7 +5157,7 @@
         <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -5185,7 +5171,7 @@
         <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -5199,7 +5185,7 @@
         <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -5213,7 +5199,7 @@
         <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -5227,7 +5213,7 @@
         <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -5241,7 +5227,7 @@
         <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -5255,7 +5241,7 @@
         <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -5269,7 +5255,7 @@
         <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -5283,7 +5269,7 @@
         <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -5297,7 +5283,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -5311,7 +5297,7 @@
         <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -5325,7 +5311,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -5339,7 +5325,7 @@
         <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -5353,7 +5339,7 @@
         <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -5367,7 +5353,7 @@
         <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -5381,7 +5367,7 @@
         <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -5395,7 +5381,7 @@
         <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -5409,7 +5395,7 @@
         <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -5423,7 +5409,7 @@
         <v>63</v>
       </c>
       <c r="D22" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -5437,7 +5423,7 @@
         <v>63</v>
       </c>
       <c r="D23" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -5451,7 +5437,7 @@
         <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -5465,7 +5451,7 @@
         <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -5479,7 +5465,7 @@
         <v>63</v>
       </c>
       <c r="D26" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -5493,7 +5479,7 @@
         <v>63</v>
       </c>
       <c r="D27" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -5507,7 +5493,7 @@
         <v>75</v>
       </c>
       <c r="D28" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -5521,7 +5507,7 @@
         <v>75</v>
       </c>
       <c r="D29" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -5535,7 +5521,7 @@
         <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -5549,7 +5535,7 @@
         <v>75</v>
       </c>
       <c r="D31" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -5563,7 +5549,7 @@
         <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -5577,7 +5563,7 @@
         <v>75</v>
       </c>
       <c r="D33" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -5591,7 +5577,7 @@
         <v>75</v>
       </c>
       <c r="D34" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -5605,7 +5591,7 @@
         <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -5619,7 +5605,7 @@
         <v>75</v>
       </c>
       <c r="D36" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -5633,7 +5619,7 @@
         <v>90</v>
       </c>
       <c r="D37" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -5647,7 +5633,7 @@
         <v>90</v>
       </c>
       <c r="D38" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -5661,7 +5647,7 @@
         <v>90</v>
       </c>
       <c r="D39" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -5675,7 +5661,7 @@
         <v>90</v>
       </c>
       <c r="D40" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -5689,7 +5675,7 @@
         <v>90</v>
       </c>
       <c r="D41" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -5703,7 +5689,7 @@
         <v>90</v>
       </c>
       <c r="D42" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -5717,7 +5703,7 @@
         <v>90</v>
       </c>
       <c r="D43" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -5731,7 +5717,7 @@
         <v>110</v>
       </c>
       <c r="D44" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -5745,7 +5731,7 @@
         <v>110</v>
       </c>
       <c r="D45" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -5759,7 +5745,7 @@
         <v>110</v>
       </c>
       <c r="D46" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -5773,7 +5759,7 @@
         <v>110</v>
       </c>
       <c r="D47" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -5787,7 +5773,7 @@
         <v>110</v>
       </c>
       <c r="D48" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -5801,7 +5787,7 @@
         <v>110</v>
       </c>
       <c r="D49" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -5815,7 +5801,7 @@
         <v>110</v>
       </c>
       <c r="D50" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -5829,7 +5815,7 @@
         <v>110</v>
       </c>
       <c r="D51" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -5843,7 +5829,7 @@
         <v>125</v>
       </c>
       <c r="D52" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -5857,7 +5843,7 @@
         <v>125</v>
       </c>
       <c r="D53" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -5871,7 +5857,7 @@
         <v>125</v>
       </c>
       <c r="D54" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -5885,7 +5871,7 @@
         <v>125</v>
       </c>
       <c r="D55" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -5899,7 +5885,7 @@
         <v>125</v>
       </c>
       <c r="D56" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -5913,7 +5899,7 @@
         <v>125</v>
       </c>
       <c r="D57" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -5927,7 +5913,7 @@
         <v>125</v>
       </c>
       <c r="D58" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -5941,7 +5927,7 @@
         <v>160</v>
       </c>
       <c r="D59" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -5955,7 +5941,7 @@
         <v>160</v>
       </c>
       <c r="D60" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -5969,7 +5955,7 @@
         <v>160</v>
       </c>
       <c r="D61" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -5983,7 +5969,7 @@
         <v>160</v>
       </c>
       <c r="D62" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -5997,7 +5983,7 @@
         <v>160</v>
       </c>
       <c r="D63" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -6011,7 +5997,7 @@
         <v>160</v>
       </c>
       <c r="D64" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -6025,7 +6011,7 @@
         <v>160</v>
       </c>
       <c r="D65" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -6039,7 +6025,7 @@
         <v>160</v>
       </c>
       <c r="D66" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -6053,7 +6039,7 @@
         <v>160</v>
       </c>
       <c r="D67" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -6067,7 +6053,7 @@
         <v>160</v>
       </c>
       <c r="D68" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -6081,7 +6067,7 @@
         <v>200</v>
       </c>
       <c r="D69" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -6095,7 +6081,7 @@
         <v>200</v>
       </c>
       <c r="D70" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -6109,7 +6095,7 @@
         <v>200</v>
       </c>
       <c r="D71" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -6123,7 +6109,7 @@
         <v>200</v>
       </c>
       <c r="D72" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -6137,7 +6123,7 @@
         <v>200</v>
       </c>
       <c r="D73" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
     </row>
   </sheetData>
@@ -6161,16 +6147,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C1" t="s">
         <v>1419</v>
       </c>
-      <c r="B1" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1421</v>
-      </c>
       <c r="D1" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6184,7 +6170,7 @@
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -6198,7 +6184,7 @@
         <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -6212,7 +6198,7 @@
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -6226,7 +6212,7 @@
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -6240,7 +6226,7 @@
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -6254,7 +6240,7 @@
         <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -6268,7 +6254,7 @@
         <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -6282,7 +6268,7 @@
         <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -6296,7 +6282,7 @@
         <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -6310,7 +6296,7 @@
         <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -6324,7 +6310,7 @@
         <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -6338,7 +6324,7 @@
         <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -6352,7 +6338,7 @@
         <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -6366,7 +6352,7 @@
         <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -6380,7 +6366,7 @@
         <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -6394,7 +6380,7 @@
         <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -6408,7 +6394,7 @@
         <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -6422,7 +6408,7 @@
         <v>110</v>
       </c>
       <c r="D19" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -6436,7 +6422,7 @@
         <v>110</v>
       </c>
       <c r="D20" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
     </row>
   </sheetData>
@@ -6451,7 +6437,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74A1C685-65B4-40E2-96F9-86C8DE8EDC41}">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -6461,16 +6447,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1419</v>
       </c>
-      <c r="B1" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1421</v>
-      </c>
       <c r="D1" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6484,7 +6470,7 @@
         <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -6498,7 +6484,7 @@
         <v>125</v>
       </c>
       <c r="D3" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -6512,7 +6498,7 @@
         <v>160</v>
       </c>
       <c r="D4" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -6526,7 +6512,7 @@
         <v>160</v>
       </c>
       <c r="D5" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -6540,7 +6526,7 @@
         <v>200</v>
       </c>
       <c r="D6" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -6554,7 +6540,7 @@
         <v>200</v>
       </c>
       <c r="D7" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -6568,7 +6554,7 @@
         <v>200</v>
       </c>
       <c r="D8" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -6582,7 +6568,7 @@
         <v>200</v>
       </c>
       <c r="D9" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -6596,7 +6582,7 @@
         <v>200</v>
       </c>
       <c r="D10" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -6610,7 +6596,7 @@
         <v>250</v>
       </c>
       <c r="D11" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -6618,374 +6604,349 @@
         <v>1212</v>
       </c>
       <c r="B12" t="s">
-        <v>1422</v>
+        <v>1213</v>
       </c>
       <c r="C12">
         <v>250</v>
       </c>
       <c r="D12" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="B13" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="C13">
         <v>250</v>
       </c>
       <c r="D13" t="s">
-        <v>1466</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="B14" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="C14">
         <v>250</v>
       </c>
       <c r="D14" t="s">
-        <v>1463</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="B15" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="C15">
-        <v>250</v>
+        <v>315</v>
       </c>
       <c r="D15" t="s">
-        <v>1461</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="B16" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="C16">
         <v>315</v>
       </c>
       <c r="D16" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="B17" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="C17">
         <v>315</v>
       </c>
       <c r="D17" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="B18" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="C18">
         <v>315</v>
       </c>
       <c r="D18" t="s">
-        <v>1466</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="B19" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C19">
-        <v>315</v>
+        <v>400</v>
       </c>
       <c r="D19" t="s">
-        <v>1463</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="B20" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="C20">
         <v>400</v>
       </c>
       <c r="D20" t="s">
-        <v>1459</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="B21" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="C21">
         <v>400</v>
       </c>
       <c r="D21" t="s">
-        <v>1466</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="B22" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="C22">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D22" t="s">
-        <v>1463</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="B23" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="C23">
         <v>500</v>
       </c>
       <c r="D23" t="s">
-        <v>1459</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="B24" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="C24">
         <v>500</v>
       </c>
       <c r="D24" t="s">
-        <v>1466</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="B25" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="C25">
-        <v>500</v>
+        <v>630</v>
       </c>
       <c r="D25" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="B26" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="C26">
         <v>630</v>
       </c>
       <c r="D26" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="B27" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="C27">
         <v>630</v>
       </c>
       <c r="D27" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="B28" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="C28">
-        <v>630</v>
+        <v>800</v>
       </c>
       <c r="D28" t="s">
-        <v>1466</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="B29" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="C29">
         <v>800</v>
       </c>
       <c r="D29" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="B30" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="C30">
         <v>800</v>
       </c>
       <c r="D30" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="B31" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="C31">
-        <v>800</v>
+        <v>930</v>
       </c>
       <c r="D31" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1250</v>
+        <v>1182</v>
       </c>
       <c r="B32" t="s">
-        <v>1251</v>
+        <v>1183</v>
       </c>
       <c r="C32">
-        <v>930</v>
+        <v>1000</v>
       </c>
       <c r="D32" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1252</v>
+        <v>1184</v>
       </c>
       <c r="B33" t="s">
-        <v>1253</v>
+        <v>1185</v>
       </c>
       <c r="C33">
-        <v>930</v>
+        <v>1000</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1462</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="B34" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="C34">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="D34" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="B35" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="C35">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="D35" t="s">
-        <v>1466</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="B36" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="C36">
         <v>1200</v>
       </c>
       <c r="D36" t="s">
-        <v>1467</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>1188</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1189</v>
-      </c>
-      <c r="C37">
-        <v>1200</v>
-      </c>
-      <c r="D37" t="s">
-        <v>1464</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B38" t="s">
-        <v>1191</v>
-      </c>
-      <c r="C38">
-        <v>1200</v>
-      </c>
-      <c r="D38" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
     </row>
   </sheetData>
@@ -7011,16 +6972,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1419</v>
       </c>
-      <c r="B1" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1421</v>
-      </c>
       <c r="D1" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -7034,7 +6995,7 @@
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -7048,7 +7009,7 @@
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -7062,7 +7023,7 @@
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -7076,7 +7037,7 @@
         <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -7090,7 +7051,7 @@
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -7104,7 +7065,7 @@
         <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -7118,7 +7079,7 @@
         <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -7132,7 +7093,7 @@
         <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -7146,7 +7107,7 @@
         <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -7160,7 +7121,7 @@
         <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -7174,7 +7135,7 @@
         <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -7188,7 +7149,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -7202,7 +7163,7 @@
         <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -7216,7 +7177,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -7230,7 +7191,7 @@
         <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -7244,7 +7205,7 @@
         <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -7258,7 +7219,7 @@
         <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -7272,7 +7233,7 @@
         <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -7286,7 +7247,7 @@
         <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -7300,7 +7261,7 @@
         <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -7314,7 +7275,7 @@
         <v>63</v>
       </c>
       <c r="D22" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -7328,7 +7289,7 @@
         <v>63</v>
       </c>
       <c r="D23" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -7342,7 +7303,7 @@
         <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -7356,7 +7317,7 @@
         <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -7370,7 +7331,7 @@
         <v>63</v>
       </c>
       <c r="D26" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -7384,7 +7345,7 @@
         <v>75</v>
       </c>
       <c r="D27" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -7398,7 +7359,7 @@
         <v>75</v>
       </c>
       <c r="D28" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -7412,7 +7373,7 @@
         <v>75</v>
       </c>
       <c r="D29" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -7426,7 +7387,7 @@
         <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -7440,7 +7401,7 @@
         <v>75</v>
       </c>
       <c r="D31" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -7454,7 +7415,7 @@
         <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -7468,7 +7429,7 @@
         <v>75</v>
       </c>
       <c r="D33" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -7482,7 +7443,7 @@
         <v>75</v>
       </c>
       <c r="D34" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -7496,7 +7457,7 @@
         <v>90</v>
       </c>
       <c r="D35" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -7510,7 +7471,7 @@
         <v>90</v>
       </c>
       <c r="D36" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -7524,7 +7485,7 @@
         <v>90</v>
       </c>
       <c r="D37" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -7538,7 +7499,7 @@
         <v>90</v>
       </c>
       <c r="D38" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -7552,7 +7513,7 @@
         <v>90</v>
       </c>
       <c r="D39" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -7566,7 +7527,7 @@
         <v>90</v>
       </c>
       <c r="D40" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -7580,7 +7541,7 @@
         <v>90</v>
       </c>
       <c r="D41" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -7594,7 +7555,7 @@
         <v>90</v>
       </c>
       <c r="D42" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -7608,7 +7569,7 @@
         <v>110</v>
       </c>
       <c r="D43" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -7622,7 +7583,7 @@
         <v>110</v>
       </c>
       <c r="D44" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -7636,7 +7597,7 @@
         <v>110</v>
       </c>
       <c r="D45" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -7650,7 +7611,7 @@
         <v>110</v>
       </c>
       <c r="D46" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -7664,7 +7625,7 @@
         <v>110</v>
       </c>
       <c r="D47" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -7678,7 +7639,7 @@
         <v>110</v>
       </c>
       <c r="D48" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -7692,7 +7653,7 @@
         <v>110</v>
       </c>
       <c r="D49" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -7706,7 +7667,7 @@
         <v>110</v>
       </c>
       <c r="D50" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -7720,7 +7681,7 @@
         <v>125</v>
       </c>
       <c r="D51" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -7734,7 +7695,7 @@
         <v>125</v>
       </c>
       <c r="D52" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -7748,7 +7709,7 @@
         <v>125</v>
       </c>
       <c r="D53" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -7762,7 +7723,7 @@
         <v>125</v>
       </c>
       <c r="D54" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -7776,7 +7737,7 @@
         <v>125</v>
       </c>
       <c r="D55" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -7790,7 +7751,7 @@
         <v>125</v>
       </c>
       <c r="D56" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -7804,7 +7765,7 @@
         <v>140</v>
       </c>
       <c r="D57" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -7818,7 +7779,7 @@
         <v>140</v>
       </c>
       <c r="D58" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -7832,7 +7793,7 @@
         <v>140</v>
       </c>
       <c r="D59" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -7846,7 +7807,7 @@
         <v>140</v>
       </c>
       <c r="D60" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -7860,7 +7821,7 @@
         <v>140</v>
       </c>
       <c r="D61" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -7874,7 +7835,7 @@
         <v>140</v>
       </c>
       <c r="D62" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -7888,7 +7849,7 @@
         <v>160</v>
       </c>
       <c r="D63" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -7902,7 +7863,7 @@
         <v>160</v>
       </c>
       <c r="D64" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -7916,7 +7877,7 @@
         <v>160</v>
       </c>
       <c r="D65" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -7930,7 +7891,7 @@
         <v>160</v>
       </c>
       <c r="D66" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -7944,7 +7905,7 @@
         <v>160</v>
       </c>
       <c r="D67" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -7958,7 +7919,7 @@
         <v>160</v>
       </c>
       <c r="D68" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -7972,7 +7933,7 @@
         <v>180</v>
       </c>
       <c r="D69" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -7986,7 +7947,7 @@
         <v>180</v>
       </c>
       <c r="D70" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -8000,7 +7961,7 @@
         <v>180</v>
       </c>
       <c r="D71" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -8014,7 +7975,7 @@
         <v>180</v>
       </c>
       <c r="D72" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -8028,7 +7989,7 @@
         <v>180</v>
       </c>
       <c r="D73" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -8042,7 +8003,7 @@
         <v>180</v>
       </c>
       <c r="D74" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -8056,7 +8017,7 @@
         <v>200</v>
       </c>
       <c r="D75" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -8070,7 +8031,7 @@
         <v>200</v>
       </c>
       <c r="D76" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -8084,7 +8045,7 @@
         <v>200</v>
       </c>
       <c r="D77" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -8098,7 +8059,7 @@
         <v>200</v>
       </c>
       <c r="D78" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -8112,7 +8073,7 @@
         <v>200</v>
       </c>
       <c r="D79" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -8126,7 +8087,7 @@
         <v>200</v>
       </c>
       <c r="D80" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -8140,7 +8101,7 @@
         <v>200</v>
       </c>
       <c r="D81" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -8154,7 +8115,7 @@
         <v>200</v>
       </c>
       <c r="D82" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -8168,7 +8129,7 @@
         <v>225</v>
       </c>
       <c r="D83" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -8182,7 +8143,7 @@
         <v>225</v>
       </c>
       <c r="D84" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -8196,7 +8157,7 @@
         <v>225</v>
       </c>
       <c r="D85" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -8210,7 +8171,7 @@
         <v>225</v>
       </c>
       <c r="D86" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -8224,7 +8185,7 @@
         <v>225</v>
       </c>
       <c r="D87" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -8238,7 +8199,7 @@
         <v>225</v>
       </c>
       <c r="D88" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -8252,7 +8213,7 @@
         <v>250</v>
       </c>
       <c r="D89" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -8266,7 +8227,7 @@
         <v>250</v>
       </c>
       <c r="D90" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -8280,7 +8241,7 @@
         <v>250</v>
       </c>
       <c r="D91" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -8294,7 +8255,7 @@
         <v>250</v>
       </c>
       <c r="D92" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -8308,7 +8269,7 @@
         <v>250</v>
       </c>
       <c r="D93" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -8322,7 +8283,7 @@
         <v>250</v>
       </c>
       <c r="D94" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -8336,7 +8297,7 @@
         <v>250</v>
       </c>
       <c r="D95" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -8350,7 +8311,7 @@
         <v>280</v>
       </c>
       <c r="D96" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -8364,7 +8325,7 @@
         <v>280</v>
       </c>
       <c r="D97" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -8378,7 +8339,7 @@
         <v>280</v>
       </c>
       <c r="D98" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -8392,7 +8353,7 @@
         <v>280</v>
       </c>
       <c r="D99" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -8406,7 +8367,7 @@
         <v>280</v>
       </c>
       <c r="D100" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -8420,7 +8381,7 @@
         <v>280</v>
       </c>
       <c r="D101" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -8434,7 +8395,7 @@
         <v>315</v>
       </c>
       <c r="D102" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -8448,7 +8409,7 @@
         <v>315</v>
       </c>
       <c r="D103" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -8462,7 +8423,7 @@
         <v>315</v>
       </c>
       <c r="D104" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -8476,7 +8437,7 @@
         <v>315</v>
       </c>
       <c r="D105" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -8490,7 +8451,7 @@
         <v>315</v>
       </c>
       <c r="D106" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -8504,7 +8465,7 @@
         <v>315</v>
       </c>
       <c r="D107" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -8518,7 +8479,7 @@
         <v>355</v>
       </c>
       <c r="D108" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -8532,7 +8493,7 @@
         <v>355</v>
       </c>
       <c r="D109" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -8546,7 +8507,7 @@
         <v>355</v>
       </c>
       <c r="D110" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -8560,7 +8521,7 @@
         <v>355</v>
       </c>
       <c r="D111" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -8574,7 +8535,7 @@
         <v>355</v>
       </c>
       <c r="D112" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
@@ -8588,7 +8549,7 @@
         <v>400</v>
       </c>
       <c r="D113" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
@@ -8602,7 +8563,7 @@
         <v>400</v>
       </c>
       <c r="D114" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
@@ -8616,7 +8577,7 @@
         <v>400</v>
       </c>
       <c r="D115" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
@@ -8630,7 +8591,7 @@
         <v>400</v>
       </c>
       <c r="D116" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
@@ -8644,7 +8605,7 @@
         <v>400</v>
       </c>
       <c r="D117" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
@@ -8658,7 +8619,7 @@
         <v>400</v>
       </c>
       <c r="D118" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
@@ -8672,7 +8633,7 @@
         <v>450</v>
       </c>
       <c r="D119" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
@@ -8686,7 +8647,7 @@
         <v>450</v>
       </c>
       <c r="D120" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
@@ -8700,7 +8661,7 @@
         <v>500</v>
       </c>
       <c r="D121" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
@@ -8714,7 +8675,7 @@
         <v>500</v>
       </c>
       <c r="D122" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
@@ -8728,7 +8689,7 @@
         <v>500</v>
       </c>
       <c r="D123" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
@@ -8742,7 +8703,7 @@
         <v>500</v>
       </c>
       <c r="D124" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
   </sheetData>
@@ -8767,16 +8728,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C1" t="s">
         <v>1419</v>
       </c>
-      <c r="B1" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1421</v>
-      </c>
       <c r="D1" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -8790,7 +8751,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -8804,7 +8765,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1477</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -8818,7 +8779,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -8832,7 +8793,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -8846,7 +8807,7 @@
         <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -8860,7 +8821,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -8874,7 +8835,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -8888,7 +8849,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -8902,7 +8863,7 @@
         <v>25</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -8916,7 +8877,7 @@
         <v>25</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -8930,7 +8891,7 @@
         <v>25</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1477</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -8944,7 +8905,7 @@
         <v>25</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -8958,7 +8919,7 @@
         <v>25</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -8972,7 +8933,7 @@
         <v>25</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -8986,7 +8947,7 @@
         <v>25</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -9000,7 +8961,7 @@
         <v>25</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -9014,7 +8975,7 @@
         <v>25</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1484</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -9028,7 +8989,7 @@
         <v>25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -9042,7 +9003,7 @@
         <v>32</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -9056,7 +9017,7 @@
         <v>32</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -9070,7 +9031,7 @@
         <v>32</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -9084,7 +9045,7 @@
         <v>32</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -9098,7 +9059,7 @@
         <v>32</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -9112,7 +9073,7 @@
         <v>32</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -9126,7 +9087,7 @@
         <v>32</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -9140,7 +9101,7 @@
         <v>32</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1477</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -9154,7 +9115,7 @@
         <v>32</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -9168,7 +9129,7 @@
         <v>40</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -9182,7 +9143,7 @@
         <v>40</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -9196,7 +9157,7 @@
         <v>40</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -9210,7 +9171,7 @@
         <v>40</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -9224,7 +9185,7 @@
         <v>40</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -9238,7 +9199,7 @@
         <v>40</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -9252,7 +9213,7 @@
         <v>50</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -9266,7 +9227,7 @@
         <v>50</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -9280,7 +9241,7 @@
         <v>50</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -9294,7 +9255,7 @@
         <v>50</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -9308,7 +9269,7 @@
         <v>50</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -9322,7 +9283,7 @@
         <v>50</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -9336,7 +9297,7 @@
         <v>63</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -9350,7 +9311,7 @@
         <v>63</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -9364,7 +9325,7 @@
         <v>63</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -9378,7 +9339,7 @@
         <v>63</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -9392,7 +9353,7 @@
         <v>63</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -9406,7 +9367,7 @@
         <v>63</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -9420,7 +9381,7 @@
         <v>75</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -9434,7 +9395,7 @@
         <v>75</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -9448,7 +9409,7 @@
         <v>75</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -9462,7 +9423,7 @@
         <v>75</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -9476,7 +9437,7 @@
         <v>75</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -9490,7 +9451,7 @@
         <v>75</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -9504,7 +9465,7 @@
         <v>90</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -9518,7 +9479,7 @@
         <v>90</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -9532,7 +9493,7 @@
         <v>90</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -9546,7 +9507,7 @@
         <v>90</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -9560,7 +9521,7 @@
         <v>90</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -9574,7 +9535,7 @@
         <v>110</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -9588,7 +9549,7 @@
         <v>110</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -9602,7 +9563,7 @@
         <v>110</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -9616,7 +9577,7 @@
         <v>110</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
     </row>
   </sheetData>
@@ -9642,16 +9603,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1419</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1423</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1421</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -9665,7 +9626,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -9679,7 +9640,7 @@
         <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -9693,7 +9654,7 @@
         <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -9707,7 +9668,7 @@
         <v>32</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -9721,7 +9682,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -9735,7 +9696,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -9749,7 +9710,7 @@
         <v>40</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -9763,7 +9724,7 @@
         <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
@@ -9779,7 +9740,7 @@
         <v>40</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -9793,7 +9754,7 @@
         <v>50</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -9807,7 +9768,7 @@
         <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -9821,7 +9782,7 @@
         <v>63</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1488</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -9835,7 +9796,7 @@
         <v>63</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -9849,7 +9810,7 @@
         <v>63</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
@@ -9865,7 +9826,7 @@
         <v>63</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -9879,7 +9840,7 @@
         <v>63</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -9893,7 +9854,7 @@
         <v>63</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -9907,7 +9868,7 @@
         <v>63</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -9921,7 +9882,7 @@
         <v>63</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -9935,7 +9896,7 @@
         <v>63</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
@@ -9951,7 +9912,7 @@
         <v>75</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1488</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -9965,7 +9926,7 @@
         <v>75</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -9979,7 +9940,7 @@
         <v>75</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -9993,7 +9954,7 @@
         <v>75</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -10007,7 +9968,7 @@
         <v>75</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -10021,7 +9982,7 @@
         <v>90</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -10035,7 +9996,7 @@
         <v>90</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -10049,7 +10010,7 @@
         <v>110</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
@@ -10064,7 +10025,7 @@
         <v>110</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -10078,7 +10039,7 @@
         <v>110</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -10092,7 +10053,7 @@
         <v>125</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
@@ -10108,7 +10069,7 @@
         <v>125</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -10122,7 +10083,7 @@
         <v>140</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -10136,7 +10097,7 @@
         <v>140</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -10150,7 +10111,7 @@
         <v>160</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -10164,7 +10125,7 @@
         <v>160</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -10178,7 +10139,7 @@
         <v>180</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -10192,7 +10153,7 @@
         <v>180</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -10206,7 +10167,7 @@
         <v>200</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -10220,7 +10181,7 @@
         <v>200</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
@@ -10235,7 +10196,7 @@
         <v>225</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -10249,7 +10210,7 @@
         <v>225</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -10263,7 +10224,7 @@
         <v>250</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -10277,7 +10238,7 @@
         <v>250</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -10291,7 +10252,7 @@
         <v>315</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -10305,7 +10266,7 @@
         <v>400</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
@@ -10375,16 +10336,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1419</v>
       </c>
-      <c r="B1" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1421</v>
-      </c>
       <c r="D1" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -10398,7 +10359,7 @@
         <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>1521</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -10412,7 +10373,7 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>1522</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -10426,7 +10387,7 @@
         <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>1523</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -10440,7 +10401,7 @@
         <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>1524</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -10454,7 +10415,7 @@
         <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -10468,7 +10429,7 @@
         <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>1526</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -10482,7 +10443,7 @@
         <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>1529</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -10496,7 +10457,7 @@
         <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>1531</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -10510,7 +10471,7 @@
         <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>1530</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -10524,7 +10485,7 @@
         <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>1532</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -10538,10 +10499,10 @@
         <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>1534</v>
+        <v>1530</v>
       </c>
       <c r="E12" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -10555,7 +10516,7 @@
         <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>1535</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -10568,8 +10529,8 @@
       <c r="C14">
         <v>40</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>1536</v>
+      <c r="D14" t="s">
+        <v>1532</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -10583,7 +10544,7 @@
         <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>1537</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -10597,7 +10558,7 @@
         <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>1563</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -10610,8 +10571,8 @@
       <c r="C17">
         <v>50</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>1528</v>
+      <c r="D17" t="s">
+        <v>1524</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -10624,8 +10585,8 @@
       <c r="C18">
         <v>50</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>1555</v>
+      <c r="D18" t="s">
+        <v>1551</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -10638,8 +10599,8 @@
       <c r="C19">
         <v>50</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>1554</v>
+      <c r="D19" t="s">
+        <v>1550</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -10652,8 +10613,8 @@
       <c r="C20">
         <v>50</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>1556</v>
+      <c r="D20" t="s">
+        <v>1552</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -10666,8 +10627,8 @@
       <c r="C21">
         <v>50</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>1557</v>
+      <c r="D21" t="s">
+        <v>1553</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -10680,8 +10641,8 @@
       <c r="C22">
         <v>50</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>1559</v>
+      <c r="D22" t="s">
+        <v>1555</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -10694,8 +10655,8 @@
       <c r="C23">
         <v>50</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>1560</v>
+      <c r="D23" t="s">
+        <v>1556</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -10708,8 +10669,8 @@
       <c r="C24">
         <v>50</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>1558</v>
+      <c r="D24" t="s">
+        <v>1554</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -10723,7 +10684,7 @@
         <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>1536</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -10737,7 +10698,7 @@
         <v>50</v>
       </c>
       <c r="D26" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -10751,7 +10712,7 @@
         <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>1553</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -10765,7 +10726,7 @@
         <v>50</v>
       </c>
       <c r="D28" t="s">
-        <v>1552</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -10779,7 +10740,7 @@
         <v>50</v>
       </c>
       <c r="D29" t="s">
-        <v>1551</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -10793,7 +10754,7 @@
         <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>1528</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -10807,7 +10768,7 @@
         <v>50</v>
       </c>
       <c r="D31" t="s">
-        <v>1561</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -10821,7 +10782,7 @@
         <v>63</v>
       </c>
       <c r="D32" t="s">
-        <v>1538</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -10835,7 +10796,7 @@
         <v>63</v>
       </c>
       <c r="D33" t="s">
-        <v>1550</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -10849,7 +10810,7 @@
         <v>63</v>
       </c>
       <c r="D34" t="s">
-        <v>1527</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -10863,7 +10824,7 @@
         <v>63</v>
       </c>
       <c r="D35" t="s">
-        <v>1548</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -10877,7 +10838,7 @@
         <v>63</v>
       </c>
       <c r="D36" t="s">
-        <v>1549</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -10891,7 +10852,7 @@
         <v>75</v>
       </c>
       <c r="D37" t="s">
-        <v>1538</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -10905,7 +10866,7 @@
         <v>75</v>
       </c>
       <c r="D38" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -10919,7 +10880,7 @@
         <v>75</v>
       </c>
       <c r="D39" t="s">
-        <v>1527</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -10933,7 +10894,7 @@
         <v>90</v>
       </c>
       <c r="D40" t="s">
-        <v>1539</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -10947,7 +10908,7 @@
         <v>90</v>
       </c>
       <c r="D41" t="s">
-        <v>1540</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -10961,7 +10922,7 @@
         <v>110</v>
       </c>
       <c r="D42" t="s">
-        <v>1542</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -10975,7 +10936,7 @@
         <v>110</v>
       </c>
       <c r="D43" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -10989,7 +10950,7 @@
         <v>125</v>
       </c>
       <c r="D44" t="s">
-        <v>1541</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -11003,7 +10964,7 @@
         <v>125</v>
       </c>
       <c r="D45" t="s">
-        <v>1542</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -11017,7 +10978,7 @@
         <v>125</v>
       </c>
       <c r="D46" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -11031,7 +10992,7 @@
         <v>125</v>
       </c>
       <c r="D47" t="s">
-        <v>1547</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -11045,7 +11006,7 @@
         <v>125</v>
       </c>
       <c r="D48" t="s">
-        <v>1539</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -11059,7 +11020,7 @@
         <v>140</v>
       </c>
       <c r="D49" t="s">
-        <v>1541</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -11073,7 +11034,7 @@
         <v>140</v>
       </c>
       <c r="D50" t="s">
-        <v>1542</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -11087,7 +11048,7 @@
         <v>140</v>
       </c>
       <c r="D51" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -11101,7 +11062,7 @@
         <v>140</v>
       </c>
       <c r="D52" t="s">
-        <v>1547</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -11115,7 +11076,7 @@
         <v>140</v>
       </c>
       <c r="D53" t="s">
-        <v>1543</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -11129,7 +11090,7 @@
         <v>140</v>
       </c>
       <c r="D54" t="s">
-        <v>1539</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -11143,7 +11104,7 @@
         <v>160</v>
       </c>
       <c r="D55" t="s">
-        <v>1541</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -11157,7 +11118,7 @@
         <v>160</v>
       </c>
       <c r="D56" t="s">
-        <v>1542</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -11171,7 +11132,7 @@
         <v>160</v>
       </c>
       <c r="D57" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -11185,7 +11146,7 @@
         <v>160</v>
       </c>
       <c r="D58" t="s">
-        <v>1547</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -11199,7 +11160,7 @@
         <v>160</v>
       </c>
       <c r="D59" t="s">
-        <v>1543</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -11213,7 +11174,7 @@
         <v>160</v>
       </c>
       <c r="D60" t="s">
-        <v>1539</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -11227,7 +11188,7 @@
         <v>180</v>
       </c>
       <c r="D61" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -11241,7 +11202,7 @@
         <v>180</v>
       </c>
       <c r="D62" t="s">
-        <v>1547</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -11255,7 +11216,7 @@
         <v>180</v>
       </c>
       <c r="D63" t="s">
-        <v>1539</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -11269,7 +11230,7 @@
         <v>200</v>
       </c>
       <c r="D64" t="s">
-        <v>1541</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -11283,7 +11244,7 @@
         <v>200</v>
       </c>
       <c r="D65" t="s">
-        <v>1542</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -11297,7 +11258,7 @@
         <v>200</v>
       </c>
       <c r="D66" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -11311,7 +11272,7 @@
         <v>200</v>
       </c>
       <c r="D67" t="s">
-        <v>1547</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -11325,7 +11286,7 @@
         <v>200</v>
       </c>
       <c r="D68" t="s">
-        <v>1543</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -11339,7 +11300,7 @@
         <v>200</v>
       </c>
       <c r="D69" t="s">
-        <v>1539</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -11353,7 +11314,7 @@
         <v>225</v>
       </c>
       <c r="D70" t="s">
-        <v>1542</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -11367,7 +11328,7 @@
         <v>225</v>
       </c>
       <c r="D71" t="s">
-        <v>1547</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -11381,7 +11342,7 @@
         <v>250</v>
       </c>
       <c r="D72" t="s">
-        <v>1542</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -11395,7 +11356,7 @@
         <v>250</v>
       </c>
       <c r="D73" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -11409,7 +11370,7 @@
         <v>250</v>
       </c>
       <c r="D74" t="s">
-        <v>1547</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -11423,7 +11384,7 @@
         <v>250</v>
       </c>
       <c r="D75" t="s">
-        <v>1539</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -11437,7 +11398,7 @@
         <v>280</v>
       </c>
       <c r="D76" t="s">
-        <v>1541</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -11451,7 +11412,7 @@
         <v>280</v>
       </c>
       <c r="D77" t="s">
-        <v>1547</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -11465,7 +11426,7 @@
         <v>315</v>
       </c>
       <c r="D78" t="s">
-        <v>1542</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -11479,7 +11440,7 @@
         <v>315</v>
       </c>
       <c r="D79" t="s">
-        <v>1543</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -11493,7 +11454,7 @@
         <v>315</v>
       </c>
       <c r="D80" t="s">
-        <v>1539</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -11507,7 +11468,7 @@
         <v>500</v>
       </c>
       <c r="D81" t="s">
-        <v>1539</v>
+        <v>1535</v>
       </c>
     </row>
   </sheetData>
@@ -11532,16 +11493,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="B1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="D1" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -11555,7 +11516,7 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -11569,7 +11530,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -11583,7 +11544,7 @@
         <v>16</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -11597,7 +11558,7 @@
         <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -11611,7 +11572,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1503</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -11625,7 +11586,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -11639,7 +11600,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -11653,7 +11614,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -11667,7 +11628,7 @@
         <v>20</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -11681,7 +11642,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1509</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -11695,7 +11656,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -11709,7 +11670,7 @@
         <v>20</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -11723,7 +11684,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -11737,7 +11698,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -11751,7 +11712,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -11765,7 +11726,7 @@
         <v>20</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -11779,7 +11740,7 @@
         <v>20</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1495</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -11793,7 +11754,7 @@
         <v>20</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1513</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -11807,7 +11768,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1511</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -11821,7 +11782,7 @@
         <v>25</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1504</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -11835,7 +11796,7 @@
         <v>25</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -11849,7 +11810,7 @@
         <v>25</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -11863,7 +11824,7 @@
         <v>25</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1514</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -11877,7 +11838,7 @@
         <v>25</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -11891,7 +11852,7 @@
         <v>25</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -11905,7 +11866,7 @@
         <v>25</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -11919,7 +11880,7 @@
         <v>25</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1506</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -11933,7 +11894,7 @@
         <v>25</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1510</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -11947,7 +11908,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1511</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -11961,7 +11922,7 @@
         <v>32</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1504</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -11975,7 +11936,7 @@
         <v>32</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -11989,7 +11950,7 @@
         <v>32</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1505</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -12002,8 +11963,8 @@
       <c r="C34">
         <v>32</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>1502</v>
+      <c r="D34" s="1" t="s">
+        <v>1498</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -12017,7 +11978,7 @@
         <v>32</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -12031,7 +11992,7 @@
         <v>32</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -12045,7 +12006,7 @@
         <v>32</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1510</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -12059,7 +12020,7 @@
         <v>32</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>1511</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -12073,7 +12034,7 @@
         <v>40</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1510</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -12087,7 +12048,7 @@
         <v>40</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1515</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -12101,7 +12062,7 @@
         <v>40</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1505</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -12115,7 +12076,7 @@
         <v>40</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -12129,7 +12090,7 @@
         <v>40</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>1506</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -12143,7 +12104,7 @@
         <v>40</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1510</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -12157,7 +12118,7 @@
         <v>50</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1504</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -12171,7 +12132,7 @@
         <v>50</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1515</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -12185,7 +12146,7 @@
         <v>50</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1505</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -12199,7 +12160,7 @@
         <v>50</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1516</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -12213,7 +12174,7 @@
         <v>50</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -12227,7 +12188,7 @@
         <v>50</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1510</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -12241,7 +12202,7 @@
         <v>63</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -12255,7 +12216,7 @@
         <v>63</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -12269,7 +12230,7 @@
         <v>63</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -12283,7 +12244,7 @@
         <v>63</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -12297,7 +12258,7 @@
         <v>75</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1504</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -12311,7 +12272,7 @@
         <v>75</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1515</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -12325,7 +12286,7 @@
         <v>75</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -12339,7 +12300,7 @@
         <v>75</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -12353,7 +12314,7 @@
         <v>90</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1515</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -12367,7 +12328,7 @@
         <v>90</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1517</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -12381,7 +12342,7 @@
         <v>110</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -12395,7 +12356,7 @@
         <v>110</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -12409,7 +12370,7 @@
         <v>161</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -12423,7 +12384,7 @@
         <v>161</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -12437,7 +12398,7 @@
         <v>162</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>1505</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -12451,7 +12412,7 @@
         <v>162</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>1506</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -12465,7 +12426,7 @@
         <v>162</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>1508</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -12479,7 +12440,7 @@
         <v>165</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>1518</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -12493,7 +12454,7 @@
         <v>165</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>1507</v>
+        <v>1503</v>
       </c>
     </row>
   </sheetData>
@@ -12517,16 +12478,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1419</v>
       </c>
-      <c r="B1" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1421</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -12540,7 +12501,7 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -12554,7 +12515,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1509</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -12568,7 +12529,7 @@
         <v>16</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -12582,7 +12543,7 @@
         <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -12596,7 +12557,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -12610,7 +12571,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -12624,7 +12585,7 @@
         <v>16</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -12638,7 +12599,7 @@
         <v>16</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1520</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -12652,7 +12613,7 @@
         <v>20</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -12666,7 +12627,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1509</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -12680,7 +12641,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -12694,7 +12655,7 @@
         <v>20</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -12708,7 +12669,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -12722,7 +12683,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -12736,7 +12697,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1495</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -12750,7 +12711,7 @@
         <v>25</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -12764,7 +12725,7 @@
         <v>25</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1509</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -12778,7 +12739,7 @@
         <v>25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -12792,7 +12753,7 @@
         <v>25</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -12806,7 +12767,7 @@
         <v>25</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -12820,7 +12781,7 @@
         <v>32</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -12834,7 +12795,7 @@
         <v>32</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -12848,7 +12809,7 @@
         <v>32</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1509</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -12862,7 +12823,7 @@
         <v>32</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -12876,7 +12837,7 @@
         <v>32</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -12890,7 +12851,7 @@
         <v>32</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -12904,7 +12865,7 @@
         <v>40</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -12918,7 +12879,7 @@
         <v>40</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -12932,7 +12893,7 @@
         <v>40</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1509</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -12946,7 +12907,7 @@
         <v>40</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -12960,7 +12921,7 @@
         <v>40</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -12974,7 +12935,7 @@
         <v>40</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -12988,7 +12949,7 @@
         <v>50</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -13002,7 +12963,7 @@
         <v>50</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -13016,7 +12977,7 @@
         <v>50</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -13030,7 +12991,7 @@
         <v>63</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -13044,7 +13005,7 @@
         <v>63</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -13058,7 +13019,7 @@
         <v>75</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -13072,7 +13033,7 @@
         <v>75</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -13086,7 +13047,7 @@
         <v>90</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -13100,7 +13061,7 @@
         <v>90</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -13114,7 +13075,7 @@
         <v>110</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -13128,7 +13089,7 @@
         <v>110</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
     </row>
   </sheetData>
@@ -13143,7 +13104,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AB8D2EC-9DC4-4A0E-9967-CD460803E46D}">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -13154,16 +13115,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C1" t="s">
         <v>1419</v>
       </c>
-      <c r="B1" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1421</v>
-      </c>
       <c r="D1" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -13177,7 +13138,7 @@
         <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -13191,7 +13152,7 @@
         <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -13205,7 +13166,7 @@
         <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -13219,7 +13180,7 @@
         <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -13233,7 +13194,7 @@
         <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -13247,7 +13208,7 @@
         <v>125</v>
       </c>
       <c r="D7" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -13261,7 +13222,7 @@
         <v>125</v>
       </c>
       <c r="D8" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -13275,7 +13236,7 @@
         <v>125</v>
       </c>
       <c r="D9" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -13289,7 +13250,7 @@
         <v>125</v>
       </c>
       <c r="D10" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -13303,7 +13264,7 @@
         <v>160</v>
       </c>
       <c r="D11" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -13317,7 +13278,7 @@
         <v>160</v>
       </c>
       <c r="D12" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -13331,181 +13292,49 @@
         <v>160</v>
       </c>
       <c r="D13" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C14">
+        <v>160</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>968</v>
+      </c>
+      <c r="B15" t="s">
+        <v>969</v>
+      </c>
+      <c r="C15">
+        <v>200</v>
+      </c>
+      <c r="D15" t="s">
         <v>1439</v>
       </c>
     </row>
-    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>1118</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C14">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>1120</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1121</v>
-      </c>
-      <c r="C15">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1122</v>
+        <v>1146</v>
       </c>
       <c r="B16" t="s">
-        <v>1123</v>
+        <v>1147</v>
       </c>
       <c r="C16">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>1124</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1125</v>
-      </c>
-      <c r="C17">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>1126</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1127</v>
-      </c>
-      <c r="C18">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C19">
-        <v>160</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1440</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>968</v>
-      </c>
-      <c r="B20" t="s">
-        <v>969</v>
-      </c>
-      <c r="C20">
         <v>200</v>
       </c>
-      <c r="D20" t="s">
-        <v>1442</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>1132</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C21">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>1134</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1135</v>
-      </c>
-      <c r="C22">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>1136</v>
-      </c>
-      <c r="B23" t="s">
-        <v>1137</v>
-      </c>
-      <c r="C23">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>1138</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C24">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1141</v>
-      </c>
-      <c r="C25">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>1142</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C26">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>1144</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1145</v>
-      </c>
-      <c r="C27">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>1146</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1147</v>
-      </c>
-      <c r="C28">
-        <v>200</v>
-      </c>
-      <c r="D28" t="s">
-        <v>1439</v>
+      <c r="D16" t="s">
+        <v>1436</v>
       </c>
     </row>
   </sheetData>
@@ -13531,16 +13360,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C1" t="s">
         <v>1419</v>
       </c>
-      <c r="B1" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1421</v>
-      </c>
       <c r="D1" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -13554,7 +13383,7 @@
         <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -13568,7 +13397,7 @@
         <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -13582,7 +13411,7 @@
         <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -13596,7 +13425,7 @@
         <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -13610,7 +13439,7 @@
         <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -13624,7 +13453,7 @@
         <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -13638,7 +13467,7 @@
         <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -13652,7 +13481,7 @@
         <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -13666,7 +13495,7 @@
         <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -13680,7 +13509,7 @@
         <v>110</v>
       </c>
       <c r="D11" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -13694,7 +13523,7 @@
         <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -13708,7 +13537,7 @@
         <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -13722,7 +13551,7 @@
         <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -13736,7 +13565,7 @@
         <v>125</v>
       </c>
       <c r="D15" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -13750,7 +13579,7 @@
         <v>125</v>
       </c>
       <c r="D16" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -13764,7 +13593,7 @@
         <v>125</v>
       </c>
       <c r="D17" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -13778,7 +13607,7 @@
         <v>160</v>
       </c>
       <c r="D18" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -13792,7 +13621,7 @@
         <v>160</v>
       </c>
       <c r="D19" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -13806,7 +13635,7 @@
         <v>160</v>
       </c>
       <c r="D20" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -13820,7 +13649,7 @@
         <v>200</v>
       </c>
       <c r="D21" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -13834,7 +13663,7 @@
         <v>200</v>
       </c>
       <c r="D22" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
     </row>
   </sheetData>
@@ -13859,16 +13688,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C1" t="s">
         <v>1419</v>
       </c>
-      <c r="B1" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1421</v>
-      </c>
       <c r="D1" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -13882,7 +13711,7 @@
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -13896,7 +13725,7 @@
         <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -13910,7 +13739,7 @@
         <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -13924,7 +13753,7 @@
         <v>125</v>
       </c>
       <c r="D5" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -13938,7 +13767,7 @@
         <v>160</v>
       </c>
       <c r="D6" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -13952,7 +13781,7 @@
         <v>200</v>
       </c>
       <c r="D7" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
     </row>
   </sheetData>
@@ -13978,100 +13807,100 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C1" t="s">
         <v>1419</v>
       </c>
-      <c r="B1" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1421</v>
-      </c>
       <c r="D1" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="B2" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="C2">
         <v>200</v>
       </c>
       <c r="D2" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="B3" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="C3">
         <v>250</v>
       </c>
       <c r="D3" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="B4" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="C4">
         <v>315</v>
       </c>
       <c r="D4" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="B5" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="C5">
         <v>400</v>
       </c>
       <c r="D5" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="B6" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="C6">
         <v>500</v>
       </c>
       <c r="D6" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="B7" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="C7">
         <v>630</v>
       </c>
       <c r="D7" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
   </sheetData>
@@ -14092,114 +13921,114 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C1" t="s">
         <v>1419</v>
       </c>
-      <c r="B1" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1421</v>
-      </c>
       <c r="D1" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="B2" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="C2">
         <v>160</v>
       </c>
       <c r="D2" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="B3" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="C3">
         <v>200</v>
       </c>
       <c r="D3" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="B4" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="C4">
         <v>250</v>
       </c>
       <c r="D4" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="B5" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="C5">
         <v>300</v>
       </c>
       <c r="D5" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="B6" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="C6">
         <v>400</v>
       </c>
       <c r="D6" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="B7" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="C7">
         <v>500</v>
       </c>
       <c r="D7" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="B8" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="C8">
         <v>600</v>
       </c>
       <c r="D8" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
   </sheetData>
@@ -14221,590 +14050,590 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C1" t="s">
         <v>1419</v>
       </c>
-      <c r="B1" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1421</v>
-      </c>
       <c r="D1" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="B2" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="C2">
         <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="B3" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C3">
         <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B4" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="C4">
         <v>125</v>
       </c>
       <c r="D4" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B5" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="C5">
         <v>125</v>
       </c>
       <c r="D5" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="B6" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="C6">
         <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="B7" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="C7">
         <v>160</v>
       </c>
       <c r="D7" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B8" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="C8">
         <v>160</v>
       </c>
       <c r="D8" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="B9" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="C9">
         <v>160</v>
       </c>
       <c r="D9" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="B10" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="C10">
         <v>160</v>
       </c>
       <c r="D10" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="B11" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="C11">
         <v>160</v>
       </c>
       <c r="D11" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="B12" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="C12">
         <v>160</v>
       </c>
       <c r="D12" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="B13" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="C13">
         <v>200</v>
       </c>
       <c r="D13" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="B14" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="C14">
         <v>200</v>
       </c>
       <c r="D14" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="B15" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="C15">
         <v>200</v>
       </c>
       <c r="D15" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B16" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="C16">
         <v>200</v>
       </c>
       <c r="D16" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B17" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="C17">
         <v>200</v>
       </c>
       <c r="D17" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="B18" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="C18">
         <v>200</v>
       </c>
       <c r="D18" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="B19" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="C19">
         <v>250</v>
       </c>
       <c r="D19" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="B20" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="C20">
         <v>250</v>
       </c>
       <c r="D20" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="B21" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="C21">
         <v>250</v>
       </c>
       <c r="D21" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B22" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="C22">
         <v>250</v>
       </c>
       <c r="D22" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="B23" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="C23">
         <v>250</v>
       </c>
       <c r="D23" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="B24" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="C24">
         <v>250</v>
       </c>
       <c r="D24" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="B25" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="C25">
         <v>315</v>
       </c>
       <c r="D25" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="B26" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="C26">
         <v>315</v>
       </c>
       <c r="D26" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="B27" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="C27">
         <v>315</v>
       </c>
       <c r="D27" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="B28" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="C28">
         <v>315</v>
       </c>
       <c r="D28" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="B29" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="C29">
         <v>315</v>
       </c>
       <c r="D29" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="B30" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="C30">
         <v>315</v>
       </c>
       <c r="D30" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B31" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="C31">
         <v>400</v>
       </c>
       <c r="D31" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="B32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="C32">
         <v>400</v>
       </c>
       <c r="D32" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="B33" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="C33">
         <v>400</v>
       </c>
       <c r="D33" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="B34" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="C34">
         <v>400</v>
       </c>
       <c r="D34" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="B35" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C35">
         <v>400</v>
       </c>
       <c r="D35" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="B36" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="C36">
         <v>400</v>
       </c>
       <c r="D36" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="B37" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="C37">
         <v>500</v>
       </c>
       <c r="D37" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="B38" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="C38">
         <v>500</v>
       </c>
       <c r="D38" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="B39" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="C39">
         <v>500</v>
       </c>
       <c r="D39" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="B40" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="C40">
         <v>500</v>
       </c>
       <c r="D40" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="B41" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="C41">
         <v>500</v>
       </c>
       <c r="D41" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="B42" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="C42">
         <v>500</v>
       </c>
       <c r="D42" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
   </sheetData>
@@ -14824,422 +14653,422 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C1" t="s">
         <v>1419</v>
       </c>
-      <c r="B1" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1421</v>
-      </c>
       <c r="D1" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B2" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="C2">
         <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="B3" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="C3">
         <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B4" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C4">
         <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="B5" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C5">
         <v>125</v>
       </c>
       <c r="D5" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B6" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="C6">
         <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="B7" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="C7">
         <v>160</v>
       </c>
       <c r="D7" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="B8" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="C8">
         <v>160</v>
       </c>
       <c r="D8" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="B9" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="C9">
         <v>160</v>
       </c>
       <c r="D9" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B10" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="C10">
         <v>160</v>
       </c>
       <c r="D10" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="B11" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="C11">
         <v>160</v>
       </c>
       <c r="D11" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="B12" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="C12">
         <v>200</v>
       </c>
       <c r="D12" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="B13" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="C13">
         <v>200</v>
       </c>
       <c r="D13" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="B14" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="C14">
         <v>200</v>
       </c>
       <c r="D14" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B15" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="C15">
         <v>200</v>
       </c>
       <c r="D15" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B16" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="C16">
         <v>250</v>
       </c>
       <c r="D16" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B17" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="C17">
         <v>250</v>
       </c>
       <c r="D17" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="B18" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="C18">
         <v>250</v>
       </c>
       <c r="D18" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="B19" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="C19">
         <v>250</v>
       </c>
       <c r="D19" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="B20" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="C20">
         <v>315</v>
       </c>
       <c r="D20" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="B21" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="C21">
         <v>315</v>
       </c>
       <c r="D21" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="B22" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="C22">
         <v>315</v>
       </c>
       <c r="D22" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="B23" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="C23">
         <v>315</v>
       </c>
       <c r="D23" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="B24" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C24">
         <v>400</v>
       </c>
       <c r="D24" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="B25" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="C25">
         <v>400</v>
       </c>
       <c r="D25" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B26" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="C26">
         <v>400</v>
       </c>
       <c r="D26" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="B27" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="C27">
         <v>400</v>
       </c>
       <c r="D27" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B28" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="C28">
         <v>500</v>
       </c>
       <c r="D28" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="B29" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="C29">
         <v>500</v>
       </c>
       <c r="D29" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="B30" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="C30">
         <v>500</v>
       </c>
       <c r="D30" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
   </sheetData>
@@ -15259,16 +15088,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C1" t="s">
         <v>1419</v>
       </c>
-      <c r="B1" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1421</v>
-      </c>
       <c r="D1" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -15282,7 +15111,7 @@
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -15296,7 +15125,7 @@
         <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -15310,7 +15139,7 @@
         <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -15324,7 +15153,7 @@
         <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -15338,7 +15167,7 @@
         <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -15352,7 +15181,7 @@
         <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -15366,7 +15195,7 @@
         <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -15380,7 +15209,7 @@
         <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -15394,7 +15223,7 @@
         <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -15408,7 +15237,7 @@
         <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -15422,7 +15251,7 @@
         <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -15436,7 +15265,7 @@
         <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -15450,7 +15279,7 @@
         <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -15464,7 +15293,7 @@
         <v>110</v>
       </c>
       <c r="D15" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -15478,7 +15307,7 @@
         <v>125</v>
       </c>
       <c r="D16" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -15492,7 +15321,7 @@
         <v>125</v>
       </c>
       <c r="D17" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -15506,7 +15335,7 @@
         <v>140</v>
       </c>
       <c r="D18" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -15520,7 +15349,7 @@
         <v>140</v>
       </c>
       <c r="D19" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -15534,7 +15363,7 @@
         <v>160</v>
       </c>
       <c r="D20" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -15548,7 +15377,7 @@
         <v>160</v>
       </c>
       <c r="D21" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -15562,7 +15391,7 @@
         <v>180</v>
       </c>
       <c r="D22" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -15576,7 +15405,7 @@
         <v>180</v>
       </c>
       <c r="D23" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -15590,7 +15419,7 @@
         <v>200</v>
       </c>
       <c r="D24" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -15604,7 +15433,7 @@
         <v>200</v>
       </c>
       <c r="D25" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -15618,7 +15447,7 @@
         <v>225</v>
       </c>
       <c r="D26" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -15632,7 +15461,7 @@
         <v>225</v>
       </c>
       <c r="D27" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -15646,7 +15475,7 @@
         <v>250</v>
       </c>
       <c r="D28" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -15660,7 +15489,7 @@
         <v>250</v>
       </c>
       <c r="D29" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -15674,7 +15503,7 @@
         <v>280</v>
       </c>
       <c r="D30" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -15688,7 +15517,7 @@
         <v>280</v>
       </c>
       <c r="D31" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -15702,7 +15531,7 @@
         <v>315</v>
       </c>
       <c r="D32" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -15716,7 +15545,7 @@
         <v>315</v>
       </c>
       <c r="D33" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -15730,7 +15559,7 @@
         <v>355</v>
       </c>
       <c r="D34" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -15744,7 +15573,7 @@
         <v>355</v>
       </c>
       <c r="D35" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -15758,7 +15587,7 @@
         <v>400</v>
       </c>
       <c r="D36" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -15772,7 +15601,7 @@
         <v>400</v>
       </c>
       <c r="D37" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
   </sheetData>

--- a/Lista Articoli per consultazione.xlsx
+++ b/Lista Articoli per consultazione.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicola.Minguzzi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89348253-FD41-47B4-BF55-59F4F9EA61AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9EB6E35-9FDD-42F8-8D5C-05646BBE982B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Corrugar Rotoli" sheetId="6" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2194" uniqueCount="1560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="1556">
   <si>
     <t>06110P10</t>
   </si>
@@ -3820,12 +3820,6 @@
     <t>TUBO PE FGN CORRUG. SN4 800 6m</t>
   </si>
   <si>
-    <t>439308</t>
-  </si>
-  <si>
-    <t>TUBO PE FGN CORR. SN8 930 M6</t>
-  </si>
-  <si>
     <t>5311016M3</t>
   </si>
   <si>
@@ -4438,30 +4432,6 @@
     <t>S5 25 m</t>
   </si>
   <si>
-    <t>SN8 6 m</t>
-  </si>
-  <si>
-    <t>SN8 3 m</t>
-  </si>
-  <si>
-    <t>SN4 3 m</t>
-  </si>
-  <si>
-    <t>800 6 m</t>
-  </si>
-  <si>
-    <t>SN4 6 m</t>
-  </si>
-  <si>
-    <t>SN8 M3</t>
-  </si>
-  <si>
-    <t>SN4 M3</t>
-  </si>
-  <si>
-    <t>SN16 M3</t>
-  </si>
-  <si>
     <t>PN16 6m</t>
   </si>
   <si>
@@ -4748,6 +4718,24 @@
   </si>
   <si>
     <t>sp 3,5 300 mt B/r</t>
+  </si>
+  <si>
+    <t>SN8 6 mt</t>
+  </si>
+  <si>
+    <t>SN8 3 mt</t>
+  </si>
+  <si>
+    <t>SN4 3 mt</t>
+  </si>
+  <si>
+    <t>SN4 6 mt</t>
+  </si>
+  <si>
+    <t>800 6 mt</t>
+  </si>
+  <si>
+    <t>SN16 6 mt</t>
   </si>
 </sst>
 </file>
@@ -5106,16 +5094,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C1" t="s">
         <v>1417</v>
       </c>
-      <c r="B1" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1419</v>
-      </c>
       <c r="D1" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -5129,7 +5117,7 @@
         <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -5143,7 +5131,7 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -5157,7 +5145,7 @@
         <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -5171,7 +5159,7 @@
         <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -5185,7 +5173,7 @@
         <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -5199,7 +5187,7 @@
         <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -5213,7 +5201,7 @@
         <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -5227,7 +5215,7 @@
         <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -5241,7 +5229,7 @@
         <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -5255,7 +5243,7 @@
         <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -5269,7 +5257,7 @@
         <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -5283,7 +5271,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -5297,7 +5285,7 @@
         <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -5311,7 +5299,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -5325,7 +5313,7 @@
         <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -5339,7 +5327,7 @@
         <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -5353,7 +5341,7 @@
         <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -5367,7 +5355,7 @@
         <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -5381,7 +5369,7 @@
         <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -5395,7 +5383,7 @@
         <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -5409,7 +5397,7 @@
         <v>63</v>
       </c>
       <c r="D22" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -5423,7 +5411,7 @@
         <v>63</v>
       </c>
       <c r="D23" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -5437,7 +5425,7 @@
         <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -5451,7 +5439,7 @@
         <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -5465,7 +5453,7 @@
         <v>63</v>
       </c>
       <c r="D26" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -5479,7 +5467,7 @@
         <v>63</v>
       </c>
       <c r="D27" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -5493,7 +5481,7 @@
         <v>75</v>
       </c>
       <c r="D28" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -5507,7 +5495,7 @@
         <v>75</v>
       </c>
       <c r="D29" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -5521,7 +5509,7 @@
         <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -5535,7 +5523,7 @@
         <v>75</v>
       </c>
       <c r="D31" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -5549,7 +5537,7 @@
         <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -5563,7 +5551,7 @@
         <v>75</v>
       </c>
       <c r="D33" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -5577,7 +5565,7 @@
         <v>75</v>
       </c>
       <c r="D34" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -5591,7 +5579,7 @@
         <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -5605,7 +5593,7 @@
         <v>75</v>
       </c>
       <c r="D36" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -5619,7 +5607,7 @@
         <v>90</v>
       </c>
       <c r="D37" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -5633,7 +5621,7 @@
         <v>90</v>
       </c>
       <c r="D38" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -5647,7 +5635,7 @@
         <v>90</v>
       </c>
       <c r="D39" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -5661,7 +5649,7 @@
         <v>90</v>
       </c>
       <c r="D40" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -5675,7 +5663,7 @@
         <v>90</v>
       </c>
       <c r="D41" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -5689,7 +5677,7 @@
         <v>90</v>
       </c>
       <c r="D42" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -5703,7 +5691,7 @@
         <v>90</v>
       </c>
       <c r="D43" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -5717,7 +5705,7 @@
         <v>110</v>
       </c>
       <c r="D44" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -5731,7 +5719,7 @@
         <v>110</v>
       </c>
       <c r="D45" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -5745,7 +5733,7 @@
         <v>110</v>
       </c>
       <c r="D46" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -5759,7 +5747,7 @@
         <v>110</v>
       </c>
       <c r="D47" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -5773,7 +5761,7 @@
         <v>110</v>
       </c>
       <c r="D48" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -5787,7 +5775,7 @@
         <v>110</v>
       </c>
       <c r="D49" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -5801,7 +5789,7 @@
         <v>110</v>
       </c>
       <c r="D50" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -5815,7 +5803,7 @@
         <v>110</v>
       </c>
       <c r="D51" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -5829,7 +5817,7 @@
         <v>125</v>
       </c>
       <c r="D52" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -5843,7 +5831,7 @@
         <v>125</v>
       </c>
       <c r="D53" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -5857,7 +5845,7 @@
         <v>125</v>
       </c>
       <c r="D54" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -5871,7 +5859,7 @@
         <v>125</v>
       </c>
       <c r="D55" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -5885,7 +5873,7 @@
         <v>125</v>
       </c>
       <c r="D56" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -5899,7 +5887,7 @@
         <v>125</v>
       </c>
       <c r="D57" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -5913,7 +5901,7 @@
         <v>125</v>
       </c>
       <c r="D58" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -5927,7 +5915,7 @@
         <v>160</v>
       </c>
       <c r="D59" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -5941,7 +5929,7 @@
         <v>160</v>
       </c>
       <c r="D60" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -5955,7 +5943,7 @@
         <v>160</v>
       </c>
       <c r="D61" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -5969,7 +5957,7 @@
         <v>160</v>
       </c>
       <c r="D62" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -5983,7 +5971,7 @@
         <v>160</v>
       </c>
       <c r="D63" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -5997,7 +5985,7 @@
         <v>160</v>
       </c>
       <c r="D64" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -6011,7 +5999,7 @@
         <v>160</v>
       </c>
       <c r="D65" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -6025,7 +6013,7 @@
         <v>160</v>
       </c>
       <c r="D66" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -6039,7 +6027,7 @@
         <v>160</v>
       </c>
       <c r="D67" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -6053,7 +6041,7 @@
         <v>160</v>
       </c>
       <c r="D68" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -6067,7 +6055,7 @@
         <v>200</v>
       </c>
       <c r="D69" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -6081,7 +6069,7 @@
         <v>200</v>
       </c>
       <c r="D70" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -6095,7 +6083,7 @@
         <v>200</v>
       </c>
       <c r="D71" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -6109,7 +6097,7 @@
         <v>200</v>
       </c>
       <c r="D72" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -6123,7 +6111,7 @@
         <v>200</v>
       </c>
       <c r="D73" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
     </row>
   </sheetData>
@@ -6147,16 +6135,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C1" t="s">
         <v>1417</v>
       </c>
-      <c r="B1" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1419</v>
-      </c>
       <c r="D1" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6170,7 +6158,7 @@
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -6184,7 +6172,7 @@
         <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -6198,7 +6186,7 @@
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -6212,7 +6200,7 @@
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -6226,7 +6214,7 @@
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -6240,7 +6228,7 @@
         <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -6254,7 +6242,7 @@
         <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -6268,7 +6256,7 @@
         <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -6282,7 +6270,7 @@
         <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -6296,7 +6284,7 @@
         <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -6310,7 +6298,7 @@
         <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -6324,7 +6312,7 @@
         <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -6338,7 +6326,7 @@
         <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -6352,7 +6340,7 @@
         <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -6366,7 +6354,7 @@
         <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -6380,7 +6368,7 @@
         <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -6394,7 +6382,7 @@
         <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -6408,7 +6396,7 @@
         <v>110</v>
       </c>
       <c r="D19" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -6422,7 +6410,7 @@
         <v>110</v>
       </c>
       <c r="D20" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
     </row>
   </sheetData>
@@ -6437,7 +6425,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74A1C685-65B4-40E2-96F9-86C8DE8EDC41}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -6447,16 +6435,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1417</v>
       </c>
-      <c r="B1" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1419</v>
-      </c>
       <c r="D1" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6469,8 +6457,8 @@
       <c r="C2">
         <v>125</v>
       </c>
-      <c r="D2" t="s">
-        <v>1456</v>
+      <c r="D2" s="1" t="s">
+        <v>1550</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -6484,7 +6472,7 @@
         <v>125</v>
       </c>
       <c r="D3" t="s">
-        <v>1457</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -6498,7 +6486,7 @@
         <v>160</v>
       </c>
       <c r="D4" t="s">
-        <v>1456</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -6511,8 +6499,8 @@
       <c r="C5">
         <v>160</v>
       </c>
-      <c r="D5" t="s">
-        <v>1461</v>
+      <c r="D5" s="1" t="s">
+        <v>1551</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -6526,7 +6514,7 @@
         <v>200</v>
       </c>
       <c r="D6" t="s">
-        <v>1456</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -6540,7 +6528,7 @@
         <v>200</v>
       </c>
       <c r="D7" t="s">
-        <v>1457</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -6554,7 +6542,7 @@
         <v>200</v>
       </c>
       <c r="D8" t="s">
-        <v>1458</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -6568,7 +6556,7 @@
         <v>200</v>
       </c>
       <c r="D9" t="s">
-        <v>1458</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -6582,7 +6570,7 @@
         <v>200</v>
       </c>
       <c r="D10" t="s">
-        <v>1460</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -6596,7 +6584,7 @@
         <v>250</v>
       </c>
       <c r="D11" t="s">
-        <v>1456</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -6609,8 +6597,8 @@
       <c r="C12">
         <v>250</v>
       </c>
-      <c r="D12" t="s">
-        <v>1462</v>
+      <c r="D12" s="1" t="s">
+        <v>1552</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -6624,7 +6612,7 @@
         <v>250</v>
       </c>
       <c r="D13" t="s">
-        <v>1460</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -6638,7 +6626,7 @@
         <v>250</v>
       </c>
       <c r="D14" t="s">
-        <v>1458</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -6652,7 +6640,7 @@
         <v>315</v>
       </c>
       <c r="D15" t="s">
-        <v>1456</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -6665,8 +6653,8 @@
       <c r="C16">
         <v>315</v>
       </c>
-      <c r="D16" t="s">
-        <v>1461</v>
+      <c r="D16" s="1" t="s">
+        <v>1551</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -6679,8 +6667,8 @@
       <c r="C17">
         <v>315</v>
       </c>
-      <c r="D17" t="s">
-        <v>1462</v>
+      <c r="D17" s="1" t="s">
+        <v>1552</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -6694,7 +6682,7 @@
         <v>315</v>
       </c>
       <c r="D18" t="s">
-        <v>1460</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -6708,7 +6696,7 @@
         <v>400</v>
       </c>
       <c r="D19" t="s">
-        <v>1456</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -6721,8 +6709,8 @@
       <c r="C20">
         <v>400</v>
       </c>
-      <c r="D20" t="s">
-        <v>1462</v>
+      <c r="D20" s="1" t="s">
+        <v>1552</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -6736,7 +6724,7 @@
         <v>400</v>
       </c>
       <c r="D21" t="s">
-        <v>1460</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -6749,8 +6737,8 @@
       <c r="C22">
         <v>500</v>
       </c>
-      <c r="D22" t="s">
-        <v>1456</v>
+      <c r="D22" s="1" t="s">
+        <v>1550</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -6763,8 +6751,8 @@
       <c r="C23">
         <v>500</v>
       </c>
-      <c r="D23" t="s">
-        <v>1462</v>
+      <c r="D23" s="1" t="s">
+        <v>1552</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -6777,8 +6765,8 @@
       <c r="C24">
         <v>500</v>
       </c>
-      <c r="D24" t="s">
-        <v>1460</v>
+      <c r="D24" s="1" t="s">
+        <v>1553</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -6791,8 +6779,8 @@
       <c r="C25">
         <v>630</v>
       </c>
-      <c r="D25" t="s">
-        <v>1461</v>
+      <c r="D25" s="1" t="s">
+        <v>1550</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -6805,8 +6793,8 @@
       <c r="C26">
         <v>630</v>
       </c>
-      <c r="D26" t="s">
-        <v>1462</v>
+      <c r="D26" s="1" t="s">
+        <v>1552</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -6819,8 +6807,8 @@
       <c r="C27">
         <v>630</v>
       </c>
-      <c r="D27" t="s">
-        <v>1462</v>
+      <c r="D27" s="1" t="s">
+        <v>1553</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -6833,8 +6821,8 @@
       <c r="C28">
         <v>800</v>
       </c>
-      <c r="D28" t="s">
-        <v>1459</v>
+      <c r="D28" s="1" t="s">
+        <v>1554</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -6847,8 +6835,8 @@
       <c r="C29">
         <v>800</v>
       </c>
-      <c r="D29" t="s">
-        <v>1456</v>
+      <c r="D29" s="1" t="s">
+        <v>1550</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -6861,92 +6849,78 @@
       <c r="C30">
         <v>800</v>
       </c>
-      <c r="D30" t="s">
-        <v>1460</v>
+      <c r="D30" s="1" t="s">
+        <v>1553</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1250</v>
+        <v>1182</v>
       </c>
       <c r="B31" t="s">
-        <v>1251</v>
+        <v>1183</v>
       </c>
       <c r="C31">
-        <v>930</v>
-      </c>
-      <c r="D31" t="s">
-        <v>1461</v>
+        <v>1000</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>1550</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="B32" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="C32">
         <v>1000</v>
       </c>
-      <c r="D32" t="s">
-        <v>1461</v>
+      <c r="D32" s="1" t="s">
+        <v>1553</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="B33" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="C33">
-        <v>1000</v>
-      </c>
-      <c r="D33" t="s">
-        <v>1462</v>
+        <v>1200</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>1555</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="B34" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="C34">
         <v>1200</v>
       </c>
-      <c r="D34" t="s">
-        <v>1463</v>
+      <c r="D34" s="1" t="s">
+        <v>1550</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="B35" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="C35">
         <v>1200</v>
       </c>
-      <c r="D35" t="s">
-        <v>1461</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B36" t="s">
-        <v>1191</v>
-      </c>
-      <c r="C36">
-        <v>1200</v>
-      </c>
-      <c r="D36" t="s">
-        <v>1462</v>
+      <c r="D35" s="1" t="s">
+        <v>1553</v>
       </c>
     </row>
   </sheetData>
@@ -6972,16 +6946,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1417</v>
       </c>
-      <c r="B1" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1419</v>
-      </c>
       <c r="D1" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6995,7 +6969,7 @@
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -7009,7 +6983,7 @@
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -7023,7 +6997,7 @@
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -7037,7 +7011,7 @@
         <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -7051,7 +7025,7 @@
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -7065,7 +7039,7 @@
         <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -7079,7 +7053,7 @@
         <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -7093,7 +7067,7 @@
         <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -7107,7 +7081,7 @@
         <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -7121,7 +7095,7 @@
         <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -7135,7 +7109,7 @@
         <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -7149,7 +7123,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>1467</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -7163,7 +7137,7 @@
         <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>1470</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -7177,7 +7151,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -7191,7 +7165,7 @@
         <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>1468</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -7205,7 +7179,7 @@
         <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -7219,7 +7193,7 @@
         <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>1469</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -7233,7 +7207,7 @@
         <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -7247,7 +7221,7 @@
         <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>1467</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -7261,7 +7235,7 @@
         <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>1470</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -7275,7 +7249,7 @@
         <v>63</v>
       </c>
       <c r="D22" t="s">
-        <v>1471</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -7289,7 +7263,7 @@
         <v>63</v>
       </c>
       <c r="D23" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -7303,7 +7277,7 @@
         <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>1468</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -7317,7 +7291,7 @@
         <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -7331,7 +7305,7 @@
         <v>63</v>
       </c>
       <c r="D26" t="s">
-        <v>1469</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -7345,7 +7319,7 @@
         <v>75</v>
       </c>
       <c r="D27" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -7359,7 +7333,7 @@
         <v>75</v>
       </c>
       <c r="D28" t="s">
-        <v>1467</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -7373,7 +7347,7 @@
         <v>75</v>
       </c>
       <c r="D29" t="s">
-        <v>1470</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -7387,7 +7361,7 @@
         <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>1471</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -7401,7 +7375,7 @@
         <v>75</v>
       </c>
       <c r="D31" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -7415,7 +7389,7 @@
         <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>1468</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -7429,7 +7403,7 @@
         <v>75</v>
       </c>
       <c r="D33" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -7443,7 +7417,7 @@
         <v>75</v>
       </c>
       <c r="D34" t="s">
-        <v>1469</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -7457,7 +7431,7 @@
         <v>90</v>
       </c>
       <c r="D35" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -7471,7 +7445,7 @@
         <v>90</v>
       </c>
       <c r="D36" t="s">
-        <v>1467</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -7485,7 +7459,7 @@
         <v>90</v>
       </c>
       <c r="D37" t="s">
-        <v>1470</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -7499,7 +7473,7 @@
         <v>90</v>
       </c>
       <c r="D38" t="s">
-        <v>1471</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -7513,7 +7487,7 @@
         <v>90</v>
       </c>
       <c r="D39" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -7527,7 +7501,7 @@
         <v>90</v>
       </c>
       <c r="D40" t="s">
-        <v>1468</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -7541,7 +7515,7 @@
         <v>90</v>
       </c>
       <c r="D41" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -7555,7 +7529,7 @@
         <v>90</v>
       </c>
       <c r="D42" t="s">
-        <v>1469</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -7569,7 +7543,7 @@
         <v>110</v>
       </c>
       <c r="D43" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -7583,7 +7557,7 @@
         <v>110</v>
       </c>
       <c r="D44" t="s">
-        <v>1467</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -7597,7 +7571,7 @@
         <v>110</v>
       </c>
       <c r="D45" t="s">
-        <v>1470</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -7611,7 +7585,7 @@
         <v>110</v>
       </c>
       <c r="D46" t="s">
-        <v>1471</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -7625,7 +7599,7 @@
         <v>110</v>
       </c>
       <c r="D47" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -7639,7 +7613,7 @@
         <v>110</v>
       </c>
       <c r="D48" t="s">
-        <v>1468</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -7653,7 +7627,7 @@
         <v>110</v>
       </c>
       <c r="D49" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -7667,7 +7641,7 @@
         <v>110</v>
       </c>
       <c r="D50" t="s">
-        <v>1469</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -7681,7 +7655,7 @@
         <v>125</v>
       </c>
       <c r="D51" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -7695,7 +7669,7 @@
         <v>125</v>
       </c>
       <c r="D52" t="s">
-        <v>1467</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -7709,7 +7683,7 @@
         <v>125</v>
       </c>
       <c r="D53" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -7723,7 +7697,7 @@
         <v>125</v>
       </c>
       <c r="D54" t="s">
-        <v>1468</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -7737,7 +7711,7 @@
         <v>125</v>
       </c>
       <c r="D55" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -7751,7 +7725,7 @@
         <v>125</v>
       </c>
       <c r="D56" t="s">
-        <v>1469</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -7765,7 +7739,7 @@
         <v>140</v>
       </c>
       <c r="D57" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -7779,7 +7753,7 @@
         <v>140</v>
       </c>
       <c r="D58" t="s">
-        <v>1467</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -7793,7 +7767,7 @@
         <v>140</v>
       </c>
       <c r="D59" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -7807,7 +7781,7 @@
         <v>140</v>
       </c>
       <c r="D60" t="s">
-        <v>1468</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -7821,7 +7795,7 @@
         <v>140</v>
       </c>
       <c r="D61" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -7835,7 +7809,7 @@
         <v>140</v>
       </c>
       <c r="D62" t="s">
-        <v>1469</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -7849,7 +7823,7 @@
         <v>160</v>
       </c>
       <c r="D63" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -7863,7 +7837,7 @@
         <v>160</v>
       </c>
       <c r="D64" t="s">
-        <v>1467</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -7877,7 +7851,7 @@
         <v>160</v>
       </c>
       <c r="D65" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -7891,7 +7865,7 @@
         <v>160</v>
       </c>
       <c r="D66" t="s">
-        <v>1468</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -7905,7 +7879,7 @@
         <v>160</v>
       </c>
       <c r="D67" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -7919,7 +7893,7 @@
         <v>160</v>
       </c>
       <c r="D68" t="s">
-        <v>1469</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -7933,7 +7907,7 @@
         <v>180</v>
       </c>
       <c r="D69" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -7947,7 +7921,7 @@
         <v>180</v>
       </c>
       <c r="D70" t="s">
-        <v>1467</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -7961,7 +7935,7 @@
         <v>180</v>
       </c>
       <c r="D71" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -7975,7 +7949,7 @@
         <v>180</v>
       </c>
       <c r="D72" t="s">
-        <v>1468</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -7989,7 +7963,7 @@
         <v>180</v>
       </c>
       <c r="D73" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -8003,7 +7977,7 @@
         <v>180</v>
       </c>
       <c r="D74" t="s">
-        <v>1469</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -8017,7 +7991,7 @@
         <v>200</v>
       </c>
       <c r="D75" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -8031,7 +8005,7 @@
         <v>200</v>
       </c>
       <c r="D76" t="s">
-        <v>1467</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -8045,7 +8019,7 @@
         <v>200</v>
       </c>
       <c r="D77" t="s">
-        <v>1467</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -8059,7 +8033,7 @@
         <v>200</v>
       </c>
       <c r="D78" t="s">
-        <v>1471</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -8073,7 +8047,7 @@
         <v>200</v>
       </c>
       <c r="D79" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -8087,7 +8061,7 @@
         <v>200</v>
       </c>
       <c r="D80" t="s">
-        <v>1468</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -8101,7 +8075,7 @@
         <v>200</v>
       </c>
       <c r="D81" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -8115,7 +8089,7 @@
         <v>200</v>
       </c>
       <c r="D82" t="s">
-        <v>1469</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -8129,7 +8103,7 @@
         <v>225</v>
       </c>
       <c r="D83" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -8143,7 +8117,7 @@
         <v>225</v>
       </c>
       <c r="D84" t="s">
-        <v>1467</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -8157,7 +8131,7 @@
         <v>225</v>
       </c>
       <c r="D85" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -8171,7 +8145,7 @@
         <v>225</v>
       </c>
       <c r="D86" t="s">
-        <v>1468</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -8185,7 +8159,7 @@
         <v>225</v>
       </c>
       <c r="D87" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -8199,7 +8173,7 @@
         <v>225</v>
       </c>
       <c r="D88" t="s">
-        <v>1469</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -8213,7 +8187,7 @@
         <v>250</v>
       </c>
       <c r="D89" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -8227,7 +8201,7 @@
         <v>250</v>
       </c>
       <c r="D90" t="s">
-        <v>1467</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -8241,7 +8215,7 @@
         <v>250</v>
       </c>
       <c r="D91" t="s">
-        <v>1471</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -8255,7 +8229,7 @@
         <v>250</v>
       </c>
       <c r="D92" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -8269,7 +8243,7 @@
         <v>250</v>
       </c>
       <c r="D93" t="s">
-        <v>1468</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -8283,7 +8257,7 @@
         <v>250</v>
       </c>
       <c r="D94" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -8297,7 +8271,7 @@
         <v>250</v>
       </c>
       <c r="D95" t="s">
-        <v>1469</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -8311,7 +8285,7 @@
         <v>280</v>
       </c>
       <c r="D96" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -8325,7 +8299,7 @@
         <v>280</v>
       </c>
       <c r="D97" t="s">
-        <v>1467</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -8339,7 +8313,7 @@
         <v>280</v>
       </c>
       <c r="D98" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -8353,7 +8327,7 @@
         <v>280</v>
       </c>
       <c r="D99" t="s">
-        <v>1468</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -8367,7 +8341,7 @@
         <v>280</v>
       </c>
       <c r="D100" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -8381,7 +8355,7 @@
         <v>280</v>
       </c>
       <c r="D101" t="s">
-        <v>1469</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -8395,7 +8369,7 @@
         <v>315</v>
       </c>
       <c r="D102" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -8409,7 +8383,7 @@
         <v>315</v>
       </c>
       <c r="D103" t="s">
-        <v>1467</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -8423,7 +8397,7 @@
         <v>315</v>
       </c>
       <c r="D104" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -8437,7 +8411,7 @@
         <v>315</v>
       </c>
       <c r="D105" t="s">
-        <v>1468</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -8451,7 +8425,7 @@
         <v>315</v>
       </c>
       <c r="D106" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -8465,7 +8439,7 @@
         <v>315</v>
       </c>
       <c r="D107" t="s">
-        <v>1469</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -8479,7 +8453,7 @@
         <v>355</v>
       </c>
       <c r="D108" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -8493,7 +8467,7 @@
         <v>355</v>
       </c>
       <c r="D109" t="s">
-        <v>1467</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -8507,7 +8481,7 @@
         <v>355</v>
       </c>
       <c r="D110" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -8521,7 +8495,7 @@
         <v>355</v>
       </c>
       <c r="D111" t="s">
-        <v>1468</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -8535,7 +8509,7 @@
         <v>355</v>
       </c>
       <c r="D112" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
@@ -8549,7 +8523,7 @@
         <v>400</v>
       </c>
       <c r="D113" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
@@ -8563,7 +8537,7 @@
         <v>400</v>
       </c>
       <c r="D114" t="s">
-        <v>1467</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
@@ -8577,7 +8551,7 @@
         <v>400</v>
       </c>
       <c r="D115" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
@@ -8591,7 +8565,7 @@
         <v>400</v>
       </c>
       <c r="D116" t="s">
-        <v>1468</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
@@ -8605,7 +8579,7 @@
         <v>400</v>
       </c>
       <c r="D117" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
@@ -8619,7 +8593,7 @@
         <v>400</v>
       </c>
       <c r="D118" t="s">
-        <v>1469</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
@@ -8633,7 +8607,7 @@
         <v>450</v>
       </c>
       <c r="D119" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
@@ -8647,7 +8621,7 @@
         <v>450</v>
       </c>
       <c r="D120" t="s">
-        <v>1467</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
@@ -8661,7 +8635,7 @@
         <v>500</v>
       </c>
       <c r="D121" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
@@ -8675,7 +8649,7 @@
         <v>500</v>
       </c>
       <c r="D122" t="s">
-        <v>1467</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
@@ -8689,7 +8663,7 @@
         <v>500</v>
       </c>
       <c r="D123" t="s">
-        <v>1464</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
@@ -8703,7 +8677,7 @@
         <v>500</v>
       </c>
       <c r="D124" t="s">
-        <v>1468</v>
+        <v>1458</v>
       </c>
     </row>
   </sheetData>
@@ -8728,16 +8702,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C1" t="s">
         <v>1417</v>
       </c>
-      <c r="B1" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1419</v>
-      </c>
       <c r="D1" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -8751,7 +8725,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1472</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -8765,7 +8739,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1473</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -8779,7 +8753,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1474</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -8793,7 +8767,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1481</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -8807,7 +8781,7 @@
         <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1475</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -8821,7 +8795,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1476</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -8835,7 +8809,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1477</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -8849,7 +8823,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1478</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -8863,7 +8837,7 @@
         <v>25</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1472</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -8877,7 +8851,7 @@
         <v>25</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1474</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -8891,7 +8865,7 @@
         <v>25</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1473</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -8905,7 +8879,7 @@
         <v>25</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1472</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -8919,7 +8893,7 @@
         <v>25</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1475</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -8933,7 +8907,7 @@
         <v>25</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1478</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -8947,7 +8921,7 @@
         <v>25</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1479</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -8961,7 +8935,7 @@
         <v>25</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1476</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -8975,7 +8949,7 @@
         <v>25</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1480</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -8989,7 +8963,7 @@
         <v>25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1477</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -9003,7 +8977,7 @@
         <v>32</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1472</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -9017,7 +8991,7 @@
         <v>32</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1472</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -9031,7 +9005,7 @@
         <v>32</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1474</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -9045,7 +9019,7 @@
         <v>32</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1475</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -9059,7 +9033,7 @@
         <v>32</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1479</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -9073,7 +9047,7 @@
         <v>32</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1476</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -9087,7 +9061,7 @@
         <v>32</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1477</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -9101,7 +9075,7 @@
         <v>32</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1473</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -9115,7 +9089,7 @@
         <v>32</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1478</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -9129,7 +9103,7 @@
         <v>40</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1472</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -9143,7 +9117,7 @@
         <v>40</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1474</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -9157,7 +9131,7 @@
         <v>40</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1475</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -9171,7 +9145,7 @@
         <v>40</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1479</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -9185,7 +9159,7 @@
         <v>40</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1476</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -9199,7 +9173,7 @@
         <v>40</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>1477</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -9213,7 +9187,7 @@
         <v>50</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1472</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -9227,7 +9201,7 @@
         <v>50</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1474</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -9241,7 +9215,7 @@
         <v>50</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1475</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -9255,7 +9229,7 @@
         <v>50</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>1479</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -9269,7 +9243,7 @@
         <v>50</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1476</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -9283,7 +9257,7 @@
         <v>50</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1477</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -9297,7 +9271,7 @@
         <v>63</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1472</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -9311,7 +9285,7 @@
         <v>63</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>1474</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -9325,7 +9299,7 @@
         <v>63</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>1475</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -9339,7 +9313,7 @@
         <v>63</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1479</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -9353,7 +9327,7 @@
         <v>63</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1476</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -9367,7 +9341,7 @@
         <v>63</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1477</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -9381,7 +9355,7 @@
         <v>75</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1472</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -9395,7 +9369,7 @@
         <v>75</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1474</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -9409,7 +9383,7 @@
         <v>75</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1475</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -9423,7 +9397,7 @@
         <v>75</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1479</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -9437,7 +9411,7 @@
         <v>75</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>1476</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -9451,7 +9425,7 @@
         <v>75</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1477</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -9465,7 +9439,7 @@
         <v>90</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1474</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -9479,7 +9453,7 @@
         <v>90</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>1479</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -9493,7 +9467,7 @@
         <v>90</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1477</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -9507,7 +9481,7 @@
         <v>90</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1475</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -9521,7 +9495,7 @@
         <v>90</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1476</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -9535,7 +9509,7 @@
         <v>110</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>1474</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -9549,7 +9523,7 @@
         <v>110</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1479</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -9563,7 +9537,7 @@
         <v>110</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1475</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -9577,7 +9551,7 @@
         <v>110</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>1477</v>
+        <v>1467</v>
       </c>
     </row>
   </sheetData>
@@ -9603,16 +9577,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1417</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1419</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>1482</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -9626,7 +9600,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1475</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -9640,7 +9614,7 @@
         <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1483</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -9654,7 +9628,7 @@
         <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1475</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -9668,7 +9642,7 @@
         <v>32</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1483</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -9682,7 +9656,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1475</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -9696,7 +9670,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1476</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -9710,7 +9684,7 @@
         <v>40</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1483</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -9724,7 +9698,7 @@
         <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1475</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
@@ -9740,7 +9714,7 @@
         <v>40</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1476</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -9754,7 +9728,7 @@
         <v>50</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1483</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -9768,7 +9742,7 @@
         <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1475</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -9782,7 +9756,7 @@
         <v>63</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1484</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -9796,7 +9770,7 @@
         <v>63</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1485</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -9810,7 +9784,7 @@
         <v>63</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1483</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
@@ -9826,7 +9800,7 @@
         <v>63</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1486</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -9840,7 +9814,7 @@
         <v>63</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1487</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -9854,7 +9828,7 @@
         <v>63</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1472</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -9868,7 +9842,7 @@
         <v>63</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1475</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -9882,7 +9856,7 @@
         <v>63</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1479</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -9896,7 +9870,7 @@
         <v>63</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1476</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
@@ -9912,7 +9886,7 @@
         <v>75</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1484</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -9926,7 +9900,7 @@
         <v>75</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1483</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -9940,7 +9914,7 @@
         <v>75</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1486</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -9954,7 +9928,7 @@
         <v>75</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1475</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -9968,7 +9942,7 @@
         <v>75</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1479</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -9982,7 +9956,7 @@
         <v>90</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1479</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -9996,7 +9970,7 @@
         <v>90</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>1477</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -10010,7 +9984,7 @@
         <v>110</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1483</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
@@ -10025,7 +9999,7 @@
         <v>110</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1486</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -10039,7 +10013,7 @@
         <v>110</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>1479</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -10053,7 +10027,7 @@
         <v>125</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1483</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
@@ -10069,7 +10043,7 @@
         <v>125</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>1486</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -10083,7 +10057,7 @@
         <v>140</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>1483</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -10097,7 +10071,7 @@
         <v>140</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1486</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -10111,7 +10085,7 @@
         <v>160</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1483</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -10125,7 +10099,7 @@
         <v>160</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1486</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -10139,7 +10113,7 @@
         <v>180</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1483</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -10153,7 +10127,7 @@
         <v>180</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1486</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -10167,7 +10141,7 @@
         <v>200</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1483</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -10181,7 +10155,7 @@
         <v>200</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1486</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
@@ -10196,7 +10170,7 @@
         <v>225</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1483</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -10210,7 +10184,7 @@
         <v>225</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1486</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -10224,7 +10198,7 @@
         <v>250</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>1483</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -10238,7 +10212,7 @@
         <v>250</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1486</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -10252,7 +10226,7 @@
         <v>315</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1486</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -10266,7 +10240,7 @@
         <v>400</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1485</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
@@ -10336,16 +10310,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1417</v>
       </c>
-      <c r="B1" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1419</v>
-      </c>
       <c r="D1" t="s">
-        <v>1482</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -10359,7 +10333,7 @@
         <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>1517</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -10373,7 +10347,7 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>1518</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -10387,7 +10361,7 @@
         <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>1519</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -10401,7 +10375,7 @@
         <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>1520</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -10415,7 +10389,7 @@
         <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>1521</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -10429,7 +10403,7 @@
         <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>1522</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -10443,7 +10417,7 @@
         <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>1525</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -10457,7 +10431,7 @@
         <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -10471,7 +10445,7 @@
         <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>1526</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -10485,7 +10459,7 @@
         <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>1528</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -10499,10 +10473,10 @@
         <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>1530</v>
+        <v>1520</v>
       </c>
       <c r="E12" t="s">
-        <v>1529</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -10516,7 +10490,7 @@
         <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>1531</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -10530,7 +10504,7 @@
         <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>1532</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -10544,7 +10518,7 @@
         <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>1533</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -10558,7 +10532,7 @@
         <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>1559</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -10572,7 +10546,7 @@
         <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>1524</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -10586,7 +10560,7 @@
         <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>1551</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -10600,7 +10574,7 @@
         <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>1550</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -10614,7 +10588,7 @@
         <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>1552</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -10628,7 +10602,7 @@
         <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>1553</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -10642,7 +10616,7 @@
         <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>1555</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -10656,7 +10630,7 @@
         <v>50</v>
       </c>
       <c r="D23" t="s">
-        <v>1556</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -10670,7 +10644,7 @@
         <v>50</v>
       </c>
       <c r="D24" t="s">
-        <v>1554</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -10684,7 +10658,7 @@
         <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>1532</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -10698,7 +10672,7 @@
         <v>50</v>
       </c>
       <c r="D26" t="s">
-        <v>1558</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -10712,7 +10686,7 @@
         <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>1549</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -10726,7 +10700,7 @@
         <v>50</v>
       </c>
       <c r="D28" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -10740,7 +10714,7 @@
         <v>50</v>
       </c>
       <c r="D29" t="s">
-        <v>1547</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -10754,7 +10728,7 @@
         <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>1524</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -10768,7 +10742,7 @@
         <v>50</v>
       </c>
       <c r="D31" t="s">
-        <v>1557</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -10782,7 +10756,7 @@
         <v>63</v>
       </c>
       <c r="D32" t="s">
-        <v>1534</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -10796,7 +10770,7 @@
         <v>63</v>
       </c>
       <c r="D33" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -10810,7 +10784,7 @@
         <v>63</v>
       </c>
       <c r="D34" t="s">
-        <v>1523</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -10824,7 +10798,7 @@
         <v>63</v>
       </c>
       <c r="D35" t="s">
-        <v>1544</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -10838,7 +10812,7 @@
         <v>63</v>
       </c>
       <c r="D36" t="s">
-        <v>1545</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -10852,7 +10826,7 @@
         <v>75</v>
       </c>
       <c r="D37" t="s">
-        <v>1534</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -10866,7 +10840,7 @@
         <v>75</v>
       </c>
       <c r="D38" t="s">
-        <v>1540</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -10880,7 +10854,7 @@
         <v>75</v>
       </c>
       <c r="D39" t="s">
-        <v>1523</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -10894,7 +10868,7 @@
         <v>90</v>
       </c>
       <c r="D40" t="s">
-        <v>1535</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -10908,7 +10882,7 @@
         <v>90</v>
       </c>
       <c r="D41" t="s">
-        <v>1536</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -10922,7 +10896,7 @@
         <v>110</v>
       </c>
       <c r="D42" t="s">
-        <v>1538</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -10936,7 +10910,7 @@
         <v>110</v>
       </c>
       <c r="D43" t="s">
-        <v>1541</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -10950,7 +10924,7 @@
         <v>125</v>
       </c>
       <c r="D44" t="s">
-        <v>1537</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -10964,7 +10938,7 @@
         <v>125</v>
       </c>
       <c r="D45" t="s">
-        <v>1538</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -10978,7 +10952,7 @@
         <v>125</v>
       </c>
       <c r="D46" t="s">
-        <v>1542</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -10992,7 +10966,7 @@
         <v>125</v>
       </c>
       <c r="D47" t="s">
-        <v>1543</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -11006,7 +10980,7 @@
         <v>125</v>
       </c>
       <c r="D48" t="s">
-        <v>1535</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -11020,7 +10994,7 @@
         <v>140</v>
       </c>
       <c r="D49" t="s">
-        <v>1537</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -11034,7 +11008,7 @@
         <v>140</v>
       </c>
       <c r="D50" t="s">
-        <v>1538</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -11048,7 +11022,7 @@
         <v>140</v>
       </c>
       <c r="D51" t="s">
-        <v>1542</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -11062,7 +11036,7 @@
         <v>140</v>
       </c>
       <c r="D52" t="s">
-        <v>1543</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -11076,7 +11050,7 @@
         <v>140</v>
       </c>
       <c r="D53" t="s">
-        <v>1539</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -11090,7 +11064,7 @@
         <v>140</v>
       </c>
       <c r="D54" t="s">
-        <v>1535</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -11104,7 +11078,7 @@
         <v>160</v>
       </c>
       <c r="D55" t="s">
-        <v>1537</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -11118,7 +11092,7 @@
         <v>160</v>
       </c>
       <c r="D56" t="s">
-        <v>1538</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -11132,7 +11106,7 @@
         <v>160</v>
       </c>
       <c r="D57" t="s">
-        <v>1542</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -11146,7 +11120,7 @@
         <v>160</v>
       </c>
       <c r="D58" t="s">
-        <v>1543</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -11160,7 +11134,7 @@
         <v>160</v>
       </c>
       <c r="D59" t="s">
-        <v>1539</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -11174,7 +11148,7 @@
         <v>160</v>
       </c>
       <c r="D60" t="s">
-        <v>1535</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -11188,7 +11162,7 @@
         <v>180</v>
       </c>
       <c r="D61" t="s">
-        <v>1542</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -11202,7 +11176,7 @@
         <v>180</v>
       </c>
       <c r="D62" t="s">
-        <v>1543</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -11216,7 +11190,7 @@
         <v>180</v>
       </c>
       <c r="D63" t="s">
-        <v>1535</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -11230,7 +11204,7 @@
         <v>200</v>
       </c>
       <c r="D64" t="s">
-        <v>1537</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -11244,7 +11218,7 @@
         <v>200</v>
       </c>
       <c r="D65" t="s">
-        <v>1538</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -11258,7 +11232,7 @@
         <v>200</v>
       </c>
       <c r="D66" t="s">
-        <v>1542</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -11272,7 +11246,7 @@
         <v>200</v>
       </c>
       <c r="D67" t="s">
-        <v>1543</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -11286,7 +11260,7 @@
         <v>200</v>
       </c>
       <c r="D68" t="s">
-        <v>1539</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -11300,7 +11274,7 @@
         <v>200</v>
       </c>
       <c r="D69" t="s">
-        <v>1535</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -11314,7 +11288,7 @@
         <v>225</v>
       </c>
       <c r="D70" t="s">
-        <v>1538</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -11328,7 +11302,7 @@
         <v>225</v>
       </c>
       <c r="D71" t="s">
-        <v>1543</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -11342,7 +11316,7 @@
         <v>250</v>
       </c>
       <c r="D72" t="s">
-        <v>1538</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -11356,7 +11330,7 @@
         <v>250</v>
       </c>
       <c r="D73" t="s">
-        <v>1542</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -11370,7 +11344,7 @@
         <v>250</v>
       </c>
       <c r="D74" t="s">
-        <v>1543</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -11384,7 +11358,7 @@
         <v>250</v>
       </c>
       <c r="D75" t="s">
-        <v>1535</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -11398,7 +11372,7 @@
         <v>280</v>
       </c>
       <c r="D76" t="s">
-        <v>1537</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -11412,7 +11386,7 @@
         <v>280</v>
       </c>
       <c r="D77" t="s">
-        <v>1543</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -11426,7 +11400,7 @@
         <v>315</v>
       </c>
       <c r="D78" t="s">
-        <v>1538</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -11440,7 +11414,7 @@
         <v>315</v>
       </c>
       <c r="D79" t="s">
-        <v>1539</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -11454,7 +11428,7 @@
         <v>315</v>
       </c>
       <c r="D80" t="s">
-        <v>1535</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -11468,7 +11442,7 @@
         <v>500</v>
       </c>
       <c r="D81" t="s">
-        <v>1535</v>
+        <v>1525</v>
       </c>
     </row>
   </sheetData>
@@ -11493,16 +11467,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="B1" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>1419</v>
+      </c>
+      <c r="D1" t="s">
         <v>1421</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1423</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -11516,7 +11490,7 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1488</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -11530,7 +11504,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1495</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -11544,7 +11518,7 @@
         <v>16</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1498</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -11558,7 +11532,7 @@
         <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1496</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -11572,7 +11546,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1499</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -11586,7 +11560,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1472</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -11600,7 +11574,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1488</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -11614,7 +11588,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1495</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -11628,7 +11602,7 @@
         <v>20</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1497</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -11642,7 +11616,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1505</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -11656,7 +11630,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1489</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -11670,7 +11644,7 @@
         <v>20</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1490</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -11684,7 +11658,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1508</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -11698,7 +11672,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1496</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -11712,7 +11686,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1493</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -11726,7 +11700,7 @@
         <v>20</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1494</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -11740,7 +11714,7 @@
         <v>20</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1491</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -11754,7 +11728,7 @@
         <v>20</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1509</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -11768,7 +11742,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1507</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -11782,7 +11756,7 @@
         <v>25</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1500</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -11796,7 +11770,7 @@
         <v>25</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1495</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -11810,7 +11784,7 @@
         <v>25</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1497</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -11824,7 +11798,7 @@
         <v>25</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -11838,7 +11812,7 @@
         <v>25</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1492</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -11852,7 +11826,7 @@
         <v>25</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1496</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -11866,7 +11840,7 @@
         <v>25</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1493</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -11880,7 +11854,7 @@
         <v>25</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1502</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -11894,7 +11868,7 @@
         <v>25</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1506</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -11908,7 +11882,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1507</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -11922,7 +11896,7 @@
         <v>32</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1500</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -11936,7 +11910,7 @@
         <v>32</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1497</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -11950,7 +11924,7 @@
         <v>32</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1501</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -11964,7 +11938,7 @@
         <v>32</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>1498</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -11978,7 +11952,7 @@
         <v>32</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1493</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -11992,7 +11966,7 @@
         <v>32</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1494</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -12006,7 +11980,7 @@
         <v>32</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1506</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -12020,7 +11994,7 @@
         <v>32</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>1507</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -12034,7 +12008,7 @@
         <v>40</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1506</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -12048,7 +12022,7 @@
         <v>40</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1511</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -12062,7 +12036,7 @@
         <v>40</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1501</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -12076,7 +12050,7 @@
         <v>40</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>1498</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -12090,7 +12064,7 @@
         <v>40</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>1502</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -12104,7 +12078,7 @@
         <v>40</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1506</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -12118,7 +12092,7 @@
         <v>50</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1500</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -12132,7 +12106,7 @@
         <v>50</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1511</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -12146,7 +12120,7 @@
         <v>50</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1501</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -12160,7 +12134,7 @@
         <v>50</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1512</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -12174,7 +12148,7 @@
         <v>50</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1498</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -12188,7 +12162,7 @@
         <v>50</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1506</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -12202,7 +12176,7 @@
         <v>63</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>1488</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -12216,7 +12190,7 @@
         <v>63</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1497</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -12230,7 +12204,7 @@
         <v>63</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1498</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -12244,7 +12218,7 @@
         <v>63</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>1498</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -12258,7 +12232,7 @@
         <v>75</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1500</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -12272,7 +12246,7 @@
         <v>75</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1511</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -12286,7 +12260,7 @@
         <v>75</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1492</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -12300,7 +12274,7 @@
         <v>75</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>1472</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -12314,7 +12288,7 @@
         <v>90</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1511</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -12328,7 +12302,7 @@
         <v>90</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1513</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -12342,7 +12316,7 @@
         <v>110</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>1497</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -12356,7 +12330,7 @@
         <v>110</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>1493</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -12370,7 +12344,7 @@
         <v>161</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1497</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -12384,7 +12358,7 @@
         <v>161</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>1493</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -12398,7 +12372,7 @@
         <v>162</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>1501</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -12412,7 +12386,7 @@
         <v>162</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>1502</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -12426,7 +12400,7 @@
         <v>162</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>1504</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -12440,7 +12414,7 @@
         <v>165</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>1514</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -12454,7 +12428,7 @@
         <v>165</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>1503</v>
+        <v>1493</v>
       </c>
     </row>
   </sheetData>
@@ -12478,16 +12452,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1417</v>
       </c>
-      <c r="B1" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1419</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>1515</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -12501,7 +12475,7 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1488</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -12515,7 +12489,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1505</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -12529,7 +12503,7 @@
         <v>16</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1489</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -12543,7 +12517,7 @@
         <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1490</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -12557,7 +12531,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1492</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -12571,7 +12545,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1493</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -12585,7 +12559,7 @@
         <v>16</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1494</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -12599,7 +12573,7 @@
         <v>16</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1516</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -12613,7 +12587,7 @@
         <v>20</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1488</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -12627,7 +12601,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1505</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -12641,7 +12615,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1489</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -12655,7 +12629,7 @@
         <v>20</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1492</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -12669,7 +12643,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1493</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -12683,7 +12657,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1494</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -12697,7 +12671,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1491</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -12711,7 +12685,7 @@
         <v>25</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1488</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -12725,7 +12699,7 @@
         <v>25</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1505</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -12739,7 +12713,7 @@
         <v>25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1492</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -12753,7 +12727,7 @@
         <v>25</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1493</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -12767,7 +12741,7 @@
         <v>25</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1494</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -12781,7 +12755,7 @@
         <v>32</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1488</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -12795,7 +12769,7 @@
         <v>32</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1497</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -12809,7 +12783,7 @@
         <v>32</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1505</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -12823,7 +12797,7 @@
         <v>32</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1492</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -12837,7 +12811,7 @@
         <v>32</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1493</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -12851,7 +12825,7 @@
         <v>32</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1494</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -12865,7 +12839,7 @@
         <v>40</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1488</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -12879,7 +12853,7 @@
         <v>40</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1497</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -12893,7 +12867,7 @@
         <v>40</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1505</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -12907,7 +12881,7 @@
         <v>40</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1492</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -12921,7 +12895,7 @@
         <v>40</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1493</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -12935,7 +12909,7 @@
         <v>40</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1494</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -12949,7 +12923,7 @@
         <v>50</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>1497</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -12963,7 +12937,7 @@
         <v>50</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1489</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -12977,7 +12951,7 @@
         <v>50</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1492</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -12991,7 +12965,7 @@
         <v>63</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1488</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -13005,7 +12979,7 @@
         <v>63</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>1492</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -13019,7 +12993,7 @@
         <v>75</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1488</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -13033,7 +13007,7 @@
         <v>75</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1492</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -13047,7 +13021,7 @@
         <v>90</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1497</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -13061,7 +13035,7 @@
         <v>90</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>1493</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -13075,7 +13049,7 @@
         <v>110</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>1497</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -13089,7 +13063,7 @@
         <v>110</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1493</v>
+        <v>1483</v>
       </c>
     </row>
   </sheetData>
@@ -13115,16 +13089,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C1" t="s">
         <v>1417</v>
       </c>
-      <c r="B1" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1419</v>
-      </c>
       <c r="D1" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -13138,7 +13112,7 @@
         <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -13152,7 +13126,7 @@
         <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -13166,7 +13140,7 @@
         <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -13180,7 +13154,7 @@
         <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -13194,7 +13168,7 @@
         <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -13208,7 +13182,7 @@
         <v>125</v>
       </c>
       <c r="D7" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -13222,7 +13196,7 @@
         <v>125</v>
       </c>
       <c r="D8" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -13236,7 +13210,7 @@
         <v>125</v>
       </c>
       <c r="D9" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -13250,7 +13224,7 @@
         <v>125</v>
       </c>
       <c r="D10" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -13264,7 +13238,7 @@
         <v>160</v>
       </c>
       <c r="D11" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -13278,7 +13252,7 @@
         <v>160</v>
       </c>
       <c r="D12" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -13292,7 +13266,7 @@
         <v>160</v>
       </c>
       <c r="D13" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -13306,7 +13280,7 @@
         <v>160</v>
       </c>
       <c r="D14" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -13320,7 +13294,7 @@
         <v>200</v>
       </c>
       <c r="D15" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -13334,7 +13308,7 @@
         <v>200</v>
       </c>
       <c r="D16" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
     </row>
   </sheetData>
@@ -13360,16 +13334,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C1" t="s">
         <v>1417</v>
       </c>
-      <c r="B1" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1419</v>
-      </c>
       <c r="D1" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -13383,7 +13357,7 @@
         <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -13397,7 +13371,7 @@
         <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -13411,7 +13385,7 @@
         <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -13425,7 +13399,7 @@
         <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -13439,7 +13413,7 @@
         <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -13453,7 +13427,7 @@
         <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -13467,7 +13441,7 @@
         <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -13481,7 +13455,7 @@
         <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -13495,7 +13469,7 @@
         <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -13509,7 +13483,7 @@
         <v>110</v>
       </c>
       <c r="D11" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -13523,7 +13497,7 @@
         <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -13537,7 +13511,7 @@
         <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -13551,7 +13525,7 @@
         <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -13565,7 +13539,7 @@
         <v>125</v>
       </c>
       <c r="D15" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -13579,7 +13553,7 @@
         <v>125</v>
       </c>
       <c r="D16" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -13593,7 +13567,7 @@
         <v>125</v>
       </c>
       <c r="D17" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -13607,7 +13581,7 @@
         <v>160</v>
       </c>
       <c r="D18" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -13621,7 +13595,7 @@
         <v>160</v>
       </c>
       <c r="D19" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -13635,7 +13609,7 @@
         <v>160</v>
       </c>
       <c r="D20" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -13649,7 +13623,7 @@
         <v>200</v>
       </c>
       <c r="D21" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -13663,7 +13637,7 @@
         <v>200</v>
       </c>
       <c r="D22" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
     </row>
   </sheetData>
@@ -13688,16 +13662,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C1" t="s">
         <v>1417</v>
       </c>
-      <c r="B1" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1419</v>
-      </c>
       <c r="D1" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -13711,7 +13685,7 @@
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -13725,7 +13699,7 @@
         <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -13739,7 +13713,7 @@
         <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -13753,7 +13727,7 @@
         <v>125</v>
       </c>
       <c r="D5" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -13767,7 +13741,7 @@
         <v>160</v>
       </c>
       <c r="D6" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -13781,7 +13755,7 @@
         <v>200</v>
       </c>
       <c r="D7" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
     </row>
   </sheetData>
@@ -13807,100 +13781,100 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C1" t="s">
         <v>1417</v>
       </c>
-      <c r="B1" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1419</v>
-      </c>
       <c r="D1" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="B2" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="C2">
         <v>200</v>
       </c>
       <c r="D2" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="B3" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="C3">
         <v>250</v>
       </c>
       <c r="D3" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="B4" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="C4">
         <v>315</v>
       </c>
       <c r="D4" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="B5" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="C5">
         <v>400</v>
       </c>
       <c r="D5" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="B6" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="C6">
         <v>500</v>
       </c>
       <c r="D6" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="B7" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="C7">
         <v>630</v>
       </c>
       <c r="D7" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
   </sheetData>
@@ -13921,114 +13895,114 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C1" t="s">
         <v>1417</v>
       </c>
-      <c r="B1" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1419</v>
-      </c>
       <c r="D1" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="B2" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="C2">
         <v>160</v>
       </c>
       <c r="D2" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="B3" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="C3">
         <v>200</v>
       </c>
       <c r="D3" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="B4" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="C4">
         <v>250</v>
       </c>
       <c r="D4" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="B5" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="C5">
         <v>300</v>
       </c>
       <c r="D5" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="B6" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="C6">
         <v>400</v>
       </c>
       <c r="D6" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="B7" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="C7">
         <v>500</v>
       </c>
       <c r="D7" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="B8" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="C8">
         <v>600</v>
       </c>
       <c r="D8" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
   </sheetData>
@@ -14050,590 +14024,590 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C1" t="s">
         <v>1417</v>
       </c>
-      <c r="B1" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1419</v>
-      </c>
       <c r="D1" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B2" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C2">
         <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="B3" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="C3">
         <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B4" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="C4">
         <v>125</v>
       </c>
       <c r="D4" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B5" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="C5">
         <v>125</v>
       </c>
       <c r="D5" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B6" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="C6">
         <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="B7" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="C7">
         <v>160</v>
       </c>
       <c r="D7" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="B8" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="C8">
         <v>160</v>
       </c>
       <c r="D8" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B9" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="C9">
         <v>160</v>
       </c>
       <c r="D9" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="B10" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="C10">
         <v>160</v>
       </c>
       <c r="D10" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="B11" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="C11">
         <v>160</v>
       </c>
       <c r="D11" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="B12" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="C12">
         <v>160</v>
       </c>
       <c r="D12" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B13" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="C13">
         <v>200</v>
       </c>
       <c r="D13" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="B14" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="C14">
         <v>200</v>
       </c>
       <c r="D14" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="B15" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="C15">
         <v>200</v>
       </c>
       <c r="D15" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="B16" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="C16">
         <v>200</v>
       </c>
       <c r="D16" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B17" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="C17">
         <v>200</v>
       </c>
       <c r="D17" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B18" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="C18">
         <v>200</v>
       </c>
       <c r="D18" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="B19" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="C19">
         <v>250</v>
       </c>
       <c r="D19" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="B20" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="C20">
         <v>250</v>
       </c>
       <c r="D20" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="B21" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="C21">
         <v>250</v>
       </c>
       <c r="D21" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="B22" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="C22">
         <v>250</v>
       </c>
       <c r="D22" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B23" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="C23">
         <v>250</v>
       </c>
       <c r="D23" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="B24" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="C24">
         <v>250</v>
       </c>
       <c r="D24" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="B25" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="C25">
         <v>315</v>
       </c>
       <c r="D25" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="B26" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="C26">
         <v>315</v>
       </c>
       <c r="D26" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="B27" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="C27">
         <v>315</v>
       </c>
       <c r="D27" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="B28" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="C28">
         <v>315</v>
       </c>
       <c r="D28" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="B29" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="C29">
         <v>315</v>
       </c>
       <c r="D29" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="B30" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="C30">
         <v>315</v>
       </c>
       <c r="D30" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="B31" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="C31">
         <v>400</v>
       </c>
       <c r="D31" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B32" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="C32">
         <v>400</v>
       </c>
       <c r="D32" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="B33" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="C33">
         <v>400</v>
       </c>
       <c r="D33" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="B34" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="C34">
         <v>400</v>
       </c>
       <c r="D34" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="B35" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="C35">
         <v>400</v>
       </c>
       <c r="D35" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="B36" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C36">
         <v>400</v>
       </c>
       <c r="D36" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="B37" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="C37">
         <v>500</v>
       </c>
       <c r="D37" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="B38" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="C38">
         <v>500</v>
       </c>
       <c r="D38" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="B39" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="C39">
         <v>500</v>
       </c>
       <c r="D39" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="B40" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="C40">
         <v>500</v>
       </c>
       <c r="D40" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="B41" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="C41">
         <v>500</v>
       </c>
       <c r="D41" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="B42" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="C42">
         <v>500</v>
       </c>
       <c r="D42" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
   </sheetData>
@@ -14653,422 +14627,422 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C1" t="s">
         <v>1417</v>
       </c>
-      <c r="B1" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1419</v>
-      </c>
       <c r="D1" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B2" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="C2">
         <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B3" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="C3">
         <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="B4" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="C4">
         <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="B5" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C5">
         <v>125</v>
       </c>
       <c r="D5" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="B6" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C6">
         <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="B7" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="C7">
         <v>160</v>
       </c>
       <c r="D7" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="B8" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="C8">
         <v>160</v>
       </c>
       <c r="D8" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="B9" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="C9">
         <v>160</v>
       </c>
       <c r="D9" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="B10" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="C10">
         <v>160</v>
       </c>
       <c r="D10" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B11" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="C11">
         <v>160</v>
       </c>
       <c r="D11" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="B12" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="C12">
         <v>200</v>
       </c>
       <c r="D12" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="B13" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="C13">
         <v>200</v>
       </c>
       <c r="D13" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="B14" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="C14">
         <v>200</v>
       </c>
       <c r="D14" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="B15" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="C15">
         <v>200</v>
       </c>
       <c r="D15" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="B16" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="C16">
         <v>250</v>
       </c>
       <c r="D16" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B17" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="C17">
         <v>250</v>
       </c>
       <c r="D17" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B18" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="C18">
         <v>250</v>
       </c>
       <c r="D18" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="B19" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="C19">
         <v>250</v>
       </c>
       <c r="D19" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="B20" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="C20">
         <v>315</v>
       </c>
       <c r="D20" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="B21" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="C21">
         <v>315</v>
       </c>
       <c r="D21" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="B22" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="C22">
         <v>315</v>
       </c>
       <c r="D22" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="B23" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="C23">
         <v>315</v>
       </c>
       <c r="D23" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="B24" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="C24">
         <v>400</v>
       </c>
       <c r="D24" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="B25" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C25">
         <v>400</v>
       </c>
       <c r="D25" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="B26" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="C26">
         <v>400</v>
       </c>
       <c r="D26" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B27" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="C27">
         <v>400</v>
       </c>
       <c r="D27" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="B28" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="C28">
         <v>500</v>
       </c>
       <c r="D28" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B29" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="C29">
         <v>500</v>
       </c>
       <c r="D29" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="B30" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="C30">
         <v>500</v>
       </c>
       <c r="D30" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
   </sheetData>
@@ -15088,16 +15062,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C1" t="s">
         <v>1417</v>
       </c>
-      <c r="B1" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1419</v>
-      </c>
       <c r="D1" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -15111,7 +15085,7 @@
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -15125,7 +15099,7 @@
         <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -15139,7 +15113,7 @@
         <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -15153,7 +15127,7 @@
         <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -15167,7 +15141,7 @@
         <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -15181,7 +15155,7 @@
         <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -15195,7 +15169,7 @@
         <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -15209,7 +15183,7 @@
         <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -15223,7 +15197,7 @@
         <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -15237,7 +15211,7 @@
         <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -15251,7 +15225,7 @@
         <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -15265,7 +15239,7 @@
         <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -15279,7 +15253,7 @@
         <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -15293,7 +15267,7 @@
         <v>110</v>
       </c>
       <c r="D15" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -15307,7 +15281,7 @@
         <v>125</v>
       </c>
       <c r="D16" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -15321,7 +15295,7 @@
         <v>125</v>
       </c>
       <c r="D17" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -15335,7 +15309,7 @@
         <v>140</v>
       </c>
       <c r="D18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -15349,7 +15323,7 @@
         <v>140</v>
       </c>
       <c r="D19" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -15363,7 +15337,7 @@
         <v>160</v>
       </c>
       <c r="D20" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -15377,7 +15351,7 @@
         <v>160</v>
       </c>
       <c r="D21" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -15391,7 +15365,7 @@
         <v>180</v>
       </c>
       <c r="D22" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -15405,7 +15379,7 @@
         <v>180</v>
       </c>
       <c r="D23" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -15419,7 +15393,7 @@
         <v>200</v>
       </c>
       <c r="D24" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -15433,7 +15407,7 @@
         <v>200</v>
       </c>
       <c r="D25" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -15447,7 +15421,7 @@
         <v>225</v>
       </c>
       <c r="D26" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -15461,7 +15435,7 @@
         <v>225</v>
       </c>
       <c r="D27" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -15475,7 +15449,7 @@
         <v>250</v>
       </c>
       <c r="D28" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -15489,7 +15463,7 @@
         <v>250</v>
       </c>
       <c r="D29" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -15503,7 +15477,7 @@
         <v>280</v>
       </c>
       <c r="D30" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -15517,7 +15491,7 @@
         <v>280</v>
       </c>
       <c r="D31" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -15531,7 +15505,7 @@
         <v>315</v>
       </c>
       <c r="D32" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -15545,7 +15519,7 @@
         <v>315</v>
       </c>
       <c r="D33" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -15559,7 +15533,7 @@
         <v>355</v>
       </c>
       <c r="D34" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -15573,7 +15547,7 @@
         <v>355</v>
       </c>
       <c r="D35" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -15587,7 +15561,7 @@
         <v>400</v>
       </c>
       <c r="D36" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -15601,7 +15575,7 @@
         <v>400</v>
       </c>
       <c r="D37" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
   </sheetData>
